--- a/Results1.xlsx
+++ b/Results1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raouf\Desktop\Clan_Chest\Chest_Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C92FD2-503D-4681-9241-DB3743D30613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA9B3FE-E7E8-4639-842F-159E7DAFB1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8B40F6D1-9A99-4C4C-A584-B5A2D365FA79}"/>
   </bookViews>
@@ -938,31 +938,31 @@
         <v>82</v>
       </c>
       <c r="B2" s="1">
-        <v>3979</v>
+        <v>4537</v>
       </c>
       <c r="C2" s="1">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="D2" s="1">
         <v>13</v>
       </c>
       <c r="E2" s="1">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F2" s="1">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J2" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V2" s="1">
         <v>0</v>
@@ -1070,22 +1070,22 @@
     </row>
     <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="B3" s="1">
-        <v>3318</v>
+        <v>3775</v>
       </c>
       <c r="C3" s="1">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D3" s="1">
         <v>13</v>
       </c>
       <c r="E3" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1094,19 +1094,19 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="1">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         <v>0</v>
       </c>
       <c r="S3" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T3" s="1">
         <v>0</v>
       </c>
       <c r="U3" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V3" s="1">
         <v>0</v>
       </c>
       <c r="W3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y3" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z3" s="1">
         <v>1</v>
       </c>
       <c r="AA3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB3" s="1">
         <v>1</v>
@@ -1205,88 +1205,88 @@
     </row>
     <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B4" s="1">
-        <v>3276</v>
+        <v>3774</v>
       </c>
       <c r="C4" s="1">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="D4" s="1">
         <v>13</v>
       </c>
       <c r="E4" s="1">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1">
+        <v>50</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>4</v>
+      </c>
+      <c r="J4" s="1">
+        <v>9</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>18</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1">
+        <v>5</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1">
         <v>1</v>
       </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>8</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
-        <v>28</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1">
-        <v>0</v>
-      </c>
-      <c r="P4" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1">
-        <v>0</v>
-      </c>
-      <c r="S4" s="1">
-        <v>0</v>
-      </c>
-      <c r="T4" s="1">
-        <v>0</v>
-      </c>
-      <c r="U4" s="1">
-        <v>0</v>
-      </c>
-      <c r="V4" s="1">
-        <v>0</v>
-      </c>
-      <c r="W4" s="1">
-        <v>0</v>
-      </c>
       <c r="X4" s="1">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Y4" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AB4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="1">
         <v>0</v>
@@ -1340,88 +1340,88 @@
     </row>
     <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1">
-        <v>3178</v>
+        <v>3682</v>
       </c>
       <c r="C5" s="1">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D5" s="1">
         <v>13</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1">
+        <v>44</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>2</v>
+      </c>
+      <c r="M5" s="1">
+        <v>8</v>
+      </c>
+      <c r="N5" s="1">
+        <v>2</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>5</v>
+      </c>
+      <c r="V5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
-        <v>54</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>6</v>
-      </c>
-      <c r="T5" s="1">
-        <v>0</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0</v>
-      </c>
-      <c r="V5" s="1">
-        <v>0</v>
-      </c>
       <c r="W5" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X5" s="1">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="1">
         <v>0</v>
       </c>
       <c r="AA5" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB5" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="1">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="AH5" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
@@ -1475,22 +1475,22 @@
     </row>
     <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="B6" s="1">
-        <v>3015</v>
+        <v>3326</v>
       </c>
       <c r="C6" s="1">
-        <v>94</v>
+        <v>198</v>
       </c>
       <c r="D6" s="1">
         <v>13</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F6" s="1">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1499,64 +1499,64 @@
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>28</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>5</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
         <v>13</v>
       </c>
-      <c r="K6" s="1">
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
         <v>2</v>
       </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1">
-        <v>15</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>6</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0</v>
-      </c>
-      <c r="V6" s="1">
-        <v>0</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-      <c r="X6" s="1">
-        <v>7</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>14</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>3</v>
-      </c>
       <c r="AB6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="1">
         <v>0</v>
@@ -1610,89 +1610,89 @@
     </row>
     <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B7" s="1">
-        <v>2932</v>
+        <v>3178</v>
       </c>
       <c r="C7" s="1">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D7" s="1">
         <v>13</v>
       </c>
       <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>35</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>54</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>6</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="1">
         <v>17</v>
       </c>
-      <c r="F7" s="1">
-        <v>27</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1">
-        <v>34</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>2</v>
-      </c>
-      <c r="M7" s="1">
-        <v>4</v>
-      </c>
-      <c r="N7" s="1">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>1</v>
-      </c>
-      <c r="W7" s="1">
-        <v>2</v>
-      </c>
-      <c r="X7" s="1">
-        <v>32</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AB7" s="1">
-        <v>0</v>
-      </c>
       <c r="AC7" s="1">
         <v>0</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
@@ -1748,19 +1748,19 @@
         <v>116</v>
       </c>
       <c r="B8" s="1">
-        <v>2456</v>
+        <v>3016</v>
       </c>
       <c r="C8" s="1">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="D8" s="1">
         <v>13</v>
       </c>
       <c r="E8" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J8" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N8" s="1">
         <v>6</v>
@@ -1805,16 +1805,16 @@
         <v>0</v>
       </c>
       <c r="U8" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V8" s="1">
         <v>0</v>
       </c>
       <c r="W8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X8" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y8" s="1">
         <v>8</v>
@@ -1880,43 +1880,43 @@
     </row>
     <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B9" s="1">
-        <v>2360</v>
+        <v>2800</v>
       </c>
       <c r="C9" s="1">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="D9" s="1">
         <v>13</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J9" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N9" s="1">
         <v>0</v>
@@ -1931,16 +1931,16 @@
         <v>0</v>
       </c>
       <c r="R9" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T9" s="1">
         <v>0</v>
       </c>
       <c r="U9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V9" s="1">
         <v>0</v>
@@ -1949,19 +1949,19 @@
         <v>0</v>
       </c>
       <c r="X9" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y9" s="1">
         <v>0</v>
       </c>
       <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
         <v>11</v>
       </c>
-      <c r="AA9" s="1">
-        <v>0</v>
-      </c>
       <c r="AB9" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="1">
         <v>0</v>
@@ -2015,89 +2015,89 @@
     </row>
     <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="B10" s="1">
-        <v>2344</v>
+        <v>2654</v>
       </c>
       <c r="C10" s="1">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="D10" s="1">
         <v>13</v>
       </c>
       <c r="E10" s="1">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>27</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>40</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>11</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <v>5</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="1">
-        <v>24</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>6</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1">
-        <v>2</v>
-      </c>
-      <c r="N10" s="1">
-        <v>4</v>
-      </c>
-      <c r="O10" s="1">
-        <v>2</v>
-      </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0</v>
-      </c>
-      <c r="V10" s="1">
-        <v>1</v>
-      </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
-      <c r="X10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>15</v>
-      </c>
-      <c r="Z10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="1">
-        <v>0</v>
-      </c>
       <c r="AC10" s="1">
         <v>0</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
@@ -2153,10 +2153,10 @@
         <v>83</v>
       </c>
       <c r="B11" s="1">
-        <v>2308</v>
+        <v>2618</v>
       </c>
       <c r="C11" s="1">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D11" s="1">
         <v>13</v>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>2</v>
       </c>
       <c r="N11" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="U11" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V11" s="1">
         <v>0</v>
@@ -2285,82 +2285,82 @@
     </row>
     <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1">
-        <v>2202</v>
+        <v>2568</v>
       </c>
       <c r="C12" s="1">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="D12" s="1">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1">
+        <v>24</v>
+      </c>
+      <c r="F12" s="1">
+        <v>11</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>8</v>
+      </c>
+      <c r="J12" s="1">
+        <v>9</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>8</v>
+      </c>
+      <c r="N12" s="1">
+        <v>10</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>6</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="1">
-        <v>21</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="V12" s="1">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y12" s="1">
         <v>4</v>
       </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>3</v>
-      </c>
-      <c r="J12" s="1">
-        <v>7</v>
-      </c>
-      <c r="K12" s="1">
-        <v>5</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>6</v>
-      </c>
-      <c r="N12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <v>0</v>
-      </c>
-      <c r="U12" s="1">
-        <v>0</v>
-      </c>
-      <c r="V12" s="1">
-        <v>0</v>
-      </c>
-      <c r="W12" s="1">
-        <v>0</v>
-      </c>
-      <c r="X12" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>7</v>
-      </c>
       <c r="Z12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
@@ -2420,22 +2420,22 @@
     </row>
     <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1">
-        <v>2145</v>
+        <v>2459</v>
       </c>
       <c r="C13" s="1">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D13" s="1">
         <v>13</v>
       </c>
       <c r="E13" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -2447,22 +2447,22 @@
         <v>0</v>
       </c>
       <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>4</v>
+      </c>
+      <c r="N13" s="1">
         <v>8</v>
       </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>7</v>
-      </c>
       <c r="O13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="1">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T13" s="1">
         <v>0</v>
       </c>
       <c r="U13" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V13" s="1">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="1">
         <v>0</v>
@@ -2504,10 +2504,10 @@
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AD13" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE13" s="1">
         <v>0</v>
@@ -2516,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="AG13" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH13" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -2555,106 +2555,106 @@
     </row>
     <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B14" s="1">
-        <v>2022</v>
+        <v>2434</v>
       </c>
       <c r="C14" s="1">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D14" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>26</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
         <v>6</v>
       </c>
-      <c r="F14" s="1">
-        <v>8</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>5</v>
-      </c>
-      <c r="J14" s="1">
-        <v>7</v>
-      </c>
       <c r="K14" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L14" s="1">
         <v>1</v>
       </c>
       <c r="M14" s="1">
+        <v>2</v>
+      </c>
+      <c r="N14" s="1">
+        <v>4</v>
+      </c>
+      <c r="O14" s="1">
+        <v>2</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
+        <v>5</v>
+      </c>
+      <c r="V14" s="1">
         <v>1</v>
       </c>
-      <c r="N14" s="1">
-        <v>2</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>9</v>
-      </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
-      <c r="U14" s="1">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
-        <v>0</v>
-      </c>
       <c r="W14" s="1">
         <v>0</v>
       </c>
       <c r="X14" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="1">
         <v>3</v>
-      </c>
-      <c r="AA14" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>3</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="1">
-        <v>0</v>
       </c>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
@@ -2690,19 +2690,19 @@
     </row>
     <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B15" s="1">
-        <v>2011</v>
+        <v>2360</v>
       </c>
       <c r="C15" s="1">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1">
         <v>13</v>
       </c>
       <c r="E15" s="1">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N15" s="1">
         <v>0</v>
@@ -2741,40 +2741,40 @@
         <v>0</v>
       </c>
       <c r="R15" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="1">
         <v>11</v>
       </c>
-      <c r="T15" s="1">
-        <v>0</v>
-      </c>
-      <c r="U15" s="1">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
-        <v>0</v>
-      </c>
-      <c r="W15" s="1">
-        <v>18</v>
-      </c>
-      <c r="X15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
       <c r="AA15" s="1">
         <v>0</v>
       </c>
       <c r="AB15" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC15" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
@@ -2786,10 +2786,10 @@
         <v>0</v>
       </c>
       <c r="AG15" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -2825,22 +2825,22 @@
     </row>
     <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="B16" s="1">
-        <v>2010</v>
+        <v>2294</v>
       </c>
       <c r="C16" s="1">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="D16" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F16" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -2852,64 +2852,64 @@
         <v>6</v>
       </c>
       <c r="J16" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="1">
+        <v>2</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>9</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1">
+        <v>5</v>
+      </c>
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
+        <v>9</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z16" s="1">
         <v>3</v>
       </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1">
-        <v>0</v>
-      </c>
-      <c r="S16" s="1">
-        <v>0</v>
-      </c>
-      <c r="T16" s="1">
-        <v>0</v>
-      </c>
-      <c r="U16" s="1">
-        <v>0</v>
-      </c>
-      <c r="V16" s="1">
-        <v>0</v>
-      </c>
-      <c r="W16" s="1">
-        <v>0</v>
-      </c>
-      <c r="X16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>17</v>
-      </c>
-      <c r="Z16" s="1">
-        <v>0</v>
-      </c>
       <c r="AA16" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB16" s="1">
         <v>1</v>
       </c>
       <c r="AC16" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD16" s="1">
         <v>0</v>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
@@ -2960,22 +2960,22 @@
     </row>
     <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B17" s="1">
-        <v>2004</v>
+        <v>2290</v>
       </c>
       <c r="C17" s="1">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="D17" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -2984,22 +2984,22 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J17" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L17" s="1">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M17" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
@@ -3023,19 +3023,19 @@
         <v>0</v>
       </c>
       <c r="V17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="X17" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y17" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA17" s="1">
         <v>0</v>
@@ -3098,28 +3098,28 @@
         <v>111</v>
       </c>
       <c r="B18" s="1">
-        <v>1998</v>
+        <v>2241</v>
       </c>
       <c r="C18" s="1">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="D18" s="1">
         <v>13</v>
       </c>
       <c r="E18" s="1">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F18" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I18" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="1">
         <v>3</v>
@@ -3131,7 +3131,7 @@
         <v>5</v>
       </c>
       <c r="M18" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18" s="1">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="U18" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" s="1">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         <v>3</v>
       </c>
       <c r="X18" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y18" s="1">
         <v>0</v>
@@ -3230,13 +3230,13 @@
     </row>
     <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1">
-        <v>1875</v>
+        <v>2205</v>
       </c>
       <c r="C19" s="1">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1">
         <v>13</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -3257,22 +3257,22 @@
         <v>0</v>
       </c>
       <c r="J19" s="1">
+        <v>8</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
         <v>7</v>
       </c>
-      <c r="K19" s="1">
-        <v>6</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1">
-        <v>4</v>
-      </c>
       <c r="O19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="1">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="Y19" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Z19" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="1">
         <v>0</v>
@@ -3365,83 +3365,83 @@
     </row>
     <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1">
-        <v>1860</v>
+        <v>2165</v>
       </c>
       <c r="C20" s="1">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="D20" s="1">
         <v>13</v>
       </c>
       <c r="E20" s="1">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F20" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>2</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
         <v>3</v>
       </c>
-      <c r="H20" s="1">
+      <c r="N20" s="1">
+        <v>8</v>
+      </c>
+      <c r="O20" s="1">
         <v>2</v>
       </c>
-      <c r="I20" s="1">
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>6</v>
+      </c>
+      <c r="T20" s="1">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1">
+        <v>5</v>
+      </c>
+      <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="1">
         <v>2</v>
       </c>
-      <c r="J20" s="1">
-        <v>3</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1">
-        <v>15</v>
-      </c>
-      <c r="M20" s="1">
-        <v>6</v>
-      </c>
-      <c r="N20" s="1">
+      <c r="Z20" s="1">
         <v>1</v>
       </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>0</v>
-      </c>
-      <c r="R20" s="1">
-        <v>0</v>
-      </c>
-      <c r="S20" s="1">
-        <v>11</v>
-      </c>
-      <c r="T20" s="1">
-        <v>0</v>
-      </c>
-      <c r="U20" s="1">
-        <v>0</v>
-      </c>
-      <c r="V20" s="1">
-        <v>5</v>
-      </c>
-      <c r="W20" s="1">
-        <v>5</v>
-      </c>
-      <c r="X20" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="1">
-        <v>0</v>
-      </c>
       <c r="AA20" s="1">
         <v>0</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE20" s="1">
         <v>0</v>
@@ -3500,94 +3500,94 @@
     </row>
     <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="B21" s="1">
-        <v>1795</v>
+        <v>2120</v>
       </c>
       <c r="C21" s="1">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="D21" s="1">
         <v>13</v>
       </c>
       <c r="E21" s="1">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F21" s="1">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
       </c>
       <c r="L21" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>6</v>
+      </c>
+      <c r="T21" s="1">
+        <v>0</v>
+      </c>
+      <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
+        <v>1</v>
+      </c>
+      <c r="W21" s="1">
+        <v>5</v>
+      </c>
+      <c r="X21" s="1">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1">
         <v>4</v>
       </c>
-      <c r="N21" s="1">
-        <v>5</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>11</v>
-      </c>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
-      <c r="U21" s="1">
-        <v>0</v>
-      </c>
-      <c r="V21" s="1">
-        <v>0</v>
-      </c>
-      <c r="W21" s="1">
-        <v>0</v>
-      </c>
-      <c r="X21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="1">
-        <v>0</v>
-      </c>
       <c r="AB21" s="1">
         <v>0</v>
       </c>
       <c r="AC21" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="1">
         <v>0</v>
@@ -3596,10 +3596,10 @@
         <v>0</v>
       </c>
       <c r="AG21" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH21" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
@@ -3635,19 +3635,19 @@
     </row>
     <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B22" s="1">
-        <v>1793</v>
+        <v>2109</v>
       </c>
       <c r="C22" s="1">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="D22" s="1">
         <v>13</v>
       </c>
       <c r="E22" s="1">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -3656,10 +3656,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J22" s="1">
         <v>0</v>
@@ -3668,10 +3668,10 @@
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N22" s="1">
         <v>0</v>
@@ -3689,19 +3689,19 @@
         <v>0</v>
       </c>
       <c r="S22" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T22" s="1">
         <v>0</v>
       </c>
       <c r="U22" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V22" s="1">
         <v>0</v>
       </c>
       <c r="W22" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X22" s="1">
         <v>0</v>
@@ -3710,16 +3710,16 @@
         <v>0</v>
       </c>
       <c r="Z22" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="1">
         <v>0</v>
       </c>
       <c r="AB22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD22" s="1">
         <v>0</v>
@@ -3731,10 +3731,10 @@
         <v>0</v>
       </c>
       <c r="AG22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
@@ -3770,88 +3770,88 @@
     </row>
     <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1">
-        <v>1766</v>
+        <v>2105</v>
       </c>
       <c r="C23" s="1">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D23" s="1">
         <v>13</v>
       </c>
       <c r="E23" s="1">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="F23" s="1">
+        <v>19</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>4</v>
+      </c>
+      <c r="I23" s="1">
+        <v>6</v>
+      </c>
+      <c r="J23" s="1">
+        <v>5</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>11</v>
+      </c>
+      <c r="N23" s="1">
+        <v>2</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>0</v>
+      </c>
+      <c r="V23" s="1">
+        <v>0</v>
+      </c>
+      <c r="W23" s="1">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="1">
         <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>8</v>
-      </c>
-      <c r="N23" s="1">
-        <v>1</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
-      <c r="S23" s="1">
-        <v>6</v>
-      </c>
-      <c r="T23" s="1">
-        <v>0</v>
-      </c>
-      <c r="U23" s="1">
-        <v>0</v>
-      </c>
-      <c r="V23" s="1">
-        <v>0</v>
-      </c>
-      <c r="W23" s="1">
-        <v>0</v>
-      </c>
-      <c r="X23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="1">
-        <v>14</v>
-      </c>
-      <c r="AB23" s="1">
-        <v>0</v>
       </c>
       <c r="AC23" s="1">
         <v>0</v>
@@ -3905,46 +3905,46 @@
     </row>
     <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="B24" s="1">
-        <v>1762</v>
+        <v>2080</v>
       </c>
       <c r="C24" s="1">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="D24" s="1">
         <v>13</v>
       </c>
       <c r="E24" s="1">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F24" s="1">
+        <v>14</v>
+      </c>
+      <c r="G24" s="1">
         <v>5</v>
       </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J24" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M24" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N24" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T24" s="1">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X24" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y24" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z24" s="1">
         <v>0</v>
@@ -4040,19 +4040,19 @@
     </row>
     <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B25" s="1">
-        <v>1702</v>
+        <v>2054</v>
       </c>
       <c r="C25" s="1">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="D25" s="1">
         <v>13</v>
       </c>
       <c r="E25" s="1">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -4061,11 +4061,11 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
         <v>11</v>
       </c>
-      <c r="I25" s="1">
-        <v>2</v>
-      </c>
       <c r="J25" s="1">
         <v>0</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="1">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
@@ -4100,16 +4100,16 @@
         <v>0</v>
       </c>
       <c r="U25" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="1">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="X25" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="1">
         <v>0</v>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="AA25" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="1">
         <v>0</v>
@@ -4175,47 +4175,47 @@
     </row>
     <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B26" s="1">
-        <v>1666</v>
+        <v>2010</v>
       </c>
       <c r="C26" s="1">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="D26" s="1">
         <v>13</v>
       </c>
       <c r="E26" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J26" s="1">
+        <v>6</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
         <v>3</v>
       </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>14</v>
-      </c>
-      <c r="M26" s="1">
-        <v>6</v>
-      </c>
-      <c r="N26" s="1">
-        <v>0</v>
-      </c>
       <c r="O26" s="1">
         <v>0</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T26" s="1">
         <v>0</v>
@@ -4244,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="X26" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="1">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Z26" s="1">
         <v>0</v>
@@ -4256,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="AB26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" s="1">
         <v>0</v>
@@ -4310,85 +4310,85 @@
     </row>
     <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1">
-        <v>1648</v>
+        <v>2004</v>
       </c>
       <c r="C27" s="1">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D27" s="1">
         <v>13</v>
       </c>
       <c r="E27" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" s="1">
+        <v>19</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>17</v>
+      </c>
+      <c r="J27" s="1">
+        <v>14</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>3</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1">
+        <v>0</v>
+      </c>
+      <c r="T27" s="1">
+        <v>0</v>
+      </c>
+      <c r="U27" s="1">
+        <v>0</v>
+      </c>
+      <c r="V27" s="1">
+        <v>0</v>
+      </c>
+      <c r="W27" s="1">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1">
         <v>2</v>
       </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>2</v>
-      </c>
-      <c r="I27" s="1">
-        <v>1</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>2</v>
-      </c>
-      <c r="N27" s="1">
-        <v>0</v>
-      </c>
-      <c r="O27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
-      <c r="S27" s="1">
-        <v>6</v>
-      </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
-      <c r="U27" s="1">
-        <v>0</v>
-      </c>
-      <c r="V27" s="1">
-        <v>3</v>
-      </c>
-      <c r="W27" s="1">
-        <v>5</v>
-      </c>
-      <c r="X27" s="1">
-        <v>1</v>
-      </c>
       <c r="Y27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="1">
         <v>9</v>
-      </c>
-      <c r="Z27" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="1">
-        <v>0</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
@@ -4445,22 +4445,22 @@
     </row>
     <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B28" s="1">
-        <v>1622</v>
+        <v>1945</v>
       </c>
       <c r="C28" s="1">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D28" s="1">
         <v>13</v>
       </c>
       <c r="E28" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -4469,67 +4469,67 @@
         <v>0</v>
       </c>
       <c r="I28" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K28" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>4</v>
+      </c>
+      <c r="O28" s="1">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+      <c r="S28" s="1">
+        <v>6</v>
+      </c>
+      <c r="T28" s="1">
+        <v>0</v>
+      </c>
+      <c r="U28" s="1">
+        <v>5</v>
+      </c>
+      <c r="V28" s="1">
+        <v>0</v>
+      </c>
+      <c r="W28" s="1">
+        <v>0</v>
+      </c>
+      <c r="X28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z28" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="1">
         <v>3</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1">
-        <v>0</v>
-      </c>
-      <c r="O28" s="1">
-        <v>0</v>
-      </c>
-      <c r="P28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="1">
-        <v>0</v>
-      </c>
-      <c r="R28" s="1">
-        <v>0</v>
-      </c>
-      <c r="S28" s="1">
-        <v>0</v>
-      </c>
-      <c r="T28" s="1">
-        <v>0</v>
-      </c>
-      <c r="U28" s="1">
-        <v>0</v>
-      </c>
-      <c r="V28" s="1">
-        <v>0</v>
-      </c>
-      <c r="W28" s="1">
-        <v>0</v>
-      </c>
-      <c r="X28" s="1">
-        <v>2</v>
-      </c>
-      <c r="Y28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="1">
-        <v>8</v>
-      </c>
-      <c r="AB28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="1">
-        <v>0</v>
       </c>
       <c r="AD28" s="1">
         <v>0</v>
@@ -4580,46 +4580,46 @@
     </row>
     <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1">
-        <v>1622</v>
+        <v>1913</v>
       </c>
       <c r="C29" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D29" s="1">
         <v>13</v>
       </c>
       <c r="E29" s="1">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F29" s="1">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
+        <v>24</v>
+      </c>
+      <c r="J29" s="1">
         <v>1</v>
       </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1">
-        <v>0</v>
-      </c>
-      <c r="J29" s="1">
-        <v>3</v>
-      </c>
       <c r="K29" s="1">
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M29" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N29" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O29" s="1">
         <v>0</v>
@@ -4634,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T29" s="1">
         <v>0</v>
@@ -4649,10 +4649,10 @@
         <v>0</v>
       </c>
       <c r="X29" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="1">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="AH29" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
@@ -4715,22 +4715,22 @@
     </row>
     <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B30" s="1">
-        <v>1579</v>
+        <v>1882</v>
       </c>
       <c r="C30" s="1">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D30" s="1">
         <v>13</v>
       </c>
       <c r="E30" s="1">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F30" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -4739,22 +4739,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M30" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T30" s="1">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="AA30" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB30" s="1">
         <v>0</v>
@@ -4850,22 +4850,22 @@
     </row>
     <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="B31" s="1">
-        <v>1550</v>
+        <v>1852</v>
       </c>
       <c r="C31" s="1">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D31" s="1">
         <v>13</v>
       </c>
       <c r="E31" s="1">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F31" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -4874,10 +4874,10 @@
         <v>0</v>
       </c>
       <c r="I31" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N31" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -4904,13 +4904,13 @@
         <v>0</v>
       </c>
       <c r="S31" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T31" s="1">
         <v>0</v>
       </c>
       <c r="U31" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V31" s="1">
         <v>0</v>
@@ -4919,10 +4919,10 @@
         <v>0</v>
       </c>
       <c r="X31" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y31" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="1">
         <v>0</v>
@@ -4949,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="AH31" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
@@ -4985,62 +4985,62 @@
     </row>
     <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="B32" s="1">
-        <v>1484</v>
+        <v>1852</v>
       </c>
       <c r="C32" s="1">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E32" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F32" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J32" s="1">
         <v>4</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="1">
         <v>0</v>
       </c>
       <c r="M32" s="1">
+        <v>2</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1">
+        <v>0</v>
+      </c>
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>0</v>
+      </c>
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="1">
         <v>6</v>
       </c>
-      <c r="N32" s="1">
-        <v>0</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>0</v>
-      </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
-      <c r="S32" s="1">
-        <v>0</v>
-      </c>
       <c r="T32" s="1">
         <v>0</v>
       </c>
@@ -5048,25 +5048,25 @@
         <v>0</v>
       </c>
       <c r="V32" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W32" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X32" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Z32" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA32" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="1">
         <v>0</v>
@@ -5120,67 +5120,67 @@
     </row>
     <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B33" s="1">
-        <v>1477</v>
+        <v>1828</v>
       </c>
       <c r="C33" s="1">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="D33" s="1">
         <v>13</v>
       </c>
       <c r="E33" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F33" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>7</v>
+      </c>
+      <c r="J33" s="1">
+        <v>6</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
         <v>4</v>
       </c>
-      <c r="I33" s="1">
+      <c r="N33" s="1">
+        <v>8</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="1">
         <v>6</v>
       </c>
-      <c r="J33" s="1">
-        <v>3</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>7</v>
-      </c>
-      <c r="N33" s="1">
-        <v>2</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>0</v>
-      </c>
       <c r="T33" s="1">
         <v>0</v>
       </c>
       <c r="U33" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V33" s="1">
         <v>0</v>
@@ -5189,10 +5189,10 @@
         <v>0</v>
       </c>
       <c r="X33" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="1">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="AB33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" s="1">
         <v>0</v>
@@ -5255,19 +5255,19 @@
     </row>
     <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B34" s="1">
-        <v>1426</v>
+        <v>1800</v>
       </c>
       <c r="C34" s="1">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D34" s="1">
         <v>13</v>
       </c>
       <c r="E34" s="1">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -5276,10 +5276,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I34" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J34" s="1">
         <v>0</v>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="M34" s="1">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>0</v>
       </c>
       <c r="S34" s="1">
+        <v>0</v>
+      </c>
+      <c r="T34" s="1">
+        <v>0</v>
+      </c>
+      <c r="U34" s="1">
+        <v>5</v>
+      </c>
+      <c r="V34" s="1">
+        <v>0</v>
+      </c>
+      <c r="W34" s="1">
         <v>6</v>
       </c>
-      <c r="T34" s="1">
-        <v>0</v>
-      </c>
-      <c r="U34" s="1">
-        <v>0</v>
-      </c>
-      <c r="V34" s="1">
-        <v>0</v>
-      </c>
-      <c r="W34" s="1">
-        <v>0</v>
-      </c>
       <c r="X34" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y34" s="1">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="AA34" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB34" s="1">
         <v>0</v>
@@ -5390,23 +5390,23 @@
     </row>
     <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B35" s="1">
-        <v>1398</v>
+        <v>1771</v>
       </c>
       <c r="C35" s="1">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D35" s="1">
         <v>13</v>
       </c>
       <c r="E35" s="1">
+        <v>14</v>
+      </c>
+      <c r="F35" s="1">
         <v>9</v>
       </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
@@ -5414,10 +5414,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J35" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -5426,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="1">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N35" s="1">
         <v>0</v>
@@ -5444,38 +5444,38 @@
         <v>0</v>
       </c>
       <c r="S35" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T35" s="1">
         <v>0</v>
       </c>
       <c r="U35" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
       </c>
       <c r="W35" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" s="1">
+        <v>19</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="1">
         <v>9</v>
       </c>
-      <c r="Y35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="1">
-        <v>6</v>
-      </c>
-      <c r="AB35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="1">
-        <v>0</v>
-      </c>
       <c r="AD35" s="1">
         <v>0</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AH35" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
@@ -5525,43 +5525,43 @@
     </row>
     <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="B36" s="1">
-        <v>1378</v>
+        <v>1702</v>
       </c>
       <c r="C36" s="1">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="D36" s="1">
         <v>13</v>
       </c>
       <c r="E36" s="1">
+        <v>28</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2</v>
+      </c>
+      <c r="I36" s="1">
         <v>9</v>
       </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1">
-        <v>0</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
       <c r="J36" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M36" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N36" s="1">
         <v>0</v>
@@ -5594,10 +5594,10 @@
         <v>0</v>
       </c>
       <c r="X36" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y36" s="1">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Z36" s="1">
         <v>0</v>
@@ -5660,22 +5660,22 @@
     </row>
     <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="B37" s="1">
-        <v>1330</v>
+        <v>1669</v>
       </c>
       <c r="C37" s="1">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="D37" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E37" s="1">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F37" s="1">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -5687,22 +5687,22 @@
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M37" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N37" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P37" s="1">
         <v>0</v>
@@ -5714,25 +5714,25 @@
         <v>0</v>
       </c>
       <c r="S37" s="1">
+        <v>0</v>
+      </c>
+      <c r="T37" s="1">
+        <v>0</v>
+      </c>
+      <c r="U37" s="1">
+        <v>3</v>
+      </c>
+      <c r="V37" s="1">
+        <v>1</v>
+      </c>
+      <c r="W37" s="1">
         <v>6</v>
       </c>
-      <c r="T37" s="1">
-        <v>0</v>
-      </c>
-      <c r="U37" s="1">
-        <v>0</v>
-      </c>
-      <c r="V37" s="1">
-        <v>0</v>
-      </c>
-      <c r="W37" s="1">
-        <v>0</v>
-      </c>
       <c r="X37" s="1">
         <v>0</v>
       </c>
       <c r="Y37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="1">
         <v>0</v>
@@ -5795,22 +5795,22 @@
     </row>
     <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="B38" s="1">
-        <v>1325</v>
+        <v>1631</v>
       </c>
       <c r="C38" s="1">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="D38" s="1">
         <v>13</v>
       </c>
       <c r="E38" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F38" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
@@ -5819,25 +5819,25 @@
         <v>0</v>
       </c>
       <c r="I38" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J38" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
       </c>
       <c r="L38" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M38" s="1">
         <v>3</v>
       </c>
       <c r="N38" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O38" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P38" s="1">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T38" s="1">
         <v>0</v>
@@ -5930,46 +5930,46 @@
     </row>
     <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="B39" s="1">
-        <v>1296</v>
+        <v>1617</v>
       </c>
       <c r="C39" s="1">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D39" s="1">
+        <v>13</v>
+      </c>
+      <c r="E39" s="1">
+        <v>16</v>
+      </c>
+      <c r="F39" s="1">
+        <v>3</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>4</v>
+      </c>
+      <c r="J39" s="1">
+        <v>4</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
         <v>5</v>
       </c>
-      <c r="E39" s="1">
-        <v>8</v>
-      </c>
-      <c r="F39" s="1">
-        <v>8</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
-        <v>7</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
-        <v>4</v>
-      </c>
       <c r="N39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -5984,13 +5984,13 @@
         <v>0</v>
       </c>
       <c r="S39" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T39" s="1">
         <v>0</v>
       </c>
       <c r="U39" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -5999,19 +5999,19 @@
         <v>0</v>
       </c>
       <c r="X39" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y39" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z39" s="1">
         <v>0</v>
       </c>
       <c r="AA39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC39" s="1">
         <v>0</v>
@@ -6065,31 +6065,31 @@
     </row>
     <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1">
-        <v>1266</v>
+        <v>1555</v>
       </c>
       <c r="C40" s="1">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D40" s="1">
         <v>13</v>
       </c>
       <c r="E40" s="1">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F40" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G40" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="1">
         <v>0</v>
@@ -6098,16 +6098,16 @@
         <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M40" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N40" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O40" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P40" s="1">
         <v>0</v>
@@ -6125,16 +6125,16 @@
         <v>0</v>
       </c>
       <c r="U40" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="1">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AA40" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
@@ -6200,61 +6200,61 @@
     </row>
     <row r="41" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B41" s="1">
-        <v>1250</v>
+        <v>1552</v>
       </c>
       <c r="C41" s="1">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D41" s="1">
         <v>13</v>
       </c>
       <c r="E41" s="1">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
       <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>5</v>
+      </c>
+      <c r="K41" s="1">
+        <v>2</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>2</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1">
         <v>1</v>
       </c>
-      <c r="I41" s="1">
-        <v>10</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
-        <v>6</v>
-      </c>
-      <c r="M41" s="1">
-        <v>6</v>
-      </c>
-      <c r="N41" s="1">
-        <v>0</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="1">
-        <v>0</v>
-      </c>
-      <c r="R41" s="1">
-        <v>0</v>
-      </c>
       <c r="S41" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T41" s="1">
         <v>0</v>
@@ -6263,22 +6263,22 @@
         <v>0</v>
       </c>
       <c r="V41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="1">
         <v>0</v>
       </c>
       <c r="X41" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="1">
         <v>4</v>
       </c>
-      <c r="Y41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="1">
-        <v>0</v>
-      </c>
       <c r="AA41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="1">
         <v>0</v>
@@ -6335,88 +6335,88 @@
     </row>
     <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="B42" s="1">
-        <v>1249</v>
+        <v>1484</v>
       </c>
       <c r="C42" s="1">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D42" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1">
+        <v>15</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>6</v>
+      </c>
+      <c r="N42" s="1">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0</v>
+      </c>
+      <c r="P42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>0</v>
+      </c>
+      <c r="R42" s="1">
+        <v>0</v>
+      </c>
+      <c r="S42" s="1">
+        <v>0</v>
+      </c>
+      <c r="T42" s="1">
+        <v>0</v>
+      </c>
+      <c r="U42" s="1">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1">
+        <v>0</v>
+      </c>
+      <c r="W42" s="1">
+        <v>0</v>
+      </c>
+      <c r="X42" s="1">
+        <v>12</v>
+      </c>
+      <c r="Y42" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="1">
         <v>3</v>
       </c>
-      <c r="G42" s="1">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1">
-        <v>14</v>
-      </c>
-      <c r="J42" s="1">
+      <c r="AB42" s="1">
         <v>1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <v>2</v>
-      </c>
-      <c r="M42" s="1">
-        <v>9</v>
-      </c>
-      <c r="N42" s="1">
-        <v>3</v>
-      </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>0</v>
-      </c>
-      <c r="R42" s="1">
-        <v>0</v>
-      </c>
-      <c r="S42" s="1">
-        <v>0</v>
-      </c>
-      <c r="T42" s="1">
-        <v>0</v>
-      </c>
-      <c r="U42" s="1">
-        <v>0</v>
-      </c>
-      <c r="V42" s="1">
-        <v>0</v>
-      </c>
-      <c r="W42" s="1">
-        <v>0</v>
-      </c>
-      <c r="X42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="1">
-        <v>0</v>
       </c>
       <c r="AC42" s="1">
         <v>0</v>
@@ -6470,88 +6470,88 @@
     </row>
     <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="B43" s="1">
-        <v>1234</v>
+        <v>1476</v>
       </c>
       <c r="C43" s="1">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D43" s="1">
         <v>13</v>
       </c>
       <c r="E43" s="1">
+        <v>23</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>10</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
         <v>20</v>
       </c>
-      <c r="F43" s="1">
-        <v>3</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
-        <v>3</v>
-      </c>
-      <c r="I43" s="1">
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+      <c r="S43" s="1">
         <v>6</v>
       </c>
-      <c r="J43" s="1">
-        <v>4</v>
-      </c>
-      <c r="K43" s="1">
-        <v>0</v>
-      </c>
-      <c r="L43" s="1">
-        <v>0</v>
-      </c>
-      <c r="M43" s="1">
-        <v>0</v>
-      </c>
-      <c r="N43" s="1">
-        <v>0</v>
-      </c>
-      <c r="O43" s="1">
-        <v>0</v>
-      </c>
-      <c r="P43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>0</v>
-      </c>
-      <c r="R43" s="1">
-        <v>0</v>
-      </c>
-      <c r="S43" s="1">
-        <v>0</v>
-      </c>
       <c r="T43" s="1">
         <v>0</v>
       </c>
       <c r="U43" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
       </c>
       <c r="W43" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X43" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Y43" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="1">
         <v>0</v>
       </c>
       <c r="AA43" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC43" s="1">
         <v>0</v>
@@ -6605,77 +6605,77 @@
     </row>
     <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="B44" s="1">
-        <v>1233</v>
+        <v>1463</v>
       </c>
       <c r="C44" s="1">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D44" s="1">
         <v>13</v>
       </c>
       <c r="E44" s="1">
+        <v>24</v>
+      </c>
+      <c r="F44" s="1">
+        <v>2</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>23</v>
+      </c>
+      <c r="N44" s="1">
+        <v>1</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>2</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1">
         <v>5</v>
       </c>
-      <c r="F44" s="1">
-        <v>4</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="1">
+      <c r="X44" s="1">
         <v>1</v>
       </c>
-      <c r="J44" s="1">
-        <v>4</v>
-      </c>
-      <c r="K44" s="1">
-        <v>0</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>2</v>
-      </c>
-      <c r="N44" s="1">
-        <v>0</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>6</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1">
-        <v>0</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
-      </c>
-      <c r="W44" s="1">
-        <v>2</v>
-      </c>
-      <c r="X44" s="1">
-        <v>19</v>
-      </c>
       <c r="Y44" s="1">
         <v>0</v>
       </c>
@@ -6683,13 +6683,13 @@
         <v>0</v>
       </c>
       <c r="AA44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" s="1">
         <v>0</v>
       </c>
       <c r="AC44" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD44" s="1">
         <v>0</v>
@@ -6704,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="AH44" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
@@ -6740,22 +6740,22 @@
     </row>
     <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B45" s="1">
-        <v>1210</v>
+        <v>1448</v>
       </c>
       <c r="C45" s="1">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D45" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E45" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F45" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
@@ -6767,20 +6767,20 @@
         <v>0</v>
       </c>
       <c r="J45" s="1">
+        <v>8</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>4</v>
+      </c>
+      <c r="N45" s="1">
         <v>1</v>
       </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
-      <c r="L45" s="1">
-        <v>0</v>
-      </c>
-      <c r="M45" s="1">
-        <v>0</v>
-      </c>
-      <c r="N45" s="1">
-        <v>3</v>
-      </c>
       <c r="O45" s="1">
         <v>0</v>
       </c>
@@ -6812,16 +6812,16 @@
         <v>0</v>
       </c>
       <c r="Y45" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z45" s="1">
         <v>0</v>
       </c>
       <c r="AA45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC45" s="1">
         <v>0</v>
@@ -6875,22 +6875,22 @@
     </row>
     <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1">
-        <v>1189</v>
+        <v>1446</v>
       </c>
       <c r="C46" s="1">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D46" s="1">
         <v>13</v>
       </c>
       <c r="E46" s="1">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G46" s="1">
         <v>0</v>
@@ -6911,10 +6911,10 @@
         <v>0</v>
       </c>
       <c r="M46" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N46" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O46" s="1">
         <v>0</v>
@@ -6944,16 +6944,16 @@
         <v>0</v>
       </c>
       <c r="X46" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y46" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z46" s="1">
         <v>0</v>
       </c>
       <c r="AA46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB46" s="1">
         <v>0</v>
@@ -7010,88 +7010,88 @@
     </row>
     <row r="47" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="B47" s="1">
-        <v>1188</v>
+        <v>1438</v>
       </c>
       <c r="C47" s="1">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D47" s="1">
         <v>13</v>
       </c>
       <c r="E47" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="1">
+        <v>6</v>
+      </c>
+      <c r="T47" s="1">
+        <v>0</v>
+      </c>
+      <c r="U47" s="1">
         <v>3</v>
       </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="J47" s="1">
-        <v>3</v>
-      </c>
-      <c r="K47" s="1">
-        <v>0</v>
-      </c>
-      <c r="L47" s="1">
-        <v>0</v>
-      </c>
-      <c r="M47" s="1">
-        <v>0</v>
-      </c>
-      <c r="N47" s="1">
-        <v>0</v>
-      </c>
-      <c r="O47" s="1">
-        <v>0</v>
-      </c>
-      <c r="P47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>0</v>
-      </c>
-      <c r="R47" s="1">
-        <v>0</v>
-      </c>
-      <c r="S47" s="1">
-        <v>3</v>
-      </c>
-      <c r="T47" s="1">
-        <v>0</v>
-      </c>
-      <c r="U47" s="1">
-        <v>0</v>
-      </c>
       <c r="V47" s="1">
         <v>0</v>
       </c>
       <c r="W47" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" s="1">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Z47" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="1">
         <v>0</v>
       </c>
       <c r="AB47" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC47" s="1">
         <v>0</v>
@@ -7145,34 +7145,34 @@
     </row>
     <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="B48" s="1">
-        <v>1160</v>
+        <v>1422</v>
       </c>
       <c r="C48" s="1">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E48" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
         <v>4</v>
       </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="1">
-        <v>1</v>
-      </c>
       <c r="J48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
         <v>0</v>
@@ -7181,7 +7181,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N48" s="1">
         <v>0</v>
@@ -7214,16 +7214,16 @@
         <v>0</v>
       </c>
       <c r="X48" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y48" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="1">
         <v>0</v>
       </c>
       <c r="AA48" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -7280,35 +7280,35 @@
     </row>
     <row r="49" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="B49" s="1">
-        <v>1136</v>
+        <v>1420</v>
       </c>
       <c r="C49" s="1">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D49" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49" s="1">
+        <v>7</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1</v>
+      </c>
+      <c r="J49" s="1">
         <v>3</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1">
-        <v>0</v>
-      </c>
       <c r="K49" s="1">
         <v>0</v>
       </c>
@@ -7316,10 +7316,10 @@
         <v>0</v>
       </c>
       <c r="M49" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N49" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O49" s="1">
         <v>0</v>
@@ -7349,16 +7349,16 @@
         <v>0</v>
       </c>
       <c r="X49" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z49" s="1">
         <v>0</v>
       </c>
       <c r="AA49" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB49" s="1">
         <v>0</v>
@@ -7415,22 +7415,22 @@
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B50" s="1">
-        <v>1072</v>
+        <v>1412</v>
       </c>
       <c r="C50" s="1">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D50" s="1">
         <v>13</v>
       </c>
       <c r="E50" s="1">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F50" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
@@ -7451,40 +7451,40 @@
         <v>0</v>
       </c>
       <c r="M50" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N50" s="1">
+        <v>3</v>
+      </c>
+      <c r="O50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="1">
         <v>1</v>
       </c>
-      <c r="O50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="1">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1">
-        <v>0</v>
-      </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
-      <c r="T50" s="1">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1">
-        <v>0</v>
-      </c>
       <c r="V50" s="1">
         <v>0</v>
       </c>
       <c r="W50" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
@@ -7550,43 +7550,43 @@
     </row>
     <row r="51" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="B51" s="1">
-        <v>1072</v>
+        <v>1389</v>
       </c>
       <c r="C51" s="1">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D51" s="1">
         <v>13</v>
       </c>
       <c r="E51" s="1">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H51" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I51" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J51" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
         <v>0</v>
       </c>
       <c r="L51" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N51" s="1">
         <v>1</v>
@@ -7613,25 +7613,25 @@
         <v>0</v>
       </c>
       <c r="V51" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W51" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X51" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z51" s="1">
         <v>0</v>
       </c>
       <c r="AA51" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC51" s="1">
         <v>0</v>
@@ -7685,22 +7685,22 @@
     </row>
     <row r="52" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B52" s="1">
-        <v>1064</v>
+        <v>1387</v>
       </c>
       <c r="C52" s="1">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D52" s="1">
         <v>13</v>
       </c>
       <c r="E52" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
@@ -7712,22 +7712,22 @@
         <v>0</v>
       </c>
       <c r="J52" s="1">
+        <v>5</v>
+      </c>
+      <c r="K52" s="1">
+        <v>2</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
         <v>3</v>
       </c>
-      <c r="K52" s="1">
+      <c r="N52" s="1">
         <v>1</v>
       </c>
-      <c r="L52" s="1">
-        <v>0</v>
-      </c>
-      <c r="M52" s="1">
-        <v>0</v>
-      </c>
-      <c r="N52" s="1">
-        <v>2</v>
-      </c>
       <c r="O52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" s="1">
         <v>0</v>
@@ -7736,34 +7736,34 @@
         <v>0</v>
       </c>
       <c r="R52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T52" s="1">
         <v>0</v>
       </c>
       <c r="U52" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V52" s="1">
         <v>1</v>
       </c>
       <c r="W52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB52" s="1">
         <v>0</v>
@@ -7820,34 +7820,34 @@
     </row>
     <row r="53" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="B53" s="1">
-        <v>1050</v>
+        <v>1338</v>
       </c>
       <c r="C53" s="1">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D53" s="1">
+        <v>13</v>
+      </c>
+      <c r="E53" s="1">
+        <v>22</v>
+      </c>
+      <c r="F53" s="1">
         <v>4</v>
       </c>
-      <c r="E53" s="1">
-        <v>0</v>
-      </c>
-      <c r="F53" s="1">
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
         <v>3</v>
       </c>
-      <c r="G53" s="1">
-        <v>0</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
       <c r="I53" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J53" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
@@ -7856,7 +7856,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N53" s="1">
         <v>1</v>
@@ -7874,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="S53" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T53" s="1">
         <v>0</v>
@@ -7886,22 +7886,22 @@
         <v>0</v>
       </c>
       <c r="W53" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X53" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y53" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z53" s="1">
         <v>0</v>
       </c>
       <c r="AA53" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC53" s="1">
         <v>0</v>
@@ -7955,79 +7955,79 @@
     </row>
     <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="B54" s="1">
-        <v>1031</v>
+        <v>1330</v>
       </c>
       <c r="C54" s="1">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D54" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E54" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1">
+        <v>37</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1">
+        <v>2</v>
+      </c>
+      <c r="K54" s="1">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>2</v>
+      </c>
+      <c r="O54" s="1">
+        <v>2</v>
+      </c>
+      <c r="P54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+      <c r="S54" s="1">
+        <v>6</v>
+      </c>
+      <c r="T54" s="1">
+        <v>0</v>
+      </c>
+      <c r="U54" s="1">
+        <v>0</v>
+      </c>
+      <c r="V54" s="1">
+        <v>0</v>
+      </c>
+      <c r="W54" s="1">
+        <v>0</v>
+      </c>
+      <c r="X54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="1">
         <v>1</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-      <c r="I54" s="1">
-        <v>5</v>
-      </c>
-      <c r="J54" s="1">
-        <v>0</v>
-      </c>
-      <c r="K54" s="1">
-        <v>0</v>
-      </c>
-      <c r="L54" s="1">
-        <v>0</v>
-      </c>
-      <c r="M54" s="1">
-        <v>7</v>
-      </c>
-      <c r="N54" s="1">
-        <v>0</v>
-      </c>
-      <c r="O54" s="1">
-        <v>0</v>
-      </c>
-      <c r="P54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="1">
-        <v>0</v>
-      </c>
-      <c r="R54" s="1">
-        <v>0</v>
-      </c>
-      <c r="S54" s="1">
-        <v>11</v>
-      </c>
-      <c r="T54" s="1">
-        <v>0</v>
-      </c>
-      <c r="U54" s="1">
-        <v>0</v>
-      </c>
-      <c r="V54" s="1">
-        <v>0</v>
-      </c>
-      <c r="W54" s="1">
-        <v>0</v>
-      </c>
-      <c r="X54" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y54" s="1">
-        <v>0</v>
       </c>
       <c r="Z54" s="1">
         <v>0</v>
@@ -8090,88 +8090,88 @@
     </row>
     <row r="55" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B55" s="1">
-        <v>1023</v>
+        <v>1316</v>
       </c>
       <c r="C55" s="1">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="D55" s="1">
         <v>13</v>
       </c>
       <c r="E55" s="1">
+        <v>49</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1">
+        <v>3</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0</v>
+      </c>
+      <c r="L55" s="1">
+        <v>3</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1">
+        <v>0</v>
+      </c>
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="1">
+        <v>0</v>
+      </c>
+      <c r="T55" s="1">
+        <v>0</v>
+      </c>
+      <c r="U55" s="1">
+        <v>0</v>
+      </c>
+      <c r="V55" s="1">
+        <v>2</v>
+      </c>
+      <c r="W55" s="1">
         <v>4</v>
       </c>
-      <c r="F55" s="1">
+      <c r="X55" s="1">
+        <v>7</v>
+      </c>
+      <c r="Y55" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="1">
         <v>2</v>
       </c>
-      <c r="G55" s="1">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-      <c r="I55" s="1">
-        <v>8</v>
-      </c>
-      <c r="J55" s="1">
-        <v>0</v>
-      </c>
-      <c r="K55" s="1">
-        <v>0</v>
-      </c>
-      <c r="L55" s="1">
-        <v>0</v>
-      </c>
-      <c r="M55" s="1">
-        <v>15</v>
-      </c>
-      <c r="N55" s="1">
-        <v>0</v>
-      </c>
-      <c r="O55" s="1">
-        <v>0</v>
-      </c>
-      <c r="P55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>0</v>
-      </c>
-      <c r="R55" s="1">
-        <v>0</v>
-      </c>
-      <c r="S55" s="1">
-        <v>0</v>
-      </c>
-      <c r="T55" s="1">
-        <v>0</v>
-      </c>
-      <c r="U55" s="1">
-        <v>0</v>
-      </c>
-      <c r="V55" s="1">
-        <v>0</v>
-      </c>
-      <c r="W55" s="1">
-        <v>0</v>
-      </c>
-      <c r="X55" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="1">
-        <v>1</v>
-      </c>
       <c r="AB55" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC55" s="1">
         <v>0</v>
@@ -8225,43 +8225,43 @@
     </row>
     <row r="56" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="B56" s="1">
-        <v>1015</v>
+        <v>1291</v>
       </c>
       <c r="C56" s="1">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D56" s="1">
         <v>13</v>
       </c>
       <c r="E56" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" s="1">
+        <v>4</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>24</v>
+      </c>
+      <c r="J56" s="1">
         <v>6</v>
       </c>
-      <c r="G56" s="1">
-        <v>7</v>
-      </c>
-      <c r="H56" s="1">
-        <v>7</v>
-      </c>
-      <c r="I56" s="1">
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1">
         <v>2</v>
       </c>
-      <c r="J56" s="1">
-        <v>0</v>
-      </c>
-      <c r="K56" s="1">
-        <v>0</v>
-      </c>
-      <c r="L56" s="1">
-        <v>5</v>
-      </c>
       <c r="M56" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N56" s="1">
         <v>1</v>
@@ -8288,25 +8288,25 @@
         <v>0</v>
       </c>
       <c r="V56" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W56" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z56" s="1">
         <v>0</v>
       </c>
       <c r="AA56" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC56" s="1">
         <v>0</v>
@@ -8360,47 +8360,47 @@
     </row>
     <row r="57" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B57" s="1">
-        <v>1012</v>
+        <v>1210</v>
       </c>
       <c r="C57" s="1">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="D57" s="1">
         <v>13</v>
       </c>
       <c r="E57" s="1">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1">
+        <v>13</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
         <v>1</v>
       </c>
-      <c r="G57" s="1">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1">
-        <v>0</v>
-      </c>
-      <c r="I57" s="1">
-        <v>0</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
       <c r="K57" s="1">
         <v>0</v>
       </c>
       <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
         <v>3</v>
       </c>
-      <c r="M57" s="1">
-        <v>4</v>
-      </c>
-      <c r="N57" s="1">
-        <v>0</v>
-      </c>
       <c r="O57" s="1">
         <v>0</v>
       </c>
@@ -8423,16 +8423,16 @@
         <v>0</v>
       </c>
       <c r="V57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X57" s="1">
         <v>0</v>
       </c>
       <c r="Y57" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z57" s="1">
         <v>0</v>
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="AB57" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC57" s="1">
         <v>0</v>
@@ -8495,22 +8495,22 @@
     </row>
     <row r="58" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="B58" s="1">
-        <v>977</v>
+        <v>1199</v>
       </c>
       <c r="C58" s="1">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D58" s="1">
         <v>13</v>
       </c>
       <c r="E58" s="1">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F58" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
@@ -8519,22 +8519,22 @@
         <v>0</v>
       </c>
       <c r="I58" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J58" s="1">
         <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="1">
         <v>0</v>
       </c>
       <c r="M58" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N58" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O58" s="1">
         <v>0</v>
@@ -8549,13 +8549,13 @@
         <v>0</v>
       </c>
       <c r="S58" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T58" s="1">
         <v>0</v>
       </c>
       <c r="U58" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V58" s="1">
         <v>0</v>
@@ -8564,13 +8564,13 @@
         <v>0</v>
       </c>
       <c r="X58" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y58" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="1">
         <v>0</v>
@@ -8630,22 +8630,22 @@
     </row>
     <row r="59" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B59" s="1">
+        <v>1188</v>
+      </c>
+      <c r="C59" s="1">
         <v>37</v>
-      </c>
-      <c r="B59" s="1">
-        <v>976</v>
-      </c>
-      <c r="C59" s="1">
-        <v>67</v>
       </c>
       <c r="D59" s="1">
         <v>13</v>
       </c>
       <c r="E59" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F59" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
@@ -8654,16 +8654,16 @@
         <v>0</v>
       </c>
       <c r="I59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
       </c>
       <c r="L59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="1">
         <v>0</v>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T59" s="1">
         <v>0</v>
@@ -8693,25 +8693,25 @@
         <v>0</v>
       </c>
       <c r="V59" s="1">
+        <v>0</v>
+      </c>
+      <c r="W59" s="1">
         <v>2</v>
       </c>
-      <c r="W59" s="1">
-        <v>4</v>
-      </c>
       <c r="X59" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="1">
         <v>3</v>
       </c>
-      <c r="Y59" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z59" s="1">
-        <v>0</v>
-      </c>
       <c r="AA59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC59" s="1">
         <v>0</v>
@@ -8765,46 +8765,46 @@
     </row>
     <row r="60" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="B60" s="1">
-        <v>976</v>
+        <v>1180</v>
       </c>
       <c r="C60" s="1">
+        <v>81</v>
+      </c>
+      <c r="D60" s="1">
+        <v>13</v>
+      </c>
+      <c r="E60" s="1">
         <v>60</v>
       </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1">
-        <v>48</v>
-      </c>
       <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
         <v>5</v>
       </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="1">
-        <v>0</v>
-      </c>
-      <c r="J60" s="1">
-        <v>0</v>
-      </c>
       <c r="K60" s="1">
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M60" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N60" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O60" s="1">
         <v>0</v>
@@ -8900,85 +8900,85 @@
     </row>
     <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="B61" s="1">
-        <v>967</v>
+        <v>1136</v>
       </c>
       <c r="C61" s="1">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D61" s="1">
         <v>13</v>
       </c>
       <c r="E61" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>20</v>
+      </c>
+      <c r="N61" s="1">
+        <v>0</v>
+      </c>
+      <c r="O61" s="1">
+        <v>0</v>
+      </c>
+      <c r="P61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>0</v>
+      </c>
+      <c r="R61" s="1">
+        <v>0</v>
+      </c>
+      <c r="S61" s="1">
+        <v>0</v>
+      </c>
+      <c r="T61" s="1">
+        <v>0</v>
+      </c>
+      <c r="U61" s="1">
+        <v>0</v>
+      </c>
+      <c r="V61" s="1">
+        <v>0</v>
+      </c>
+      <c r="W61" s="1">
+        <v>0</v>
+      </c>
+      <c r="X61" s="1">
         <v>4</v>
       </c>
-      <c r="G61" s="1">
-        <v>1</v>
-      </c>
-      <c r="H61" s="1">
-        <v>4</v>
-      </c>
-      <c r="I61" s="1">
-        <v>3</v>
-      </c>
-      <c r="J61" s="1">
-        <v>3</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
-      </c>
-      <c r="L61" s="1">
-        <v>0</v>
-      </c>
-      <c r="M61" s="1">
-        <v>1</v>
-      </c>
-      <c r="N61" s="1">
-        <v>0</v>
-      </c>
-      <c r="O61" s="1">
-        <v>0</v>
-      </c>
-      <c r="P61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>0</v>
-      </c>
-      <c r="R61" s="1">
-        <v>0</v>
-      </c>
-      <c r="S61" s="1">
-        <v>0</v>
-      </c>
-      <c r="T61" s="1">
-        <v>0</v>
-      </c>
-      <c r="U61" s="1">
-        <v>0</v>
-      </c>
-      <c r="V61" s="1">
-        <v>0</v>
-      </c>
-      <c r="W61" s="1">
-        <v>1</v>
-      </c>
-      <c r="X61" s="1">
-        <v>7</v>
-      </c>
       <c r="Y61" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z61" s="1">
         <v>0</v>
       </c>
       <c r="AA61" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB61" s="1">
         <v>0</v>
@@ -9035,43 +9035,43 @@
     </row>
     <row r="62" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="B62" s="1">
-        <v>944</v>
+        <v>1110</v>
       </c>
       <c r="C62" s="1">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D62" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E62" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F62" s="1">
+        <v>6</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1</v>
+      </c>
+      <c r="J62" s="1">
         <v>3</v>
       </c>
-      <c r="G62" s="1">
-        <v>0</v>
-      </c>
-      <c r="H62" s="1">
-        <v>0</v>
-      </c>
-      <c r="I62" s="1">
-        <v>13</v>
-      </c>
-      <c r="J62" s="1">
-        <v>6</v>
-      </c>
       <c r="K62" s="1">
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="1">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N62" s="1">
         <v>1</v>
@@ -9089,7 +9089,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T62" s="1">
         <v>0</v>
@@ -9104,7 +9104,7 @@
         <v>0</v>
       </c>
       <c r="X62" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y62" s="1">
         <v>0</v>
@@ -9170,23 +9170,23 @@
     </row>
     <row r="63" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="B63" s="1">
-        <v>937</v>
+        <v>1106</v>
       </c>
       <c r="C63" s="1">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D63" s="1">
         <v>13</v>
       </c>
       <c r="E63" s="1">
+        <v>13</v>
+      </c>
+      <c r="F63" s="1">
         <v>8</v>
       </c>
-      <c r="F63" s="1">
-        <v>4</v>
-      </c>
       <c r="G63" s="1">
         <v>0</v>
       </c>
@@ -9194,61 +9194,61 @@
         <v>0</v>
       </c>
       <c r="I63" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J63" s="1">
+        <v>1</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>2</v>
+      </c>
+      <c r="N63" s="1">
+        <v>3</v>
+      </c>
+      <c r="O63" s="1">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="1">
+        <v>11</v>
+      </c>
+      <c r="T63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="1">
         <v>5</v>
       </c>
-      <c r="K63" s="1">
-        <v>0</v>
-      </c>
-      <c r="L63" s="1">
-        <v>0</v>
-      </c>
-      <c r="M63" s="1">
+      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="W63" s="1">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y63" s="1">
         <v>1</v>
       </c>
-      <c r="N63" s="1">
-        <v>1</v>
-      </c>
-      <c r="O63" s="1">
-        <v>0</v>
-      </c>
-      <c r="P63" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="1">
-        <v>0</v>
-      </c>
-      <c r="R63" s="1">
-        <v>1</v>
-      </c>
-      <c r="S63" s="1">
-        <v>6</v>
-      </c>
-      <c r="T63" s="1">
-        <v>0</v>
-      </c>
-      <c r="U63" s="1">
-        <v>0</v>
-      </c>
-      <c r="V63" s="1">
-        <v>1</v>
-      </c>
-      <c r="W63" s="1">
-        <v>1</v>
-      </c>
-      <c r="X63" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y63" s="1">
-        <v>0</v>
-      </c>
       <c r="Z63" s="1">
         <v>0</v>
       </c>
       <c r="AA63" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB63" s="1">
         <v>0</v>
@@ -9305,22 +9305,22 @@
     </row>
     <row r="64" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B64" s="1">
-        <v>860</v>
+        <v>1094</v>
       </c>
       <c r="C64" s="1">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D64" s="1">
         <v>13</v>
       </c>
       <c r="E64" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -9329,13 +9329,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J64" s="1">
         <v>1</v>
       </c>
       <c r="K64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -9344,10 +9344,10 @@
         <v>0</v>
       </c>
       <c r="N64" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P64" s="1">
         <v>0</v>
@@ -9377,10 +9377,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA64" s="1">
         <v>0</v>
@@ -9440,34 +9440,34 @@
     </row>
     <row r="65" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B65" s="1">
-        <v>851</v>
+        <v>1075</v>
       </c>
       <c r="C65" s="1">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D65" s="1">
         <v>13</v>
       </c>
       <c r="E65" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I65" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J65" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
@@ -9476,7 +9476,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N65" s="1">
         <v>0</v>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T65" s="1">
         <v>0</v>
@@ -9506,10 +9506,10 @@
         <v>0</v>
       </c>
       <c r="W65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X65" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y65" s="1">
         <v>3</v>
@@ -9518,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="AA65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB65" s="1">
         <v>0</v>
@@ -9575,85 +9575,85 @@
     </row>
     <row r="66" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="B66" s="1">
-        <v>850</v>
+        <v>1073</v>
       </c>
       <c r="C66" s="1">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D66" s="1">
         <v>13</v>
       </c>
       <c r="E66" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1">
         <v>8</v>
       </c>
-      <c r="G66" s="1">
-        <v>0</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0</v>
-      </c>
-      <c r="I66" s="1">
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1">
+        <v>15</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="O66" s="1">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>0</v>
+      </c>
+      <c r="R66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
+      </c>
+      <c r="T66" s="1">
+        <v>0</v>
+      </c>
+      <c r="U66" s="1">
+        <v>5</v>
+      </c>
+      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" s="1">
+        <v>0</v>
+      </c>
+      <c r="X66" s="1">
         <v>3</v>
       </c>
-      <c r="J66" s="1">
-        <v>8</v>
-      </c>
-      <c r="K66" s="1">
+      <c r="Y66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="1">
         <v>1</v>
-      </c>
-      <c r="L66" s="1">
-        <v>0</v>
-      </c>
-      <c r="M66" s="1">
-        <v>0</v>
-      </c>
-      <c r="N66" s="1">
-        <v>2</v>
-      </c>
-      <c r="O66" s="1">
-        <v>0</v>
-      </c>
-      <c r="P66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>0</v>
-      </c>
-      <c r="R66" s="1">
-        <v>0</v>
-      </c>
-      <c r="S66" s="1">
-        <v>0</v>
-      </c>
-      <c r="T66" s="1">
-        <v>0</v>
-      </c>
-      <c r="U66" s="1">
-        <v>0</v>
-      </c>
-      <c r="V66" s="1">
-        <v>0</v>
-      </c>
-      <c r="W66" s="1">
-        <v>0</v>
-      </c>
-      <c r="X66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="1">
-        <v>0</v>
       </c>
       <c r="AB66" s="1">
         <v>0</v>
@@ -9710,28 +9710,28 @@
     </row>
     <row r="67" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="B67" s="1">
-        <v>850</v>
+        <v>1032</v>
       </c>
       <c r="C67" s="1">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D67" s="1">
         <v>13</v>
       </c>
       <c r="E67" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F67" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -9749,10 +9749,10 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O67" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P67" s="1">
         <v>0</v>
@@ -9764,13 +9764,13 @@
         <v>0</v>
       </c>
       <c r="S67" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T67" s="1">
         <v>0</v>
       </c>
       <c r="U67" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V67" s="1">
         <v>0</v>
@@ -9779,10 +9779,10 @@
         <v>0</v>
       </c>
       <c r="X67" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y67" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z67" s="1">
         <v>0</v>
@@ -9845,22 +9845,22 @@
     </row>
     <row r="68" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="B68" s="1">
-        <v>815</v>
+        <v>1011</v>
       </c>
       <c r="C68" s="1">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D68" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F68" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -9878,13 +9878,13 @@
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M68" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N68" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O68" s="1">
         <v>0</v>
@@ -9980,76 +9980,76 @@
     </row>
     <row r="69" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="B69" s="1">
-        <v>790</v>
+        <v>991</v>
       </c>
       <c r="C69" s="1">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="D69" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E69" s="1">
+        <v>12</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>22</v>
+      </c>
+      <c r="I69" s="1">
+        <v>12</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1">
+        <v>4</v>
+      </c>
+      <c r="M69" s="1">
         <v>5</v>
       </c>
-      <c r="F69" s="1">
-        <v>12</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0</v>
-      </c>
-      <c r="H69" s="1">
-        <v>0</v>
-      </c>
-      <c r="I69" s="1">
-        <v>7</v>
-      </c>
-      <c r="J69" s="1">
+      <c r="N69" s="1">
+        <v>0</v>
+      </c>
+      <c r="O69" s="1">
+        <v>0</v>
+      </c>
+      <c r="P69" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>0</v>
+      </c>
+      <c r="R69" s="1">
+        <v>0</v>
+      </c>
+      <c r="S69" s="1">
+        <v>0</v>
+      </c>
+      <c r="T69" s="1">
+        <v>0</v>
+      </c>
+      <c r="U69" s="1">
+        <v>0</v>
+      </c>
+      <c r="V69" s="1">
+        <v>0</v>
+      </c>
+      <c r="W69" s="1">
+        <v>24</v>
+      </c>
+      <c r="X69" s="1">
         <v>1</v>
-      </c>
-      <c r="K69" s="1">
-        <v>0</v>
-      </c>
-      <c r="L69" s="1">
-        <v>0</v>
-      </c>
-      <c r="M69" s="1">
-        <v>0</v>
-      </c>
-      <c r="N69" s="1">
-        <v>3</v>
-      </c>
-      <c r="O69" s="1">
-        <v>0</v>
-      </c>
-      <c r="P69" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="1">
-        <v>0</v>
-      </c>
-      <c r="R69" s="1">
-        <v>0</v>
-      </c>
-      <c r="S69" s="1">
-        <v>0</v>
-      </c>
-      <c r="T69" s="1">
-        <v>0</v>
-      </c>
-      <c r="U69" s="1">
-        <v>0</v>
-      </c>
-      <c r="V69" s="1">
-        <v>0</v>
-      </c>
-      <c r="W69" s="1">
-        <v>0</v>
-      </c>
-      <c r="X69" s="1">
-        <v>0</v>
       </c>
       <c r="Y69" s="1">
         <v>0</v>
@@ -10115,37 +10115,37 @@
     </row>
     <row r="70" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="B70" s="1">
-        <v>754</v>
+        <v>920</v>
       </c>
       <c r="C70" s="1">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D70" s="1">
         <v>13</v>
       </c>
       <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1">
         <v>19</v>
       </c>
-      <c r="F70" s="1">
-        <v>5</v>
-      </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="1">
         <v>0</v>
@@ -10154,10 +10154,10 @@
         <v>0</v>
       </c>
       <c r="N70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P70" s="1">
         <v>0</v>
@@ -10169,7 +10169,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T70" s="1">
         <v>0</v>
@@ -10187,10 +10187,10 @@
         <v>0</v>
       </c>
       <c r="Y70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA70" s="1">
         <v>0</v>
@@ -10250,22 +10250,22 @@
     </row>
     <row r="71" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B71" s="1">
-        <v>740</v>
+        <v>850</v>
       </c>
       <c r="C71" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D71" s="1">
         <v>13</v>
       </c>
       <c r="E71" s="1">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F71" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
@@ -10274,22 +10274,22 @@
         <v>0</v>
       </c>
       <c r="I71" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J71" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="1">
         <v>0</v>
       </c>
       <c r="M71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N71" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O71" s="1">
         <v>0</v>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T71" s="1">
         <v>0</v>
@@ -10316,10 +10316,10 @@
         <v>0</v>
       </c>
       <c r="W71" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X71" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y71" s="1">
         <v>0</v>
@@ -10385,76 +10385,76 @@
     </row>
     <row r="72" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B72" s="1">
-        <v>722</v>
+        <v>837</v>
       </c>
       <c r="C72" s="1">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1">
         <v>5</v>
       </c>
-      <c r="E72" s="1">
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
+        <v>1</v>
+      </c>
+      <c r="N72" s="1">
+        <v>0</v>
+      </c>
+      <c r="O72" s="1">
+        <v>2</v>
+      </c>
+      <c r="P72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1">
+        <v>0</v>
+      </c>
+      <c r="S72" s="1">
+        <v>6</v>
+      </c>
+      <c r="T72" s="1">
+        <v>0</v>
+      </c>
+      <c r="U72" s="1">
         <v>5</v>
       </c>
-      <c r="F72" s="1">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0</v>
-      </c>
-      <c r="H72" s="1">
-        <v>22</v>
-      </c>
-      <c r="I72" s="1">
-        <v>12</v>
-      </c>
-      <c r="J72" s="1">
-        <v>0</v>
-      </c>
-      <c r="K72" s="1">
-        <v>0</v>
-      </c>
-      <c r="L72" s="1">
-        <v>0</v>
-      </c>
-      <c r="M72" s="1">
-        <v>2</v>
-      </c>
-      <c r="N72" s="1">
-        <v>0</v>
-      </c>
-      <c r="O72" s="1">
-        <v>0</v>
-      </c>
-      <c r="P72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="1">
-        <v>0</v>
-      </c>
-      <c r="R72" s="1">
-        <v>0</v>
-      </c>
-      <c r="S72" s="1">
-        <v>0</v>
-      </c>
-      <c r="T72" s="1">
-        <v>0</v>
-      </c>
-      <c r="U72" s="1">
-        <v>0</v>
-      </c>
       <c r="V72" s="1">
         <v>0</v>
       </c>
       <c r="W72" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y72" s="1">
         <v>0</v>
@@ -10520,22 +10520,22 @@
     </row>
     <row r="73" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B73" s="1">
-        <v>674</v>
+        <v>830</v>
       </c>
       <c r="C73" s="1">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D73" s="1">
         <v>13</v>
       </c>
       <c r="E73" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F73" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
@@ -10544,7 +10544,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J73" s="1">
         <v>0</v>
@@ -10556,7 +10556,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N73" s="1">
         <v>0</v>
@@ -10574,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T73" s="1">
         <v>0</v>
@@ -10586,10 +10586,10 @@
         <v>0</v>
       </c>
       <c r="W73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X73" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y73" s="1">
         <v>0</v>
@@ -10601,7 +10601,7 @@
         <v>0</v>
       </c>
       <c r="AB73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC73" s="1">
         <v>0</v>
@@ -10655,22 +10655,22 @@
     </row>
     <row r="74" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B74" s="1">
-        <v>518</v>
+        <v>815</v>
       </c>
       <c r="C74" s="1">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D74" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E74" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F74" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
@@ -10691,10 +10691,10 @@
         <v>0</v>
       </c>
       <c r="M74" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N74" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O74" s="1">
         <v>0</v>
@@ -10709,7 +10709,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T74" s="1">
         <v>0</v>
@@ -10733,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="AA74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB74" s="1">
         <v>0</v>
@@ -10790,22 +10790,22 @@
     </row>
     <row r="75" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="B75" s="1">
-        <v>485</v>
+        <v>674</v>
       </c>
       <c r="C75" s="1">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D75" s="1">
         <v>13</v>
       </c>
       <c r="E75" s="1">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F75" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
@@ -10826,7 +10826,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N75" s="1">
         <v>0</v>
@@ -10859,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="X75" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y75" s="1">
         <v>0</v>
@@ -10871,7 +10871,7 @@
         <v>0</v>
       </c>
       <c r="AB75" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC75" s="1">
         <v>0</v>
@@ -10925,22 +10925,22 @@
     </row>
     <row r="76" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B76" s="1">
-        <v>433</v>
+        <v>639</v>
       </c>
       <c r="C76" s="1">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D76" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E76" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -10961,49 +10961,49 @@
         <v>0</v>
       </c>
       <c r="M76" s="1">
+        <v>9</v>
+      </c>
+      <c r="N76" s="1">
+        <v>0</v>
+      </c>
+      <c r="O76" s="1">
+        <v>0</v>
+      </c>
+      <c r="P76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>0</v>
+      </c>
+      <c r="R76" s="1">
+        <v>0</v>
+      </c>
+      <c r="S76" s="1">
+        <v>11</v>
+      </c>
+      <c r="T76" s="1">
+        <v>0</v>
+      </c>
+      <c r="U76" s="1">
+        <v>0</v>
+      </c>
+      <c r="V76" s="1">
+        <v>0</v>
+      </c>
+      <c r="W76" s="1">
+        <v>0</v>
+      </c>
+      <c r="X76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="1">
         <v>1</v>
-      </c>
-      <c r="N76" s="1">
-        <v>1</v>
-      </c>
-      <c r="O76" s="1">
-        <v>0</v>
-      </c>
-      <c r="P76" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="1">
-        <v>0</v>
-      </c>
-      <c r="R76" s="1">
-        <v>0</v>
-      </c>
-      <c r="S76" s="1">
-        <v>6</v>
-      </c>
-      <c r="T76" s="1">
-        <v>0</v>
-      </c>
-      <c r="U76" s="1">
-        <v>0</v>
-      </c>
-      <c r="V76" s="1">
-        <v>0</v>
-      </c>
-      <c r="W76" s="1">
-        <v>0</v>
-      </c>
-      <c r="X76" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="1">
-        <v>0</v>
       </c>
       <c r="AB76" s="1">
         <v>0</v>
@@ -11060,22 +11060,22 @@
     </row>
     <row r="77" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="B77" s="1">
-        <v>410</v>
+        <v>592</v>
       </c>
       <c r="C77" s="1">
+        <v>40</v>
+      </c>
+      <c r="D77" s="1">
+        <v>13</v>
+      </c>
+      <c r="E77" s="1">
         <v>21</v>
       </c>
-      <c r="D77" s="1">
-        <v>5</v>
-      </c>
-      <c r="E77" s="1">
-        <v>0</v>
-      </c>
       <c r="F77" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
@@ -11096,13 +11096,13 @@
         <v>0</v>
       </c>
       <c r="M77" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N77" s="1">
         <v>0</v>
       </c>
       <c r="O77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P77" s="1">
         <v>0</v>
@@ -11114,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T77" s="1">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="AA77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB77" s="1">
         <v>0</v>
@@ -11198,10 +11198,10 @@
         <v>102</v>
       </c>
       <c r="B78" s="1">
-        <v>360</v>
+        <v>440</v>
       </c>
       <c r="C78" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D78" s="1">
         <v>4</v>
@@ -11210,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
@@ -11330,62 +11330,62 @@
     </row>
     <row r="79" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="B79" s="1">
-        <v>332</v>
+        <v>410</v>
       </c>
       <c r="C79" s="1">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D79" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="1">
+        <v>8</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>0</v>
+      </c>
+      <c r="O79" s="1">
         <v>1</v>
       </c>
-      <c r="F79" s="1">
+      <c r="P79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>0</v>
+      </c>
+      <c r="R79" s="1">
+        <v>0</v>
+      </c>
+      <c r="S79" s="1">
         <v>6</v>
       </c>
-      <c r="G79" s="1">
-        <v>0</v>
-      </c>
-      <c r="H79" s="1">
-        <v>0</v>
-      </c>
-      <c r="I79" s="1">
-        <v>0</v>
-      </c>
-      <c r="J79" s="1">
-        <v>5</v>
-      </c>
-      <c r="K79" s="1">
-        <v>0</v>
-      </c>
-      <c r="L79" s="1">
-        <v>0</v>
-      </c>
-      <c r="M79" s="1">
-        <v>0</v>
-      </c>
-      <c r="N79" s="1">
-        <v>0</v>
-      </c>
-      <c r="O79" s="1">
-        <v>0</v>
-      </c>
-      <c r="P79" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="1">
-        <v>0</v>
-      </c>
-      <c r="R79" s="1">
-        <v>0</v>
-      </c>
-      <c r="S79" s="1">
-        <v>0</v>
-      </c>
       <c r="T79" s="1">
         <v>0</v>
       </c>
@@ -11408,7 +11408,7 @@
         <v>0</v>
       </c>
       <c r="AA79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB79" s="1">
         <v>0</v>
@@ -11468,10 +11468,10 @@
         <v>107</v>
       </c>
       <c r="B80" s="1">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C80" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D80" s="1">
         <v>13</v>
@@ -11525,7 +11525,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V80" s="1">
         <v>0</v>
@@ -11600,31 +11600,31 @@
     </row>
     <row r="81" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="B81" s="1">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="C81" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D81" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
         <v>3</v>
       </c>
-      <c r="F81" s="1">
-        <v>2</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0</v>
-      </c>
-      <c r="H81" s="1">
-        <v>0</v>
-      </c>
       <c r="I81" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J81" s="1">
         <v>0</v>
@@ -11636,7 +11636,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="1">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" s="1">
         <v>0</v>
@@ -11666,10 +11666,10 @@
         <v>0</v>
       </c>
       <c r="W81" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y81" s="1">
         <v>0</v>
@@ -11735,22 +11735,22 @@
     </row>
     <row r="82" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B82" s="1">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="C82" s="1">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D82" s="1">
         <v>13</v>
       </c>
       <c r="E82" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F82" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -11870,7 +11870,7 @@
     </row>
     <row r="83" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="B83" s="1">
         <v>130</v>
@@ -12005,16 +12005,16 @@
     </row>
     <row r="84" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="B84" s="1">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="C84" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D84" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -12059,7 +12059,7 @@
         <v>0</v>
       </c>
       <c r="S84" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T84" s="1">
         <v>0</v>
@@ -12140,19 +12140,19 @@
     </row>
     <row r="85" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B85" s="1">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C85" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -12194,7 +12194,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T85" s="1">
         <v>0</v>
@@ -12275,22 +12275,22 @@
     </row>
     <row r="86" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B86" s="1">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C86" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F86" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="1">
         <v>0</v>
@@ -12410,10 +12410,10 @@
     </row>
     <row r="87" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B87" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C87" s="1">
         <v>1</v>
@@ -12422,10 +12422,10 @@
         <v>0</v>
       </c>
       <c r="E87" s="1">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1">
         <v>1</v>
-      </c>
-      <c r="F87" s="1">
-        <v>0</v>
       </c>
       <c r="G87" s="1">
         <v>0</v>
@@ -12545,19 +12545,19 @@
     </row>
     <row r="88" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="B88" s="1">
         <v>12</v>
       </c>
       <c r="C88" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -12611,7 +12611,7 @@
         <v>0</v>
       </c>
       <c r="W88" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X88" s="1">
         <v>0</v>

--- a/Results1.xlsx
+++ b/Results1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raouf\Desktop\Clan_Chest\Chest_Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA9B3FE-E7E8-4639-842F-159E7DAFB1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2595D613-6607-45C3-B47C-23A571386B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8B40F6D1-9A99-4C4C-A584-B5A2D365FA79}"/>
   </bookViews>
@@ -938,19 +938,19 @@
         <v>82</v>
       </c>
       <c r="B2" s="1">
-        <v>4537</v>
+        <v>5306</v>
       </c>
       <c r="C2" s="1">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="D2" s="1">
         <v>13</v>
       </c>
       <c r="E2" s="1">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F2" s="1">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -971,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N2" s="1">
         <v>4</v>
@@ -1022,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="AD2" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE2" s="1">
         <v>0</v>
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -1070,22 +1070,22 @@
     </row>
     <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="B3" s="1">
-        <v>3775</v>
+        <v>3914</v>
       </c>
       <c r="C3" s="1">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="D3" s="1">
         <v>13</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1094,19 +1094,19 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K3" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M3" s="1">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T3" s="1">
         <v>0</v>
@@ -1136,19 +1136,19 @@
         <v>0</v>
       </c>
       <c r="W3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y3" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z3" s="1">
         <v>1</v>
       </c>
       <c r="AA3" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AB3" s="1">
         <v>1</v>
@@ -1205,22 +1205,22 @@
     </row>
     <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="B4" s="1">
-        <v>3774</v>
+        <v>3775</v>
       </c>
       <c r="C4" s="1">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="D4" s="1">
         <v>13</v>
       </c>
       <c r="E4" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1229,19 +1229,19 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="1">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N4" s="1">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T4" s="1">
         <v>0</v>
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="W4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y4" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z4" s="1">
         <v>1</v>
       </c>
       <c r="AA4" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AB4" s="1">
         <v>1</v>
@@ -1475,22 +1475,22 @@
     </row>
     <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="B6" s="1">
-        <v>3326</v>
+        <v>3374</v>
       </c>
       <c r="C6" s="1">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="D6" s="1">
         <v>13</v>
       </c>
       <c r="E6" s="1">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1499,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -1511,10 +1511,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="N6" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
@@ -1541,13 +1541,13 @@
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X6" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y6" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z6" s="1">
         <v>0</v>
@@ -1610,31 +1610,31 @@
     </row>
     <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="B7" s="1">
-        <v>3178</v>
+        <v>3326</v>
       </c>
       <c r="C7" s="1">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="D7" s="1">
         <v>13</v>
       </c>
       <c r="E7" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F7" s="1">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="1">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N7" s="1">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="S7" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T7" s="1">
         <v>0</v>
       </c>
       <c r="U7" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
@@ -1679,19 +1679,19 @@
         <v>0</v>
       </c>
       <c r="X7" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="1">
         <v>0</v>
       </c>
       <c r="AA7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB7" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="1">
         <v>0</v>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
@@ -1745,46 +1745,46 @@
     </row>
     <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1">
-        <v>3016</v>
+        <v>3228</v>
       </c>
       <c r="C8" s="1">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="D8" s="1">
         <v>13</v>
       </c>
       <c r="E8" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M8" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -1811,22 +1811,22 @@
         <v>0</v>
       </c>
       <c r="W8" s="1">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1">
         <v>3</v>
       </c>
-      <c r="X8" s="1">
-        <v>12</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>8</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>2</v>
-      </c>
       <c r="AB8" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC8" s="1">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
@@ -1880,46 +1880,46 @@
     </row>
     <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="B9" s="1">
-        <v>2800</v>
+        <v>3028</v>
       </c>
       <c r="C9" s="1">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1">
         <v>13</v>
       </c>
       <c r="E9" s="1">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J9" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V9" s="1">
         <v>0</v>
@@ -1949,16 +1949,16 @@
         <v>0</v>
       </c>
       <c r="X9" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z9" s="1">
         <v>0</v>
       </c>
       <c r="AA9" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="1">
         <v>0</v>
@@ -2015,22 +2015,22 @@
     </row>
     <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B10" s="1">
-        <v>2654</v>
+        <v>2978</v>
       </c>
       <c r="C10" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" s="1">
         <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2039,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J10" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -2051,10 +2051,10 @@
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="N10" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T10" s="1">
         <v>0</v>
@@ -2084,19 +2084,19 @@
         <v>0</v>
       </c>
       <c r="X10" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y10" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z10" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="1">
         <v>0</v>
       </c>
       <c r="AB10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="1">
         <v>0</v>
@@ -2150,34 +2150,34 @@
     </row>
     <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1">
-        <v>2618</v>
+        <v>2890</v>
       </c>
       <c r="C11" s="1">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D11" s="1">
         <v>13</v>
       </c>
       <c r="E11" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N11" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -2222,22 +2222,22 @@
         <v>0</v>
       </c>
       <c r="Y11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AD11" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE11" s="1">
         <v>0</v>
@@ -2246,10 +2246,10 @@
         <v>0</v>
       </c>
       <c r="AG11" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH11" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
@@ -2285,61 +2285,61 @@
     </row>
     <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B12" s="1">
-        <v>2568</v>
+        <v>2879</v>
       </c>
       <c r="C12" s="1">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="D12" s="1">
         <v>13</v>
       </c>
       <c r="E12" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>30</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>43</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
         <v>11</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>8</v>
-      </c>
-      <c r="J12" s="1">
-        <v>9</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>8</v>
-      </c>
-      <c r="N12" s="1">
-        <v>10</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>6</v>
       </c>
       <c r="T12" s="1">
         <v>0</v>
@@ -2354,19 +2354,19 @@
         <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
       </c>
       <c r="AB12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" s="1">
         <v>0</v>
@@ -2420,46 +2420,46 @@
     </row>
     <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="B13" s="1">
-        <v>2459</v>
+        <v>2836</v>
       </c>
       <c r="C13" s="1">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="D13" s="1">
         <v>13</v>
       </c>
       <c r="E13" s="1">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
+        <v>21</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>6</v>
+      </c>
+      <c r="M13" s="1">
         <v>26</v>
       </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>4</v>
-      </c>
       <c r="N13" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O13" s="1">
         <v>0</v>
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T13" s="1">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="X13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y13" s="1">
         <v>0</v>
@@ -2498,16 +2498,16 @@
         <v>0</v>
       </c>
       <c r="AA13" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AB13" s="1">
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="1">
         <v>0</v>
@@ -2516,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="AG13" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -2555,49 +2555,49 @@
     </row>
     <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="B14" s="1">
-        <v>2434</v>
+        <v>2768</v>
       </c>
       <c r="C14" s="1">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>15</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="1">
-        <v>26</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1">
         <v>2</v>
       </c>
       <c r="N14" s="1">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" s="1">
         <v>0</v>
@@ -2609,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T14" s="1">
         <v>0</v>
@@ -2618,28 +2618,28 @@
         <v>5</v>
       </c>
       <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1">
         <v>1</v>
       </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-      <c r="X14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>15</v>
-      </c>
       <c r="Z14" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" s="1">
         <v>0</v>
       </c>
       <c r="AC14" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD14" s="1">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
@@ -2690,23 +2690,23 @@
     </row>
     <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="B15" s="1">
-        <v>2360</v>
+        <v>2627</v>
       </c>
       <c r="C15" s="1">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="D15" s="1">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1">
         <v>13</v>
       </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
@@ -2714,22 +2714,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J15" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -2741,40 +2741,40 @@
         <v>0</v>
       </c>
       <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>11</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1">
+        <v>5</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="1">
         <v>3</v>
       </c>
-      <c r="S15" s="1">
-        <v>0</v>
-      </c>
-      <c r="T15" s="1">
-        <v>0</v>
-      </c>
-      <c r="U15" s="1">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
-        <v>0</v>
-      </c>
-      <c r="W15" s="1">
-        <v>0</v>
-      </c>
-      <c r="X15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>11</v>
-      </c>
       <c r="AA15" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB15" s="1">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AC15" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -2825,22 +2825,22 @@
     </row>
     <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B16" s="1">
-        <v>2294</v>
+        <v>2434</v>
       </c>
       <c r="C16" s="1">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D16" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -2849,26 +2849,26 @@
         <v>0</v>
       </c>
       <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
         <v>6</v>
       </c>
-      <c r="J16" s="1">
-        <v>9</v>
-      </c>
       <c r="K16" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" s="1">
         <v>1</v>
       </c>
       <c r="M16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" s="1">
+        <v>4</v>
+      </c>
+      <c r="O16" s="1">
         <v>2</v>
       </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
       <c r="P16" s="1">
         <v>0</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T16" s="1">
         <v>0</v>
@@ -2888,28 +2888,28 @@
         <v>5</v>
       </c>
       <c r="V16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
       </c>
       <c r="X16" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Z16" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD16" s="1">
         <v>0</v>
@@ -2960,91 +2960,91 @@
     </row>
     <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1">
-        <v>2290</v>
+        <v>2415</v>
       </c>
       <c r="C17" s="1">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D17" s="1">
+        <v>13</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>34</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>8</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>7</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>6</v>
+      </c>
+      <c r="T17" s="1">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1">
         <v>5</v>
       </c>
-      <c r="E17" s="1">
-        <v>25</v>
-      </c>
-      <c r="F17" s="1">
-        <v>6</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
+      <c r="V17" s="1">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1">
         <v>3</v>
-      </c>
-      <c r="J17" s="1">
-        <v>7</v>
-      </c>
-      <c r="K17" s="1">
-        <v>5</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>6</v>
-      </c>
-      <c r="N17" s="1">
-        <v>1</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="1">
-        <v>0</v>
-      </c>
-      <c r="U17" s="1">
-        <v>0</v>
-      </c>
-      <c r="V17" s="1">
-        <v>0</v>
-      </c>
-      <c r="W17" s="1">
-        <v>0</v>
-      </c>
-      <c r="X17" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>7</v>
-      </c>
-      <c r="Z17" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="1">
-        <v>0</v>
       </c>
       <c r="AD17" s="1">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         <v>111</v>
       </c>
       <c r="B18" s="1">
-        <v>2241</v>
+        <v>2403</v>
       </c>
       <c r="C18" s="1">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="D18" s="1">
         <v>13</v>
       </c>
       <c r="E18" s="1">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I18" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="1">
         <v>3</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M18" s="1">
         <v>5</v>
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="U18" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V18" s="1">
         <v>1</v>
@@ -3230,13 +3230,13 @@
     </row>
     <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="B19" s="1">
-        <v>2205</v>
+        <v>2360</v>
       </c>
       <c r="C19" s="1">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="D19" s="1">
         <v>13</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -3269,10 +3269,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="1">
         <v>0</v>
@@ -3281,10 +3281,10 @@
         <v>0</v>
       </c>
       <c r="R19" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S19" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T19" s="1">
         <v>0</v>
@@ -3302,19 +3302,19 @@
         <v>0</v>
       </c>
       <c r="Y19" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA19" s="1">
         <v>0</v>
       </c>
       <c r="AB19" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC19" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD19" s="1">
         <v>0</v>
@@ -3368,7 +3368,7 @@
         <v>98</v>
       </c>
       <c r="B20" s="1">
-        <v>2165</v>
+        <v>2345</v>
       </c>
       <c r="C20" s="1">
         <v>68</v>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE20" s="1">
         <v>0</v>
@@ -3461,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="AG20" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH20" s="1">
         <v>0</v>
@@ -3500,49 +3500,49 @@
     </row>
     <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1">
-        <v>2120</v>
+        <v>2334</v>
       </c>
       <c r="C21" s="1">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="D21" s="1">
         <v>13</v>
       </c>
       <c r="E21" s="1">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F21" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G21" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>7</v>
+      </c>
+      <c r="J21" s="1">
+        <v>9</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>4</v>
+      </c>
+      <c r="N21" s="1">
+        <v>10</v>
+      </c>
+      <c r="O21" s="1">
         <v>1</v>
-      </c>
-      <c r="I21" s="1">
-        <v>1</v>
-      </c>
-      <c r="J21" s="1">
-        <v>2</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>11</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
       </c>
       <c r="P21" s="1">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="U21" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X21" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="1">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="AA21" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="1">
         <v>0</v>
@@ -3635,83 +3635,83 @@
     </row>
     <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B22" s="1">
-        <v>2109</v>
+        <v>2332</v>
       </c>
       <c r="C22" s="1">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="D22" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E22" s="1">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>3</v>
+      </c>
+      <c r="J22" s="1">
+        <v>7</v>
+      </c>
+      <c r="K22" s="1">
+        <v>5</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>6</v>
+      </c>
+      <c r="N22" s="1">
         <v>1</v>
       </c>
-      <c r="I22" s="1">
-        <v>10</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1">
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
         <v>1</v>
       </c>
-      <c r="M22" s="1">
-        <v>20</v>
-      </c>
-      <c r="N22" s="1">
-        <v>0</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>0</v>
-      </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>11</v>
-      </c>
-      <c r="T22" s="1">
-        <v>0</v>
-      </c>
-      <c r="U22" s="1">
+      <c r="W22" s="1">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z22" s="1">
         <v>5</v>
       </c>
-      <c r="V22" s="1">
-        <v>0</v>
-      </c>
-      <c r="W22" s="1">
-        <v>18</v>
-      </c>
-      <c r="X22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="1">
-        <v>0</v>
-      </c>
       <c r="AA22" s="1">
         <v>0</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="1">
         <v>0</v>
@@ -3731,10 +3731,10 @@
         <v>0</v>
       </c>
       <c r="AG22" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH22" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
@@ -3770,68 +3770,68 @@
     </row>
     <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B23" s="1">
-        <v>2105</v>
+        <v>2242</v>
       </c>
       <c r="C23" s="1">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D23" s="1">
         <v>13</v>
       </c>
       <c r="E23" s="1">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F23" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I23" s="1">
+        <v>17</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>30</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
         <v>6</v>
       </c>
-      <c r="J23" s="1">
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
         <v>5</v>
       </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>11</v>
-      </c>
-      <c r="N23" s="1">
-        <v>2</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
-      <c r="S23" s="1">
-        <v>0</v>
-      </c>
-      <c r="T23" s="1">
-        <v>0</v>
-      </c>
-      <c r="U23" s="1">
-        <v>0</v>
-      </c>
       <c r="V23" s="1">
         <v>0</v>
       </c>
@@ -3839,10 +3839,10 @@
         <v>0</v>
       </c>
       <c r="X23" s="1">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Y23" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="1">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="AB23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="1">
         <v>0</v>
@@ -3908,10 +3908,10 @@
         <v>80</v>
       </c>
       <c r="B24" s="1">
-        <v>2080</v>
+        <v>2215</v>
       </c>
       <c r="C24" s="1">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D24" s="1">
         <v>13</v>
@@ -3920,7 +3920,7 @@
         <v>29</v>
       </c>
       <c r="F24" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G24" s="1">
         <v>5</v>
@@ -3938,10 +3938,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M24" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N24" s="1">
         <v>3</v>
@@ -4040,46 +4040,46 @@
     </row>
     <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B25" s="1">
-        <v>2054</v>
+        <v>2203</v>
       </c>
       <c r="C25" s="1">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="D25" s="1">
         <v>13</v>
       </c>
       <c r="E25" s="1">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I25" s="1">
+        <v>6</v>
+      </c>
+      <c r="J25" s="1">
+        <v>5</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
         <v>11</v>
       </c>
-      <c r="J25" s="1">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>42</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
       <c r="N25" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -4103,25 +4103,25 @@
         <v>5</v>
       </c>
       <c r="V25" s="1">
+        <v>0</v>
+      </c>
+      <c r="W25" s="1">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>8</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="1">
         <v>1</v>
-      </c>
-      <c r="W25" s="1">
-        <v>17</v>
-      </c>
-      <c r="X25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="1">
-        <v>0</v>
       </c>
       <c r="AC25" s="1">
         <v>0</v>
@@ -4175,62 +4175,62 @@
     </row>
     <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B26" s="1">
-        <v>2010</v>
+        <v>2184</v>
       </c>
       <c r="C26" s="1">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="D26" s="1">
         <v>13</v>
       </c>
       <c r="E26" s="1">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F26" s="1">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>11</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>0</v>
+      </c>
+      <c r="P26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+      <c r="S26" s="1">
         <v>6</v>
       </c>
-      <c r="J26" s="1">
-        <v>6</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1">
-        <v>3</v>
-      </c>
-      <c r="O26" s="1">
-        <v>0</v>
-      </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
-      <c r="R26" s="1">
-        <v>0</v>
-      </c>
-      <c r="S26" s="1">
-        <v>0</v>
-      </c>
       <c r="T26" s="1">
         <v>0</v>
       </c>
@@ -4238,25 +4238,25 @@
         <v>0</v>
       </c>
       <c r="V26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X26" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y26" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="1">
         <v>0</v>
       </c>
       <c r="AA26" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="1">
         <v>0</v>
@@ -4313,10 +4313,10 @@
         <v>40</v>
       </c>
       <c r="B27" s="1">
-        <v>2004</v>
+        <v>2154</v>
       </c>
       <c r="C27" s="1">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D27" s="1">
         <v>13</v>
@@ -4325,7 +4325,7 @@
         <v>17</v>
       </c>
       <c r="F27" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="1">
         <v>0</v>
@@ -4445,46 +4445,46 @@
     </row>
     <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1">
-        <v>1945</v>
+        <v>2145</v>
       </c>
       <c r="C28" s="1">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="D28" s="1">
         <v>13</v>
       </c>
       <c r="E28" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F28" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J28" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N28" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -4499,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T28" s="1">
         <v>0</v>
@@ -4511,16 +4511,16 @@
         <v>0</v>
       </c>
       <c r="W28" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X28" s="1">
         <v>0</v>
       </c>
       <c r="Y28" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="1">
         <v>0</v>
@@ -4541,10 +4541,10 @@
         <v>0</v>
       </c>
       <c r="AG28" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH28" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1">
-        <v>1913</v>
+        <v>2121</v>
       </c>
       <c r="C29" s="1">
+        <v>130</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1">
         <v>93</v>
       </c>
-      <c r="D29" s="1">
-        <v>13</v>
-      </c>
-      <c r="E29" s="1">
-        <v>29</v>
-      </c>
       <c r="F29" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -4604,22 +4604,22 @@
         <v>0</v>
       </c>
       <c r="I29" s="1">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M29" s="1">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N29" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O29" s="1">
         <v>0</v>
@@ -4715,46 +4715,46 @@
     </row>
     <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B30" s="1">
-        <v>1882</v>
+        <v>2113</v>
       </c>
       <c r="C30" s="1">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D30" s="1">
         <v>13</v>
       </c>
       <c r="E30" s="1">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="F30" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J30" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M30" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N30" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -4769,13 +4769,13 @@
         <v>0</v>
       </c>
       <c r="S30" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T30" s="1">
         <v>0</v>
       </c>
       <c r="U30" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
@@ -4784,16 +4784,16 @@
         <v>0</v>
       </c>
       <c r="X30" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y30" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z30" s="1">
         <v>0</v>
       </c>
       <c r="AA30" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="1">
         <v>0</v>
@@ -4850,22 +4850,22 @@
     </row>
     <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="B31" s="1">
-        <v>1852</v>
+        <v>2074</v>
       </c>
       <c r="C31" s="1">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="D31" s="1">
         <v>13</v>
       </c>
       <c r="E31" s="1">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="F31" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -4874,19 +4874,19 @@
         <v>0</v>
       </c>
       <c r="I31" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J31" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M31" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N31" s="1">
         <v>0</v>
@@ -4904,7 +4904,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T31" s="1">
         <v>0</v>
@@ -4913,16 +4913,16 @@
         <v>5</v>
       </c>
       <c r="V31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="X31" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="1">
         <v>0</v>
@@ -4949,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="AH31" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
@@ -4985,46 +4985,46 @@
     </row>
     <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1">
-        <v>1852</v>
+        <v>2061</v>
       </c>
       <c r="C32" s="1">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D32" s="1">
         <v>13</v>
       </c>
       <c r="E32" s="1">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" s="1">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J32" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M32" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N32" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T32" s="1">
         <v>0</v>
@@ -5048,19 +5048,19 @@
         <v>0</v>
       </c>
       <c r="V32" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W32" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="1">
         <v>0</v>
@@ -5120,22 +5120,22 @@
     </row>
     <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B33" s="1">
-        <v>1828</v>
+        <v>2031</v>
       </c>
       <c r="C33" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D33" s="1">
         <v>13</v>
       </c>
       <c r="E33" s="1">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -5144,25 +5144,25 @@
         <v>0</v>
       </c>
       <c r="I33" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J33" s="1">
         <v>6</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
       </c>
       <c r="M33" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N33" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="1">
         <v>0</v>
@@ -5174,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T33" s="1">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="W33" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X33" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y33" s="1">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="AC33" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD33" s="1">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="AH33" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
@@ -5255,46 +5255,46 @@
     </row>
     <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="B34" s="1">
-        <v>1800</v>
+        <v>2010</v>
       </c>
       <c r="C34" s="1">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="D34" s="1">
         <v>13</v>
       </c>
       <c r="E34" s="1">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I34" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J34" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M34" s="1">
         <v>0</v>
       </c>
       <c r="N34" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -5315,28 +5315,28 @@
         <v>0</v>
       </c>
       <c r="U34" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V34" s="1">
         <v>0</v>
       </c>
       <c r="W34" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X34" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z34" s="1">
         <v>0</v>
       </c>
       <c r="AA34" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AB34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC34" s="1">
         <v>0</v>
@@ -5390,43 +5390,43 @@
     </row>
     <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="B35" s="1">
-        <v>1771</v>
+        <v>2008</v>
       </c>
       <c r="C35" s="1">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D35" s="1">
         <v>13</v>
       </c>
       <c r="E35" s="1">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F35" s="1">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
         <v>9</v>
       </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-      <c r="I35" s="1">
-        <v>1</v>
-      </c>
-      <c r="J35" s="1">
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
         <v>6</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
-        <v>2</v>
       </c>
       <c r="N35" s="1">
         <v>0</v>
@@ -5456,14 +5456,14 @@
         <v>0</v>
       </c>
       <c r="W35" s="1">
+        <v>0</v>
+      </c>
+      <c r="X35" s="1">
+        <v>15</v>
+      </c>
+      <c r="Y35" s="1">
         <v>2</v>
       </c>
-      <c r="X35" s="1">
-        <v>19</v>
-      </c>
-      <c r="Y35" s="1">
-        <v>0</v>
-      </c>
       <c r="Z35" s="1">
         <v>0</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="AC35" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD35" s="1">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AH35" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
@@ -5525,40 +5525,40 @@
     </row>
     <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1">
-        <v>1702</v>
+        <v>1978</v>
       </c>
       <c r="C36" s="1">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D36" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F36" s="1">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J36" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1">
         <v>6</v>
@@ -5579,13 +5579,13 @@
         <v>0</v>
       </c>
       <c r="S36" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T36" s="1">
         <v>0</v>
       </c>
       <c r="U36" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
@@ -5594,19 +5594,19 @@
         <v>0</v>
       </c>
       <c r="X36" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Y36" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z36" s="1">
         <v>0</v>
       </c>
       <c r="AA36" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" s="1">
         <v>0</v>
@@ -5660,43 +5660,43 @@
     </row>
     <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="B37" s="1">
-        <v>1669</v>
+        <v>1972</v>
       </c>
       <c r="C37" s="1">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="D37" s="1">
         <v>13</v>
       </c>
       <c r="E37" s="1">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="F37" s="1">
+        <v>5</v>
+      </c>
+      <c r="G37" s="1">
         <v>1</v>
       </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J37" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M37" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N37" s="1">
         <v>0</v>
@@ -5714,28 +5714,28 @@
         <v>0</v>
       </c>
       <c r="S37" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T37" s="1">
         <v>0</v>
       </c>
       <c r="U37" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V37" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W37" s="1">
         <v>6</v>
       </c>
       <c r="X37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z37" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA37" s="1">
         <v>0</v>
@@ -5795,22 +5795,22 @@
     </row>
     <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="B38" s="1">
-        <v>1631</v>
+        <v>1945</v>
       </c>
       <c r="C38" s="1">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="D38" s="1">
         <v>13</v>
       </c>
       <c r="E38" s="1">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F38" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
@@ -5819,67 +5819,67 @@
         <v>0</v>
       </c>
       <c r="I38" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
+        <v>7</v>
+      </c>
+      <c r="K38" s="1">
+        <v>6</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
+        <v>4</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>6</v>
+      </c>
+      <c r="T38" s="1">
+        <v>0</v>
+      </c>
+      <c r="U38" s="1">
+        <v>5</v>
+      </c>
+      <c r="V38" s="1">
+        <v>0</v>
+      </c>
+      <c r="W38" s="1">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="1">
         <v>2</v>
       </c>
-      <c r="K38" s="1">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1">
-        <v>17</v>
-      </c>
-      <c r="M38" s="1">
+      <c r="Z38" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="1">
         <v>3</v>
-      </c>
-      <c r="N38" s="1">
-        <v>0</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>0</v>
-      </c>
-      <c r="R38" s="1">
-        <v>0</v>
-      </c>
-      <c r="S38" s="1">
-        <v>0</v>
-      </c>
-      <c r="T38" s="1">
-        <v>0</v>
-      </c>
-      <c r="U38" s="1">
-        <v>0</v>
-      </c>
-      <c r="V38" s="1">
-        <v>0</v>
-      </c>
-      <c r="W38" s="1">
-        <v>0</v>
-      </c>
-      <c r="X38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="1">
-        <v>0</v>
       </c>
       <c r="AD38" s="1">
         <v>0</v>
@@ -5930,22 +5930,22 @@
     </row>
     <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B39" s="1">
-        <v>1617</v>
+        <v>1926</v>
       </c>
       <c r="C39" s="1">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="D39" s="1">
         <v>13</v>
       </c>
       <c r="E39" s="1">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="F39" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -5954,10 +5954,10 @@
         <v>0</v>
       </c>
       <c r="I39" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -5966,10 +5966,10 @@
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -5990,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -5999,16 +5999,16 @@
         <v>0</v>
       </c>
       <c r="X39" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="1">
         <v>0</v>
       </c>
       <c r="AA39" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB39" s="1">
         <v>0</v>
@@ -6065,31 +6065,31 @@
     </row>
     <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="B40" s="1">
-        <v>1555</v>
+        <v>1860</v>
       </c>
       <c r="C40" s="1">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="D40" s="1">
         <v>13</v>
       </c>
       <c r="E40" s="1">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F40" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I40" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J40" s="1">
         <v>0</v>
@@ -6098,16 +6098,16 @@
         <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M40" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P40" s="1">
         <v>0</v>
@@ -6119,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T40" s="1">
         <v>0</v>
@@ -6131,10 +6131,10 @@
         <v>0</v>
       </c>
       <c r="W40" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X40" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y40" s="1">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AA40" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
@@ -6203,19 +6203,19 @@
         <v>117</v>
       </c>
       <c r="B41" s="1">
-        <v>1552</v>
+        <v>1842</v>
       </c>
       <c r="C41" s="1">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D41" s="1">
         <v>13</v>
       </c>
       <c r="E41" s="1">
+        <v>18</v>
+      </c>
+      <c r="F41" s="1">
         <v>15</v>
-      </c>
-      <c r="F41" s="1">
-        <v>12</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
@@ -6260,22 +6260,22 @@
         <v>0</v>
       </c>
       <c r="U41" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V41" s="1">
         <v>1</v>
       </c>
       <c r="W41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y41" s="1">
         <v>3</v>
       </c>
       <c r="Z41" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA41" s="1">
         <v>0</v>
@@ -6335,19 +6335,19 @@
     </row>
     <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1">
-        <v>1484</v>
+        <v>1785</v>
       </c>
       <c r="C42" s="1">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E42" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F42" s="1">
         <v>15</v>
@@ -6359,26 +6359,26 @@
         <v>0</v>
       </c>
       <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>3</v>
+      </c>
+      <c r="N42" s="1">
+        <v>9</v>
+      </c>
+      <c r="O42" s="1">
         <v>5</v>
       </c>
-      <c r="J42" s="1">
-        <v>4</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1">
-        <v>6</v>
-      </c>
-      <c r="N42" s="1">
-        <v>0</v>
-      </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
       <c r="P42" s="1">
         <v>0</v>
       </c>
@@ -6389,13 +6389,13 @@
         <v>0</v>
       </c>
       <c r="S42" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T42" s="1">
         <v>0</v>
       </c>
       <c r="U42" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V42" s="1">
         <v>0</v>
@@ -6404,19 +6404,19 @@
         <v>0</v>
       </c>
       <c r="X42" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="1">
         <v>0</v>
       </c>
       <c r="AA42" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC42" s="1">
         <v>0</v>
@@ -6470,22 +6470,22 @@
     </row>
     <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="B43" s="1">
-        <v>1476</v>
+        <v>1755</v>
       </c>
       <c r="C43" s="1">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D43" s="1">
         <v>13</v>
       </c>
       <c r="E43" s="1">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F43" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
@@ -6494,22 +6494,22 @@
         <v>0</v>
       </c>
       <c r="I43" s="1">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J43" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K43" s="1">
         <v>0</v>
       </c>
       <c r="L43" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M43" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="1">
         <v>0</v>
@@ -6524,13 +6524,13 @@
         <v>0</v>
       </c>
       <c r="S43" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T43" s="1">
         <v>0</v>
       </c>
       <c r="U43" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -6539,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="X43" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="1">
         <v>0</v>
@@ -6605,10 +6605,10 @@
     </row>
     <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="B44" s="1">
-        <v>1463</v>
+        <v>1741</v>
       </c>
       <c r="C44" s="1">
         <v>73</v>
@@ -6617,61 +6617,61 @@
         <v>13</v>
       </c>
       <c r="E44" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F44" s="1">
+        <v>10</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+      <c r="J44" s="1">
+        <v>5</v>
+      </c>
+      <c r="K44" s="1">
+        <v>3</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>3</v>
+      </c>
+      <c r="N44" s="1">
         <v>2</v>
       </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1">
+      <c r="O44" s="1">
+        <v>2</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
         <v>1</v>
       </c>
-      <c r="K44" s="1">
-        <v>0</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>23</v>
-      </c>
-      <c r="N44" s="1">
+      <c r="S44" s="1">
+        <v>6</v>
+      </c>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>5</v>
+      </c>
+      <c r="V44" s="1">
         <v>1</v>
       </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1">
-        <v>2</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
-      </c>
       <c r="W44" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X44" s="1">
         <v>1</v>
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="AA44" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AB44" s="1">
         <v>0</v>
@@ -6740,35 +6740,35 @@
     </row>
     <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="B45" s="1">
-        <v>1448</v>
+        <v>1693</v>
       </c>
       <c r="C45" s="1">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="D45" s="1">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1">
+        <v>19</v>
+      </c>
+      <c r="F45" s="1">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>4</v>
+      </c>
+      <c r="J45" s="1">
         <v>5</v>
       </c>
-      <c r="E45" s="1">
-        <v>9</v>
-      </c>
-      <c r="F45" s="1">
-        <v>10</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>8</v>
-      </c>
       <c r="K45" s="1">
         <v>0</v>
       </c>
@@ -6776,10 +6776,10 @@
         <v>0</v>
       </c>
       <c r="M45" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -6794,13 +6794,13 @@
         <v>0</v>
       </c>
       <c r="S45" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T45" s="1">
         <v>0</v>
       </c>
       <c r="U45" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V45" s="1">
         <v>0</v>
@@ -6809,19 +6809,19 @@
         <v>0</v>
       </c>
       <c r="X45" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y45" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z45" s="1">
         <v>0</v>
       </c>
       <c r="AA45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="1">
         <v>0</v>
@@ -6875,22 +6875,22 @@
     </row>
     <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="B46" s="1">
-        <v>1446</v>
+        <v>1679</v>
       </c>
       <c r="C46" s="1">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D46" s="1">
         <v>13</v>
       </c>
       <c r="E46" s="1">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="F46" s="1">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G46" s="1">
         <v>0</v>
@@ -6908,10 +6908,10 @@
         <v>0</v>
       </c>
       <c r="L46" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N46" s="1">
         <v>0</v>
@@ -6935,19 +6935,19 @@
         <v>0</v>
       </c>
       <c r="U46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X46" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="1">
         <v>0</v>
@@ -7010,34 +7010,34 @@
     </row>
     <row r="47" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B47" s="1">
-        <v>1438</v>
+        <v>1660</v>
       </c>
       <c r="C47" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D47" s="1">
         <v>13</v>
       </c>
       <c r="E47" s="1">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I47" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
@@ -7046,10 +7046,10 @@
         <v>0</v>
       </c>
       <c r="M47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N47" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47" s="1">
         <v>0</v>
@@ -7064,34 +7064,34 @@
         <v>0</v>
       </c>
       <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="1">
+        <v>0</v>
+      </c>
+      <c r="U47" s="1">
+        <v>0</v>
+      </c>
+      <c r="V47" s="1">
+        <v>0</v>
+      </c>
+      <c r="W47" s="1">
+        <v>5</v>
+      </c>
+      <c r="X47" s="1">
         <v>6</v>
       </c>
-      <c r="T47" s="1">
-        <v>0</v>
-      </c>
-      <c r="U47" s="1">
+      <c r="Y47" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="1">
         <v>3</v>
       </c>
-      <c r="V47" s="1">
-        <v>0</v>
-      </c>
-      <c r="W47" s="1">
-        <v>0</v>
-      </c>
-      <c r="X47" s="1">
+      <c r="AB47" s="1">
         <v>1</v>
-      </c>
-      <c r="Y47" s="1">
-        <v>18</v>
-      </c>
-      <c r="Z47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="1">
-        <v>0</v>
       </c>
       <c r="AC47" s="1">
         <v>0</v>
@@ -7145,22 +7145,22 @@
     </row>
     <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="B48" s="1">
-        <v>1422</v>
+        <v>1579</v>
       </c>
       <c r="C48" s="1">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D48" s="1">
         <v>13</v>
       </c>
       <c r="E48" s="1">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F48" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
@@ -7169,10 +7169,10 @@
         <v>0</v>
       </c>
       <c r="I48" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="1">
         <v>0</v>
@@ -7181,10 +7181,10 @@
         <v>0</v>
       </c>
       <c r="M48" s="1">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -7205,16 +7205,16 @@
         <v>0</v>
       </c>
       <c r="U48" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V48" s="1">
         <v>0</v>
       </c>
       <c r="W48" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X48" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y48" s="1">
         <v>0</v>
@@ -7223,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="AA48" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -7280,88 +7280,88 @@
     </row>
     <row r="49" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>1420</v>
+        <v>1501</v>
       </c>
       <c r="C49" s="1">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E49" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F49" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I49" s="1">
+        <v>4</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1">
+        <v>9</v>
+      </c>
+      <c r="M49" s="1">
+        <v>3</v>
+      </c>
+      <c r="N49" s="1">
         <v>1</v>
       </c>
-      <c r="J49" s="1">
+      <c r="O49" s="1">
+        <v>0</v>
+      </c>
+      <c r="P49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+      <c r="S49" s="1">
+        <v>0</v>
+      </c>
+      <c r="T49" s="1">
+        <v>0</v>
+      </c>
+      <c r="U49" s="1">
+        <v>4</v>
+      </c>
+      <c r="V49" s="1">
+        <v>8</v>
+      </c>
+      <c r="W49" s="1">
+        <v>9</v>
+      </c>
+      <c r="X49" s="1">
         <v>3</v>
       </c>
-      <c r="K49" s="1">
-        <v>0</v>
-      </c>
-      <c r="L49" s="1">
-        <v>0</v>
-      </c>
-      <c r="M49" s="1">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1">
-        <v>2</v>
-      </c>
-      <c r="O49" s="1">
-        <v>0</v>
-      </c>
-      <c r="P49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="1">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1">
-        <v>0</v>
-      </c>
-      <c r="T49" s="1">
-        <v>0</v>
-      </c>
-      <c r="U49" s="1">
-        <v>0</v>
-      </c>
-      <c r="V49" s="1">
-        <v>0</v>
-      </c>
-      <c r="W49" s="1">
-        <v>0</v>
-      </c>
-      <c r="X49" s="1">
-        <v>0</v>
-      </c>
       <c r="Y49" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="1">
         <v>0</v>
       </c>
       <c r="AA49" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC49" s="1">
         <v>0</v>
@@ -7415,22 +7415,22 @@
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>1412</v>
+        <v>1495</v>
       </c>
       <c r="C50" s="1">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D50" s="1">
         <v>13</v>
       </c>
       <c r="E50" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F50" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
@@ -7439,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J50" s="1">
         <v>0</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="M50" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N50" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
@@ -7469,13 +7469,13 @@
         <v>0</v>
       </c>
       <c r="S50" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T50" s="1">
         <v>0</v>
       </c>
       <c r="U50" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V50" s="1">
         <v>0</v>
@@ -7484,7 +7484,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
@@ -7493,7 +7493,7 @@
         <v>0</v>
       </c>
       <c r="AA50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB50" s="1">
         <v>0</v>
@@ -7550,43 +7550,43 @@
     </row>
     <row r="51" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1488</v>
+      </c>
+      <c r="C51" s="1">
         <v>49</v>
       </c>
-      <c r="B51" s="1">
-        <v>1389</v>
-      </c>
-      <c r="C51" s="1">
-        <v>98</v>
-      </c>
       <c r="D51" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E51" s="1">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F51" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
         <v>8</v>
       </c>
-      <c r="H51" s="1">
-        <v>9</v>
-      </c>
-      <c r="I51" s="1">
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
         <v>4</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0</v>
-      </c>
-      <c r="K51" s="1">
-        <v>0</v>
-      </c>
-      <c r="L51" s="1">
-        <v>8</v>
-      </c>
-      <c r="M51" s="1">
-        <v>3</v>
       </c>
       <c r="N51" s="1">
         <v>1</v>
@@ -7613,25 +7613,25 @@
         <v>0</v>
       </c>
       <c r="V51" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W51" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X51" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y51" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="1">
         <v>1</v>
       </c>
-      <c r="Z51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="1">
-        <v>4</v>
-      </c>
       <c r="AB51" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC51" s="1">
         <v>0</v>
@@ -7685,22 +7685,22 @@
     </row>
     <row r="52" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="B52" s="1">
-        <v>1387</v>
+        <v>1460</v>
       </c>
       <c r="C52" s="1">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D52" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F52" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
@@ -7709,25 +7709,25 @@
         <v>0</v>
       </c>
       <c r="I52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
         <v>2</v>
       </c>
-      <c r="L52" s="1">
-        <v>0</v>
-      </c>
-      <c r="M52" s="1">
-        <v>3</v>
-      </c>
-      <c r="N52" s="1">
-        <v>1</v>
-      </c>
       <c r="O52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52" s="1">
         <v>0</v>
@@ -7736,34 +7736,34 @@
         <v>0</v>
       </c>
       <c r="R52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T52" s="1">
         <v>0</v>
       </c>
       <c r="U52" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z52" s="1">
         <v>0</v>
       </c>
       <c r="AA52" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="1">
         <v>0</v>
@@ -7820,88 +7820,88 @@
     </row>
     <row r="53" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="B53" s="1">
-        <v>1338</v>
+        <v>1458</v>
       </c>
       <c r="C53" s="1">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D53" s="1">
         <v>13</v>
       </c>
       <c r="E53" s="1">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="F53" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
       <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>10</v>
+      </c>
+      <c r="N53" s="1">
         <v>3</v>
       </c>
-      <c r="I53" s="1">
-        <v>6</v>
-      </c>
-      <c r="J53" s="1">
-        <v>4</v>
-      </c>
-      <c r="K53" s="1">
-        <v>0</v>
-      </c>
-      <c r="L53" s="1">
-        <v>0</v>
-      </c>
-      <c r="M53" s="1">
-        <v>0</v>
-      </c>
-      <c r="N53" s="1">
+      <c r="O53" s="1">
+        <v>0</v>
+      </c>
+      <c r="P53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+      <c r="S53" s="1">
+        <v>0</v>
+      </c>
+      <c r="T53" s="1">
+        <v>0</v>
+      </c>
+      <c r="U53" s="1">
+        <v>2</v>
+      </c>
+      <c r="V53" s="1">
+        <v>0</v>
+      </c>
+      <c r="W53" s="1">
+        <v>0</v>
+      </c>
+      <c r="X53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="1">
         <v>1</v>
       </c>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
-      <c r="P53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>0</v>
-      </c>
-      <c r="R53" s="1">
-        <v>0</v>
-      </c>
-      <c r="S53" s="1">
-        <v>0</v>
-      </c>
-      <c r="T53" s="1">
-        <v>0</v>
-      </c>
-      <c r="U53" s="1">
-        <v>0</v>
-      </c>
-      <c r="V53" s="1">
-        <v>0</v>
-      </c>
-      <c r="W53" s="1">
-        <v>5</v>
-      </c>
-      <c r="X53" s="1">
-        <v>6</v>
-      </c>
-      <c r="Y53" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="1">
-        <v>2</v>
-      </c>
       <c r="AB53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC53" s="1">
         <v>0</v>
@@ -7955,22 +7955,22 @@
     </row>
     <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="B54" s="1">
-        <v>1330</v>
+        <v>1457</v>
       </c>
       <c r="C54" s="1">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D54" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E54" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>0</v>
       </c>
       <c r="I54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J54" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="M54" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N54" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O54" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P54" s="1">
         <v>0</v>
@@ -8009,31 +8009,31 @@
         <v>0</v>
       </c>
       <c r="S54" s="1">
+        <v>0</v>
+      </c>
+      <c r="T54" s="1">
+        <v>0</v>
+      </c>
+      <c r="U54" s="1">
+        <v>0</v>
+      </c>
+      <c r="V54" s="1">
+        <v>0</v>
+      </c>
+      <c r="W54" s="1">
+        <v>0</v>
+      </c>
+      <c r="X54" s="1">
+        <v>9</v>
+      </c>
+      <c r="Y54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="1">
         <v>6</v>
-      </c>
-      <c r="T54" s="1">
-        <v>0</v>
-      </c>
-      <c r="U54" s="1">
-        <v>0</v>
-      </c>
-      <c r="V54" s="1">
-        <v>0</v>
-      </c>
-      <c r="W54" s="1">
-        <v>0</v>
-      </c>
-      <c r="X54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z54" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="1">
-        <v>0</v>
       </c>
       <c r="AB54" s="1">
         <v>0</v>
@@ -8090,88 +8090,88 @@
     </row>
     <row r="55" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="B55" s="1">
-        <v>1316</v>
+        <v>1450</v>
       </c>
       <c r="C55" s="1">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="D55" s="1">
         <v>13</v>
       </c>
       <c r="E55" s="1">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
       </c>
       <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
         <v>1</v>
       </c>
-      <c r="I55" s="1">
+      <c r="K55" s="1">
+        <v>0</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
         <v>3</v>
       </c>
-      <c r="J55" s="1">
-        <v>0</v>
-      </c>
-      <c r="K55" s="1">
-        <v>0</v>
-      </c>
-      <c r="L55" s="1">
+      <c r="O55" s="1">
+        <v>0</v>
+      </c>
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="1">
+        <v>0</v>
+      </c>
+      <c r="T55" s="1">
+        <v>0</v>
+      </c>
+      <c r="U55" s="1">
+        <v>0</v>
+      </c>
+      <c r="V55" s="1">
+        <v>0</v>
+      </c>
+      <c r="W55" s="1">
+        <v>0</v>
+      </c>
+      <c r="X55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="1">
         <v>3</v>
       </c>
-      <c r="M55" s="1">
-        <v>0</v>
-      </c>
-      <c r="N55" s="1">
-        <v>0</v>
-      </c>
-      <c r="O55" s="1">
-        <v>0</v>
-      </c>
-      <c r="P55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>0</v>
-      </c>
-      <c r="R55" s="1">
-        <v>0</v>
-      </c>
-      <c r="S55" s="1">
-        <v>0</v>
-      </c>
-      <c r="T55" s="1">
-        <v>0</v>
-      </c>
-      <c r="U55" s="1">
-        <v>0</v>
-      </c>
-      <c r="V55" s="1">
-        <v>2</v>
-      </c>
-      <c r="W55" s="1">
-        <v>4</v>
-      </c>
-      <c r="X55" s="1">
+      <c r="Z55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="1">
         <v>7</v>
-      </c>
-      <c r="Y55" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="1">
-        <v>2</v>
-      </c>
-      <c r="AB55" s="1">
-        <v>2</v>
       </c>
       <c r="AC55" s="1">
         <v>0</v>
@@ -8225,22 +8225,22 @@
     </row>
     <row r="56" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="B56" s="1">
-        <v>1291</v>
+        <v>1446</v>
       </c>
       <c r="C56" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D56" s="1">
         <v>13</v>
       </c>
       <c r="E56" s="1">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
@@ -8249,55 +8249,55 @@
         <v>0</v>
       </c>
       <c r="I56" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1">
         <v>0</v>
       </c>
       <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
+        <v>0</v>
+      </c>
+      <c r="T56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="1">
+        <v>0</v>
+      </c>
+      <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="W56" s="1">
+        <v>0</v>
+      </c>
+      <c r="X56" s="1">
         <v>2</v>
       </c>
-      <c r="M56" s="1">
-        <v>3</v>
-      </c>
-      <c r="N56" s="1">
-        <v>1</v>
-      </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
-      <c r="P56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1">
-        <v>0</v>
-      </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
-      <c r="T56" s="1">
-        <v>0</v>
-      </c>
-      <c r="U56" s="1">
-        <v>0</v>
-      </c>
-      <c r="V56" s="1">
-        <v>0</v>
-      </c>
-      <c r="W56" s="1">
-        <v>0</v>
-      </c>
-      <c r="X56" s="1">
-        <v>0</v>
-      </c>
       <c r="Y56" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z56" s="1">
         <v>0</v>
@@ -8360,88 +8360,88 @@
     </row>
     <row r="57" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="B57" s="1">
-        <v>1210</v>
+        <v>1416</v>
       </c>
       <c r="C57" s="1">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="D57" s="1">
         <v>13</v>
       </c>
       <c r="E57" s="1">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F57" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>4</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="O57" s="1">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="1">
+        <v>0</v>
+      </c>
+      <c r="T57" s="1">
+        <v>0</v>
+      </c>
+      <c r="U57" s="1">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
+        <v>2</v>
+      </c>
+      <c r="W57" s="1">
+        <v>4</v>
+      </c>
+      <c r="X57" s="1">
+        <v>7</v>
+      </c>
+      <c r="Y57" s="1">
         <v>1</v>
       </c>
-      <c r="K57" s="1">
-        <v>0</v>
-      </c>
-      <c r="L57" s="1">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1">
-        <v>3</v>
-      </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
-      <c r="T57" s="1">
-        <v>0</v>
-      </c>
-      <c r="U57" s="1">
-        <v>0</v>
-      </c>
-      <c r="V57" s="1">
-        <v>0</v>
-      </c>
-      <c r="W57" s="1">
-        <v>0</v>
-      </c>
-      <c r="X57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="1">
-        <v>3</v>
-      </c>
       <c r="Z57" s="1">
         <v>0</v>
       </c>
       <c r="AA57" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB57" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC57" s="1">
         <v>0</v>
@@ -8495,35 +8495,35 @@
     </row>
     <row r="58" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="B58" s="1">
-        <v>1199</v>
+        <v>1330</v>
       </c>
       <c r="C58" s="1">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D58" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E58" s="1">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F58" s="1">
+        <v>37</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
         <v>2</v>
       </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
-        <v>5</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0</v>
-      </c>
       <c r="K58" s="1">
         <v>0</v>
       </c>
@@ -8531,13 +8531,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N58" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O58" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P58" s="1">
         <v>0</v>
@@ -8549,13 +8549,13 @@
         <v>0</v>
       </c>
       <c r="S58" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T58" s="1">
         <v>0</v>
       </c>
       <c r="U58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V58" s="1">
         <v>0</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="X58" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z58" s="1">
         <v>0</v>
@@ -8630,22 +8630,22 @@
     </row>
     <row r="59" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="B59" s="1">
-        <v>1188</v>
+        <v>1326</v>
       </c>
       <c r="C59" s="1">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D59" s="1">
         <v>13</v>
       </c>
       <c r="E59" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F59" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="I59" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J59" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
@@ -8669,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O59" s="1">
         <v>0</v>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T59" s="1">
         <v>0</v>
@@ -8696,22 +8696,22 @@
         <v>0</v>
       </c>
       <c r="W59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X59" s="1">
         <v>0</v>
       </c>
       <c r="Y59" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z59" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="1">
         <v>0</v>
       </c>
       <c r="AB59" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="1">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="60" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="B60" s="1">
-        <v>1180</v>
+        <v>1326</v>
       </c>
       <c r="C60" s="1">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D60" s="1">
         <v>13</v>
       </c>
       <c r="E60" s="1">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="F60" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
@@ -8789,19 +8789,19 @@
         <v>0</v>
       </c>
       <c r="I60" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J60" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N60" s="1">
         <v>1</v>
@@ -8900,46 +8900,46 @@
     </row>
     <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B61" s="1">
-        <v>1136</v>
+        <v>1265</v>
       </c>
       <c r="C61" s="1">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="D61" s="1">
         <v>13</v>
       </c>
       <c r="E61" s="1">
+        <v>60</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1">
+        <v>5</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
         <v>3</v>
       </c>
-      <c r="F61" s="1">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0</v>
-      </c>
-      <c r="H61" s="1">
-        <v>0</v>
-      </c>
-      <c r="I61" s="1">
-        <v>0</v>
-      </c>
-      <c r="J61" s="1">
-        <v>0</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
-      </c>
-      <c r="L61" s="1">
-        <v>0</v>
-      </c>
-      <c r="M61" s="1">
-        <v>20</v>
-      </c>
       <c r="N61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" s="1">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V61" s="1">
         <v>0</v>
@@ -8969,7 +8969,7 @@
         <v>0</v>
       </c>
       <c r="X61" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="1">
         <v>0</v>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="AA61" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB61" s="1">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="62" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B62" s="1">
-        <v>1110</v>
+        <v>1218</v>
       </c>
       <c r="C62" s="1">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D62" s="1">
+        <v>13</v>
+      </c>
+      <c r="E62" s="1">
         <v>4</v>
       </c>
-      <c r="E62" s="1">
-        <v>0</v>
-      </c>
       <c r="F62" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
@@ -9059,10 +9059,10 @@
         <v>0</v>
       </c>
       <c r="I62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -9071,10 +9071,10 @@
         <v>0</v>
       </c>
       <c r="M62" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" s="1">
         <v>0</v>
@@ -9089,7 +9089,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T62" s="1">
         <v>0</v>
@@ -9113,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="AA62" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB62" s="1">
         <v>0</v>
@@ -9170,22 +9170,22 @@
     </row>
     <row r="63" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="B63" s="1">
-        <v>1106</v>
+        <v>1188</v>
       </c>
       <c r="C63" s="1">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D63" s="1">
         <v>13</v>
       </c>
       <c r="E63" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F63" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
@@ -9194,11 +9194,11 @@
         <v>0</v>
       </c>
       <c r="I63" s="1">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1">
         <v>3</v>
       </c>
-      <c r="J63" s="1">
-        <v>1</v>
-      </c>
       <c r="K63" s="1">
         <v>0</v>
       </c>
@@ -9206,52 +9206,52 @@
         <v>0</v>
       </c>
       <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>0</v>
+      </c>
+      <c r="O63" s="1">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="1">
+        <v>3</v>
+      </c>
+      <c r="T63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="1">
+        <v>0</v>
+      </c>
+      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="W63" s="1">
         <v>2</v>
       </c>
-      <c r="N63" s="1">
+      <c r="X63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z63" s="1">
         <v>3</v>
       </c>
-      <c r="O63" s="1">
-        <v>0</v>
-      </c>
-      <c r="P63" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="1">
-        <v>0</v>
-      </c>
-      <c r="R63" s="1">
-        <v>0</v>
-      </c>
-      <c r="S63" s="1">
-        <v>11</v>
-      </c>
-      <c r="T63" s="1">
-        <v>0</v>
-      </c>
-      <c r="U63" s="1">
+      <c r="AA63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="1">
         <v>5</v>
-      </c>
-      <c r="V63" s="1">
-        <v>0</v>
-      </c>
-      <c r="W63" s="1">
-        <v>0</v>
-      </c>
-      <c r="X63" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y63" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB63" s="1">
-        <v>0</v>
       </c>
       <c r="AC63" s="1">
         <v>0</v>
@@ -9305,85 +9305,85 @@
     </row>
     <row r="64" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="B64" s="1">
-        <v>1094</v>
+        <v>1180</v>
       </c>
       <c r="C64" s="1">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D64" s="1">
         <v>13</v>
       </c>
       <c r="E64" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I64" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J64" s="1">
+        <v>3</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <v>2</v>
+      </c>
+      <c r="N64" s="1">
+        <v>0</v>
+      </c>
+      <c r="O64" s="1">
+        <v>0</v>
+      </c>
+      <c r="P64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>0</v>
+      </c>
+      <c r="R64" s="1">
+        <v>0</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0</v>
+      </c>
+      <c r="T64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1">
         <v>1</v>
       </c>
-      <c r="K64" s="1">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1">
-        <v>0</v>
-      </c>
-      <c r="M64" s="1">
-        <v>0</v>
-      </c>
-      <c r="N64" s="1">
-        <v>4</v>
-      </c>
-      <c r="O64" s="1">
-        <v>0</v>
-      </c>
-      <c r="P64" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="1">
-        <v>0</v>
-      </c>
-      <c r="R64" s="1">
-        <v>0</v>
-      </c>
-      <c r="S64" s="1">
-        <v>0</v>
-      </c>
-      <c r="T64" s="1">
-        <v>0</v>
-      </c>
-      <c r="U64" s="1">
-        <v>0</v>
-      </c>
       <c r="V64" s="1">
         <v>0</v>
       </c>
       <c r="W64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y64" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z64" s="1">
         <v>0</v>
       </c>
       <c r="AA64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB64" s="1">
         <v>0</v>
@@ -9440,85 +9440,85 @@
     </row>
     <row r="65" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B65" s="1">
-        <v>1075</v>
+        <v>1178</v>
       </c>
       <c r="C65" s="1">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D65" s="1">
         <v>13</v>
       </c>
       <c r="E65" s="1">
+        <v>31</v>
+      </c>
+      <c r="F65" s="1">
+        <v>8</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>2</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1">
+        <v>2</v>
+      </c>
+      <c r="O65" s="1">
+        <v>2</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>0</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+      <c r="S65" s="1">
         <v>11</v>
       </c>
-      <c r="F65" s="1">
-        <v>7</v>
-      </c>
-      <c r="G65" s="1">
-        <v>1</v>
-      </c>
-      <c r="H65" s="1">
-        <v>4</v>
-      </c>
-      <c r="I65" s="1">
-        <v>3</v>
-      </c>
-      <c r="J65" s="1">
-        <v>3</v>
-      </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
-      <c r="L65" s="1">
-        <v>0</v>
-      </c>
-      <c r="M65" s="1">
-        <v>1</v>
-      </c>
-      <c r="N65" s="1">
-        <v>0</v>
-      </c>
-      <c r="O65" s="1">
-        <v>0</v>
-      </c>
-      <c r="P65" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>0</v>
-      </c>
-      <c r="R65" s="1">
-        <v>0</v>
-      </c>
-      <c r="S65" s="1">
-        <v>0</v>
-      </c>
       <c r="T65" s="1">
         <v>0</v>
       </c>
       <c r="U65" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V65" s="1">
         <v>0</v>
       </c>
       <c r="W65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X65" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y65" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z65" s="1">
         <v>0</v>
       </c>
       <c r="AA65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB65" s="1">
         <v>0</v>
@@ -9575,22 +9575,22 @@
     </row>
     <row r="66" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="B66" s="1">
-        <v>1073</v>
+        <v>1160</v>
       </c>
       <c r="C66" s="1">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D66" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E66" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F66" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
@@ -9599,10 +9599,10 @@
         <v>0</v>
       </c>
       <c r="I66" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J66" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
@@ -9611,10 +9611,10 @@
         <v>0</v>
       </c>
       <c r="M66" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" s="1">
         <v>0</v>
@@ -9629,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T66" s="1">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y66" s="1">
         <v>0</v>
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AA66" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB66" s="1">
         <v>0</v>
@@ -9710,49 +9710,49 @@
     </row>
     <row r="67" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="B67" s="1">
-        <v>1032</v>
+        <v>1142</v>
       </c>
       <c r="C67" s="1">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D67" s="1">
         <v>13</v>
       </c>
       <c r="E67" s="1">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F67" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
       </c>
       <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="1">
+        <v>3</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1">
         <v>2</v>
       </c>
-      <c r="I67" s="1">
-        <v>0</v>
-      </c>
-      <c r="J67" s="1">
-        <v>0</v>
-      </c>
-      <c r="K67" s="1">
-        <v>0</v>
-      </c>
-      <c r="L67" s="1">
-        <v>0</v>
-      </c>
-      <c r="M67" s="1">
-        <v>0</v>
-      </c>
       <c r="N67" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O67" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P67" s="1">
         <v>0</v>
@@ -9764,7 +9764,7 @@
         <v>0</v>
       </c>
       <c r="S67" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T67" s="1">
         <v>0</v>
@@ -9779,10 +9779,10 @@
         <v>0</v>
       </c>
       <c r="X67" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y67" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z67" s="1">
         <v>0</v>
@@ -9845,85 +9845,85 @@
     </row>
     <row r="68" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B68" s="1">
-        <v>1011</v>
+        <v>1073</v>
       </c>
       <c r="C68" s="1">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E68" s="1">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1">
+        <v>8</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>15</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="1">
         <v>5</v>
       </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1">
-        <v>0</v>
-      </c>
-      <c r="I68" s="1">
-        <v>0</v>
-      </c>
-      <c r="J68" s="1">
-        <v>0</v>
-      </c>
-      <c r="K68" s="1">
-        <v>0</v>
-      </c>
-      <c r="L68" s="1">
+      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
         <v>3</v>
       </c>
-      <c r="M68" s="1">
+      <c r="Y68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="1">
         <v>1</v>
-      </c>
-      <c r="N68" s="1">
-        <v>4</v>
-      </c>
-      <c r="O68" s="1">
-        <v>0</v>
-      </c>
-      <c r="P68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>0</v>
-      </c>
-      <c r="R68" s="1">
-        <v>0</v>
-      </c>
-      <c r="S68" s="1">
-        <v>0</v>
-      </c>
-      <c r="T68" s="1">
-        <v>0</v>
-      </c>
-      <c r="U68" s="1">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1">
-        <v>0</v>
-      </c>
-      <c r="W68" s="1">
-        <v>0</v>
-      </c>
-      <c r="X68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="1">
-        <v>0</v>
       </c>
       <c r="AB68" s="1">
         <v>0</v>
@@ -9980,49 +9980,49 @@
     </row>
     <row r="69" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="B69" s="1">
-        <v>991</v>
+        <v>1050</v>
       </c>
       <c r="C69" s="1">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="D69" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E69" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F69" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I69" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M69" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P69" s="1">
         <v>0</v>
@@ -10046,16 +10046,16 @@
         <v>0</v>
       </c>
       <c r="W69" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X69" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="1">
         <v>1</v>
       </c>
-      <c r="Y69" s="1">
-        <v>0</v>
-      </c>
       <c r="Z69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA69" s="1">
         <v>0</v>
@@ -10115,82 +10115,82 @@
     </row>
     <row r="70" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="B70" s="1">
-        <v>920</v>
+        <v>1035</v>
       </c>
       <c r="C70" s="1">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="D70" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E70" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I70" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>5</v>
+      </c>
+      <c r="M70" s="1">
+        <v>5</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
+      <c r="O70" s="1">
+        <v>0</v>
+      </c>
+      <c r="P70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>0</v>
+      </c>
+      <c r="R70" s="1">
+        <v>0</v>
+      </c>
+      <c r="S70" s="1">
+        <v>0</v>
+      </c>
+      <c r="T70" s="1">
+        <v>0</v>
+      </c>
+      <c r="U70" s="1">
+        <v>0</v>
+      </c>
+      <c r="V70" s="1">
+        <v>0</v>
+      </c>
+      <c r="W70" s="1">
+        <v>24</v>
+      </c>
+      <c r="X70" s="1">
         <v>1</v>
       </c>
-      <c r="K70" s="1">
-        <v>1</v>
-      </c>
-      <c r="L70" s="1">
-        <v>0</v>
-      </c>
-      <c r="M70" s="1">
-        <v>0</v>
-      </c>
-      <c r="N70" s="1">
-        <v>1</v>
-      </c>
-      <c r="O70" s="1">
-        <v>1</v>
-      </c>
-      <c r="P70" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="1">
-        <v>0</v>
-      </c>
-      <c r="R70" s="1">
-        <v>0</v>
-      </c>
-      <c r="S70" s="1">
-        <v>0</v>
-      </c>
-      <c r="T70" s="1">
-        <v>0</v>
-      </c>
-      <c r="U70" s="1">
-        <v>0</v>
-      </c>
-      <c r="V70" s="1">
-        <v>0</v>
-      </c>
-      <c r="W70" s="1">
-        <v>0</v>
-      </c>
-      <c r="X70" s="1">
-        <v>0</v>
-      </c>
       <c r="Y70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="1">
         <v>0</v>
@@ -10250,22 +10250,22 @@
     </row>
     <row r="71" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1">
-        <v>850</v>
+        <v>902</v>
       </c>
       <c r="C71" s="1">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D71" s="1">
         <v>13</v>
       </c>
       <c r="E71" s="1">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F71" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
@@ -10274,52 +10274,52 @@
         <v>0</v>
       </c>
       <c r="I71" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J71" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1">
+        <v>4</v>
+      </c>
+      <c r="N71" s="1">
+        <v>0</v>
+      </c>
+      <c r="O71" s="1">
+        <v>0</v>
+      </c>
+      <c r="P71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>0</v>
+      </c>
+      <c r="R71" s="1">
+        <v>0</v>
+      </c>
+      <c r="S71" s="1">
+        <v>6</v>
+      </c>
+      <c r="T71" s="1">
+        <v>0</v>
+      </c>
+      <c r="U71" s="1">
+        <v>0</v>
+      </c>
+      <c r="V71" s="1">
+        <v>0</v>
+      </c>
+      <c r="W71" s="1">
         <v>1</v>
       </c>
-      <c r="L71" s="1">
-        <v>0</v>
-      </c>
-      <c r="M71" s="1">
-        <v>0</v>
-      </c>
-      <c r="N71" s="1">
-        <v>2</v>
-      </c>
-      <c r="O71" s="1">
-        <v>0</v>
-      </c>
-      <c r="P71" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="1">
-        <v>0</v>
-      </c>
-      <c r="R71" s="1">
-        <v>0</v>
-      </c>
-      <c r="S71" s="1">
-        <v>0</v>
-      </c>
-      <c r="T71" s="1">
-        <v>0</v>
-      </c>
-      <c r="U71" s="1">
-        <v>0</v>
-      </c>
-      <c r="V71" s="1">
-        <v>0</v>
-      </c>
-      <c r="W71" s="1">
-        <v>0</v>
-      </c>
       <c r="X71" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y71" s="1">
         <v>0</v>
@@ -10388,10 +10388,10 @@
         <v>85</v>
       </c>
       <c r="B72" s="1">
-        <v>837</v>
+        <v>897</v>
       </c>
       <c r="C72" s="1">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -10400,7 +10400,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
@@ -10520,22 +10520,22 @@
     </row>
     <row r="73" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B73" s="1">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="C73" s="1">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D73" s="1">
         <v>13</v>
       </c>
       <c r="E73" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F73" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
@@ -10544,22 +10544,22 @@
         <v>0</v>
       </c>
       <c r="I73" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J73" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="1">
         <v>0</v>
       </c>
       <c r="M73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N73" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O73" s="1">
         <v>0</v>
@@ -10574,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T73" s="1">
         <v>0</v>
@@ -10586,10 +10586,10 @@
         <v>0</v>
       </c>
       <c r="W73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y73" s="1">
         <v>0</v>
@@ -10790,22 +10790,22 @@
     </row>
     <row r="75" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B75" s="1">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="C75" s="1">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D75" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E75" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
@@ -10826,7 +10826,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N75" s="1">
         <v>0</v>
@@ -10844,13 +10844,13 @@
         <v>0</v>
       </c>
       <c r="S75" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T75" s="1">
         <v>0</v>
       </c>
       <c r="U75" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V75" s="1">
         <v>0</v>
@@ -10859,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="X75" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y75" s="1">
         <v>0</v>
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="AA75" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC75" s="1">
         <v>0</v>
@@ -10925,22 +10925,22 @@
     </row>
     <row r="76" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B76" s="1">
-        <v>639</v>
+        <v>674</v>
       </c>
       <c r="C76" s="1">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D76" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E76" s="1">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F76" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -10961,7 +10961,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N76" s="1">
         <v>0</v>
@@ -10979,7 +10979,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T76" s="1">
         <v>0</v>
@@ -10994,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y76" s="1">
         <v>0</v>
@@ -11003,10 +11003,10 @@
         <v>0</v>
       </c>
       <c r="AA76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="1">
         <v>1</v>
-      </c>
-      <c r="AB76" s="1">
-        <v>0</v>
       </c>
       <c r="AC76" s="1">
         <v>0</v>
@@ -11195,22 +11195,22 @@
     </row>
     <row r="78" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B78" s="1">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="C78" s="1">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D78" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E78" s="1">
         <v>0</v>
       </c>
       <c r="F78" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
@@ -11222,23 +11222,23 @@
         <v>0</v>
       </c>
       <c r="J78" s="1">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+      <c r="L78" s="1">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1">
+        <v>0</v>
+      </c>
+      <c r="O78" s="1">
         <v>1</v>
       </c>
-      <c r="K78" s="1">
-        <v>0</v>
-      </c>
-      <c r="L78" s="1">
-        <v>0</v>
-      </c>
-      <c r="M78" s="1">
-        <v>0</v>
-      </c>
-      <c r="N78" s="1">
-        <v>2</v>
-      </c>
-      <c r="O78" s="1">
-        <v>0</v>
-      </c>
       <c r="P78" s="1">
         <v>0</v>
       </c>
@@ -11249,13 +11249,13 @@
         <v>0</v>
       </c>
       <c r="S78" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T78" s="1">
         <v>0</v>
       </c>
       <c r="U78" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V78" s="1">
         <v>0</v>
@@ -11267,13 +11267,13 @@
         <v>0</v>
       </c>
       <c r="Y78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="1">
         <v>1</v>
-      </c>
-      <c r="Z78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="1">
-        <v>0</v>
       </c>
       <c r="AB78" s="1">
         <v>0</v>
@@ -11330,22 +11330,22 @@
     </row>
     <row r="79" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B79" s="1">
-        <v>410</v>
+        <v>451</v>
       </c>
       <c r="C79" s="1">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D79" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E79" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G79" s="1">
         <v>0</v>
@@ -11366,13 +11366,13 @@
         <v>0</v>
       </c>
       <c r="M79" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N79" s="1">
         <v>0</v>
       </c>
       <c r="O79" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P79" s="1">
         <v>0</v>
@@ -11384,19 +11384,19 @@
         <v>0</v>
       </c>
       <c r="S79" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T79" s="1">
         <v>0</v>
       </c>
       <c r="U79" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V79" s="1">
         <v>0</v>
       </c>
       <c r="W79" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X79" s="1">
         <v>0</v>
@@ -11465,32 +11465,32 @@
     </row>
     <row r="80" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B80" s="1">
-        <v>270</v>
+        <v>447</v>
       </c>
       <c r="C80" s="1">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D80" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E80" s="1">
+        <v>2</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>3</v>
+      </c>
+      <c r="I80" s="1">
         <v>8</v>
       </c>
-      <c r="F80" s="1">
-        <v>0</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0</v>
-      </c>
-      <c r="H80" s="1">
-        <v>0</v>
-      </c>
-      <c r="I80" s="1">
-        <v>0</v>
-      </c>
       <c r="J80" s="1">
         <v>0</v>
       </c>
@@ -11498,10 +11498,10 @@
         <v>0</v>
       </c>
       <c r="L80" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" s="1">
         <v>0</v>
@@ -11519,7 +11519,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" s="1">
         <v>0</v>
@@ -11531,10 +11531,10 @@
         <v>0</v>
       </c>
       <c r="W80" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X80" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y80" s="1">
         <v>0</v>
@@ -11543,7 +11543,7 @@
         <v>0</v>
       </c>
       <c r="AA80" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB80" s="1">
         <v>0</v>
@@ -11600,34 +11600,34 @@
     </row>
     <row r="81" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B81" s="1">
-        <v>251</v>
+        <v>440</v>
       </c>
       <c r="C81" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D81" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E81" s="1">
         <v>0</v>
       </c>
       <c r="F81" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I81" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
@@ -11636,43 +11636,43 @@
         <v>0</v>
       </c>
       <c r="M81" s="1">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1">
+        <v>2</v>
+      </c>
+      <c r="O81" s="1">
+        <v>0</v>
+      </c>
+      <c r="P81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>0</v>
+      </c>
+      <c r="R81" s="1">
+        <v>0</v>
+      </c>
+      <c r="S81" s="1">
+        <v>0</v>
+      </c>
+      <c r="T81" s="1">
+        <v>0</v>
+      </c>
+      <c r="U81" s="1">
+        <v>0</v>
+      </c>
+      <c r="V81" s="1">
+        <v>0</v>
+      </c>
+      <c r="W81" s="1">
+        <v>0</v>
+      </c>
+      <c r="X81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="1">
         <v>1</v>
-      </c>
-      <c r="N81" s="1">
-        <v>0</v>
-      </c>
-      <c r="O81" s="1">
-        <v>0</v>
-      </c>
-      <c r="P81" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="1">
-        <v>0</v>
-      </c>
-      <c r="R81" s="1">
-        <v>0</v>
-      </c>
-      <c r="S81" s="1">
-        <v>1</v>
-      </c>
-      <c r="T81" s="1">
-        <v>0</v>
-      </c>
-      <c r="U81" s="1">
-        <v>0</v>
-      </c>
-      <c r="V81" s="1">
-        <v>0</v>
-      </c>
-      <c r="W81" s="1">
-        <v>3</v>
-      </c>
-      <c r="X81" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y81" s="1">
-        <v>0</v>
       </c>
       <c r="Z81" s="1">
         <v>0</v>
@@ -11735,22 +11735,22 @@
     </row>
     <row r="82" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="B82" s="1">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C82" s="1">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D82" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F82" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -11870,22 +11870,22 @@
     </row>
     <row r="83" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B83" s="1">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="C83" s="1">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D83" s="1">
         <v>13</v>
       </c>
       <c r="E83" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F83" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G83" s="1">
         <v>0</v>
@@ -12005,7 +12005,7 @@
     </row>
     <row r="84" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="B84" s="1">
         <v>130</v>
@@ -12140,16 +12140,16 @@
     </row>
     <row r="85" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="B85" s="1">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="C85" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D85" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
@@ -12194,7 +12194,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T85" s="1">
         <v>0</v>
@@ -12275,19 +12275,19 @@
     </row>
     <row r="86" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B86" s="1">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C86" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -12335,7 +12335,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V86" s="1">
         <v>0</v>
@@ -12410,13 +12410,13 @@
     </row>
     <row r="87" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B87" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C87" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
@@ -12425,7 +12425,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="1">
         <v>0</v>
@@ -12464,7 +12464,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T87" s="1">
         <v>0</v>
@@ -12545,19 +12545,19 @@
     </row>
     <row r="88" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B88" s="1">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C88" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -12680,13 +12680,13 @@
     </row>
     <row r="89" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B89" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -12695,7 +12695,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="1">
         <v>0</v>
@@ -12815,7 +12815,7 @@
     </row>
     <row r="90" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B90" s="1">
         <v>0</v>
@@ -12950,7 +12950,7 @@
     </row>
     <row r="91" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="B91" s="1">
         <v>0</v>
@@ -13085,7 +13085,7 @@
     </row>
     <row r="92" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B92" s="1">
         <v>0</v>

--- a/Results1.xlsx
+++ b/Results1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raouf\Desktop\Clan_Chest\Chest_Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2595D613-6607-45C3-B47C-23A571386B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4AB5CF-9735-43D1-94A2-D733CB9EF361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8B40F6D1-9A99-4C4C-A584-B5A2D365FA79}"/>
   </bookViews>
@@ -267,9 +267,6 @@
     <t>Maxi</t>
   </si>
   <si>
-    <t>mazerunner</t>
-  </si>
-  <si>
     <t>Megrin</t>
   </si>
   <si>
@@ -403,6 +400,9 @@
   </si>
   <si>
     <t>x3kerrypiex3</t>
+  </si>
+  <si>
+    <t>Starshij Brat</t>
   </si>
 </sst>
 </file>
@@ -935,22 +935,22 @@
     </row>
     <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="1">
-        <v>5306</v>
+        <v>5541</v>
       </c>
       <c r="C2" s="1">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D2" s="1">
         <v>13</v>
       </c>
       <c r="E2" s="1">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F2" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="AC2" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD2" s="1">
         <v>3</v>
@@ -1031,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="AG2" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH2" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -1070,43 +1070,43 @@
     </row>
     <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>3914</v>
+        <v>4065</v>
       </c>
       <c r="C3" s="1">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D3" s="1">
         <v>13</v>
       </c>
       <c r="E3" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I3" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="1">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T3" s="1">
         <v>0</v>
@@ -1136,19 +1136,19 @@
         <v>0</v>
       </c>
       <c r="W3" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X3" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y3" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z3" s="1">
         <v>1</v>
       </c>
       <c r="AA3" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AB3" s="1">
         <v>1</v>
@@ -1205,22 +1205,22 @@
     </row>
     <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="B4" s="1">
-        <v>3775</v>
+        <v>4060</v>
       </c>
       <c r="C4" s="1">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="D4" s="1">
         <v>13</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1229,19 +1229,19 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K4" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M4" s="1">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T4" s="1">
         <v>0</v>
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="W4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y4" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z4" s="1">
         <v>1</v>
       </c>
       <c r="AA4" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AB4" s="1">
         <v>1</v>
@@ -1343,10 +1343,10 @@
         <v>60</v>
       </c>
       <c r="B5" s="1">
-        <v>3682</v>
+        <v>3762</v>
       </c>
       <c r="C5" s="1">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D5" s="1">
         <v>13</v>
@@ -1373,13 +1373,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="1">
         <v>8</v>
       </c>
       <c r="N5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -1475,22 +1475,22 @@
     </row>
     <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="C6" s="1">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D6" s="1">
         <v>13</v>
       </c>
       <c r="E6" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1499,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J6" s="1">
         <v>11</v>
@@ -1511,13 +1511,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="N6" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O6" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X6" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y6" s="1">
         <v>8</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="AA6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC6" s="1">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1">
-        <v>3326</v>
+        <v>3445</v>
       </c>
       <c r="C7" s="1">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="D7" s="1">
         <v>13</v>
       </c>
       <c r="E7" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1634,25 +1634,25 @@
         <v>0</v>
       </c>
       <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>7</v>
+      </c>
+      <c r="K7" s="1">
         <v>8</v>
       </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
       <c r="L7" s="1">
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T7" s="1">
         <v>0</v>
@@ -1679,22 +1679,22 @@
         <v>0</v>
       </c>
       <c r="X7" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="1">
         <v>0</v>
       </c>
       <c r="AC7" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD7" s="1">
         <v>0</v>
@@ -1745,46 +1745,46 @@
     </row>
     <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="B8" s="1">
-        <v>3228</v>
+        <v>3409</v>
       </c>
       <c r="C8" s="1">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D8" s="1">
         <v>13</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J8" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -1811,22 +1811,22 @@
         <v>0</v>
       </c>
       <c r="W8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X8" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y8" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z8" s="1">
         <v>0</v>
       </c>
       <c r="AA8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="1">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
@@ -1880,22 +1880,22 @@
     </row>
     <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B9" s="1">
-        <v>3028</v>
+        <v>3338</v>
       </c>
       <c r="C9" s="1">
-        <v>104</v>
+        <v>199</v>
       </c>
       <c r="D9" s="1">
         <v>13</v>
       </c>
       <c r="E9" s="1">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="F9" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1904,10 +1904,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J9" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -1916,32 +1916,32 @@
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
         <v>5</v>
       </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>6</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
-      <c r="U9" s="1">
-        <v>3</v>
-      </c>
       <c r="V9" s="1">
         <v>0</v>
       </c>
@@ -1949,16 +1949,16 @@
         <v>0</v>
       </c>
       <c r="X9" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y9" s="1">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="1">
         <v>0</v>
       </c>
       <c r="AA9" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" s="1">
         <v>0</v>
@@ -2015,46 +2015,46 @@
     </row>
     <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B10" s="1">
-        <v>2978</v>
+        <v>3316</v>
       </c>
       <c r="C10" s="1">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="D10" s="1">
         <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F10" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="1">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J10" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" s="1">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="N10" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -2084,16 +2084,16 @@
         <v>0</v>
       </c>
       <c r="X10" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y10" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="1">
         <v>0</v>
       </c>
       <c r="AA10" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AB10" s="1">
         <v>0</v>
@@ -2150,34 +2150,34 @@
     </row>
     <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>2890</v>
+        <v>3243</v>
       </c>
       <c r="C11" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" s="1">
         <v>13</v>
       </c>
       <c r="E11" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -2186,13 +2186,13 @@
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N11" s="1">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="O11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -2222,22 +2222,22 @@
         <v>0</v>
       </c>
       <c r="Y11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
       </c>
       <c r="AC11" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AD11" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="1">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="AG11" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="1">
         <v>12</v>
@@ -2285,31 +2285,31 @@
     </row>
     <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B12" s="1">
-        <v>2879</v>
+        <v>3228</v>
       </c>
       <c r="C12" s="1">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D12" s="1">
         <v>13</v>
       </c>
       <c r="E12" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M12" s="1">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="N12" s="1">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T12" s="1">
         <v>0</v>
@@ -2357,16 +2357,16 @@
         <v>0</v>
       </c>
       <c r="Y12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB12" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AC12" s="1">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
@@ -2420,46 +2420,46 @@
     </row>
     <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1">
-        <v>2836</v>
+        <v>3151</v>
       </c>
       <c r="C13" s="1">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D13" s="1">
         <v>13</v>
       </c>
       <c r="E13" s="1">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
       </c>
       <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
         <v>6</v>
       </c>
-      <c r="M13" s="1">
-        <v>26</v>
-      </c>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O13" s="1">
         <v>0</v>
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T13" s="1">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="X13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="1">
         <v>0</v>
@@ -2498,16 +2498,16 @@
         <v>0</v>
       </c>
       <c r="AA13" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="1">
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD13" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE13" s="1">
         <v>0</v>
@@ -2516,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="AG13" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH13" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -2555,31 +2555,31 @@
     </row>
     <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B14" s="1">
-        <v>2768</v>
+        <v>3084</v>
       </c>
       <c r="C14" s="1">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J14" s="1">
         <v>8</v>
@@ -2591,10 +2591,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N14" s="1">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -2609,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T14" s="1">
         <v>0</v>
@@ -2624,22 +2624,22 @@
         <v>0</v>
       </c>
       <c r="X14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="1">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Z14" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="1">
         <v>0</v>
       </c>
       <c r="AC14" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="1">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
@@ -2690,22 +2690,22 @@
     </row>
     <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="B15" s="1">
-        <v>2627</v>
+        <v>2990</v>
       </c>
       <c r="C15" s="1">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="D15" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F15" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -2714,22 +2714,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J15" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="N15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -2759,22 +2759,22 @@
         <v>0</v>
       </c>
       <c r="X15" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA15" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC15" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -2825,49 +2825,49 @@
     </row>
     <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="B16" s="1">
-        <v>2434</v>
+        <v>2983</v>
       </c>
       <c r="C16" s="1">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="D16" s="1">
         <v>13</v>
       </c>
       <c r="E16" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F16" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J16" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="1">
+        <v>13</v>
+      </c>
+      <c r="N16" s="1">
         <v>2</v>
       </c>
-      <c r="N16" s="1">
-        <v>4</v>
-      </c>
       <c r="O16" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" s="1">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T16" s="1">
         <v>0</v>
@@ -2888,26 +2888,26 @@
         <v>5</v>
       </c>
       <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>12</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="1">
         <v>1</v>
       </c>
-      <c r="W16" s="1">
-        <v>0</v>
-      </c>
-      <c r="X16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>15</v>
-      </c>
-      <c r="Z16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="1">
-        <v>0</v>
-      </c>
       <c r="AC16" s="1">
         <v>0</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
@@ -2960,22 +2960,22 @@
     </row>
     <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1">
-        <v>2415</v>
+        <v>2978</v>
       </c>
       <c r="C17" s="1">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="D17" s="1">
         <v>13</v>
       </c>
       <c r="E17" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -2984,25 +2984,25 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J17" s="1">
+        <v>12</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
         <v>8</v>
       </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
       <c r="N17" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="1">
         <v>0</v>
@@ -3029,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="X17" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y17" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z17" s="1">
         <v>0</v>
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="AC17" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD17" s="1">
         <v>0</v>
@@ -3095,88 +3095,88 @@
     </row>
     <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B18" s="1">
-        <v>2403</v>
+        <v>2910</v>
       </c>
       <c r="C18" s="1">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="D18" s="1">
         <v>13</v>
       </c>
       <c r="E18" s="1">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>6</v>
+      </c>
+      <c r="O18" s="1">
+        <v>2</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="1">
         <v>3</v>
       </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1">
+      <c r="Z18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1">
         <v>7</v>
-      </c>
-      <c r="M18" s="1">
-        <v>5</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-      <c r="P18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1">
-        <v>0</v>
-      </c>
-      <c r="S18" s="1">
-        <v>0</v>
-      </c>
-      <c r="T18" s="1">
-        <v>0</v>
-      </c>
-      <c r="U18" s="1">
-        <v>4</v>
-      </c>
-      <c r="V18" s="1">
-        <v>1</v>
-      </c>
-      <c r="W18" s="1">
-        <v>3</v>
-      </c>
-      <c r="X18" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB18" s="1">
-        <v>1</v>
       </c>
       <c r="AC18" s="1">
         <v>0</v>
@@ -3230,13 +3230,13 @@
     </row>
     <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1">
-        <v>2360</v>
+        <v>2715</v>
       </c>
       <c r="C19" s="1">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="D19" s="1">
         <v>13</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -3269,10 +3269,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="1">
         <v>0</v>
@@ -3281,40 +3281,40 @@
         <v>0</v>
       </c>
       <c r="R19" s="1">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <v>6</v>
+      </c>
+      <c r="T19" s="1">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1">
+        <v>5</v>
+      </c>
+      <c r="V19" s="1">
+        <v>0</v>
+      </c>
+      <c r="W19" s="1">
+        <v>0</v>
+      </c>
+      <c r="X19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="1">
         <v>3</v>
-      </c>
-      <c r="S19" s="1">
-        <v>0</v>
-      </c>
-      <c r="T19" s="1">
-        <v>0</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0</v>
-      </c>
-      <c r="V19" s="1">
-        <v>0</v>
-      </c>
-      <c r="W19" s="1">
-        <v>0</v>
-      </c>
-      <c r="X19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="1">
-        <v>11</v>
-      </c>
-      <c r="AA19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="1">
-        <v>21</v>
-      </c>
-      <c r="AC19" s="1">
-        <v>0</v>
       </c>
       <c r="AD19" s="1">
         <v>0</v>
@@ -3365,49 +3365,49 @@
     </row>
     <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B20" s="1">
-        <v>2345</v>
+        <v>2644</v>
       </c>
       <c r="C20" s="1">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="D20" s="1">
         <v>13</v>
       </c>
       <c r="E20" s="1">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="F20" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I20" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J20" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M20" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N20" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P20" s="1">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T20" s="1">
         <v>0</v>
@@ -3428,31 +3428,31 @@
         <v>5</v>
       </c>
       <c r="V20" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X20" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="1">
         <v>1</v>
       </c>
-      <c r="AA20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="1">
-        <v>0</v>
-      </c>
       <c r="AC20" s="1">
         <v>0</v>
       </c>
       <c r="AD20" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="1">
         <v>0</v>
@@ -3461,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="AG20" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="1">
         <v>0</v>
@@ -3500,22 +3500,22 @@
     </row>
     <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="B21" s="1">
-        <v>2334</v>
+        <v>2642</v>
       </c>
       <c r="C21" s="1">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="D21" s="1">
         <v>13</v>
       </c>
       <c r="E21" s="1">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F21" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -3524,25 +3524,25 @@
         <v>0</v>
       </c>
       <c r="I21" s="1">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J21" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
       </c>
       <c r="L21" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M21" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N21" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="1">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="X21" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y21" s="1">
         <v>0</v>
@@ -3635,92 +3635,92 @@
     </row>
     <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="B22" s="1">
-        <v>2332</v>
+        <v>2627</v>
       </c>
       <c r="C22" s="1">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D22" s="1">
         <v>5</v>
       </c>
       <c r="E22" s="1">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1">
+        <v>13</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
         <v>8</v>
       </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
+        <v>10</v>
+      </c>
+      <c r="K22" s="1">
         <v>3</v>
       </c>
-      <c r="J22" s="1">
-        <v>7</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1">
+        <v>2</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>11</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
         <v>5</v>
       </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1">
+        <v>9</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC22" s="1">
         <v>6</v>
       </c>
-      <c r="N22" s="1">
-        <v>1</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>0</v>
-      </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>0</v>
-      </c>
-      <c r="T22" s="1">
-        <v>0</v>
-      </c>
-      <c r="U22" s="1">
-        <v>0</v>
-      </c>
-      <c r="V22" s="1">
-        <v>1</v>
-      </c>
-      <c r="W22" s="1">
-        <v>0</v>
-      </c>
-      <c r="X22" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y22" s="1">
-        <v>7</v>
-      </c>
-      <c r="Z22" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="1">
-        <v>0</v>
-      </c>
       <c r="AD22" s="1">
         <v>0</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="AH22" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
@@ -3770,22 +3770,22 @@
     </row>
     <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="1">
-        <v>2242</v>
+        <v>2565</v>
       </c>
       <c r="C23" s="1">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="D23" s="1">
         <v>13</v>
       </c>
       <c r="E23" s="1">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -3794,25 +3794,25 @@
         <v>0</v>
       </c>
       <c r="I23" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J23" s="1">
         <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N23" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O23" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P23" s="1">
         <v>0</v>
@@ -3839,13 +3839,13 @@
         <v>0</v>
       </c>
       <c r="X23" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" s="1">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE23" s="1">
         <v>0</v>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="AG23" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH23" s="1">
         <v>0</v>
@@ -3905,106 +3905,106 @@
     </row>
     <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="B24" s="1">
-        <v>2215</v>
+        <v>2494</v>
       </c>
       <c r="C24" s="1">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D24" s="1">
         <v>13</v>
       </c>
       <c r="E24" s="1">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>6</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1">
+        <v>2</v>
+      </c>
+      <c r="N24" s="1">
         <v>5</v>
       </c>
-      <c r="H24" s="1">
-        <v>4</v>
-      </c>
-      <c r="I24" s="1">
+      <c r="O24" s="1">
+        <v>2</v>
+      </c>
+      <c r="P24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>0</v>
+      </c>
+      <c r="S24" s="1">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1">
+        <v>5</v>
+      </c>
+      <c r="V24" s="1">
+        <v>1</v>
+      </c>
+      <c r="W24" s="1">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="1">
         <v>3</v>
-      </c>
-      <c r="J24" s="1">
-        <v>3</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1">
-        <v>16</v>
-      </c>
-      <c r="M24" s="1">
-        <v>7</v>
-      </c>
-      <c r="N24" s="1">
-        <v>3</v>
-      </c>
-      <c r="O24" s="1">
-        <v>0</v>
-      </c>
-      <c r="P24" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>0</v>
-      </c>
-      <c r="R24" s="1">
-        <v>0</v>
-      </c>
-      <c r="S24" s="1">
-        <v>11</v>
-      </c>
-      <c r="T24" s="1">
-        <v>0</v>
-      </c>
-      <c r="U24" s="1">
-        <v>0</v>
-      </c>
-      <c r="V24" s="1">
-        <v>5</v>
-      </c>
-      <c r="W24" s="1">
-        <v>5</v>
-      </c>
-      <c r="X24" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="1">
-        <v>0</v>
       </c>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
@@ -4040,61 +4040,61 @@
     </row>
     <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="B25" s="1">
-        <v>2203</v>
+        <v>2430</v>
       </c>
       <c r="C25" s="1">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="D25" s="1">
         <v>13</v>
       </c>
       <c r="E25" s="1">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="F25" s="1">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H25" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>11</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1">
         <v>6</v>
-      </c>
-      <c r="J25" s="1">
-        <v>5</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>11</v>
-      </c>
-      <c r="N25" s="1">
-        <v>2</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>0</v>
-      </c>
-      <c r="R25" s="1">
-        <v>0</v>
-      </c>
-      <c r="S25" s="1">
-        <v>0</v>
       </c>
       <c r="T25" s="1">
         <v>0</v>
@@ -4103,25 +4103,25 @@
         <v>5</v>
       </c>
       <c r="V25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X25" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y25" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="1">
         <v>0</v>
       </c>
       <c r="AA25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" s="1">
         <v>0</v>
@@ -4175,47 +4175,47 @@
     </row>
     <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="B26" s="1">
-        <v>2184</v>
+        <v>2398</v>
       </c>
       <c r="C26" s="1">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="D26" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E26" s="1">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="F26" s="1">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G26" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>3</v>
+      </c>
+      <c r="J26" s="1">
+        <v>7</v>
+      </c>
+      <c r="K26" s="1">
+        <v>5</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>6</v>
+      </c>
+      <c r="N26" s="1">
         <v>1</v>
       </c>
-      <c r="I26" s="1">
-        <v>1</v>
-      </c>
-      <c r="J26" s="1">
-        <v>2</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>11</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1">
-        <v>0</v>
-      </c>
       <c r="O26" s="1">
         <v>0</v>
       </c>
@@ -4229,31 +4229,31 @@
         <v>0</v>
       </c>
       <c r="S26" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T26" s="1">
         <v>0</v>
       </c>
       <c r="U26" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" s="1">
         <v>1</v>
       </c>
       <c r="W26" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X26" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y26" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z26" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="1">
         <v>0</v>
@@ -4310,22 +4310,22 @@
     </row>
     <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="B27" s="1">
-        <v>2154</v>
+        <v>2383</v>
       </c>
       <c r="C27" s="1">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D27" s="1">
         <v>13</v>
       </c>
       <c r="E27" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F27" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -4334,22 +4334,22 @@
         <v>0</v>
       </c>
       <c r="I27" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O27" s="1">
         <v>1</v>
@@ -4361,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="R27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="1">
         <v>0</v>
@@ -4370,25 +4370,25 @@
         <v>0</v>
       </c>
       <c r="U27" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z27" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA27" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
@@ -4445,49 +4445,49 @@
     </row>
     <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1">
-        <v>2145</v>
+        <v>2374</v>
       </c>
       <c r="C28" s="1">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="D28" s="1">
         <v>13</v>
       </c>
       <c r="E28" s="1">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="1">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J28" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
       </c>
       <c r="L28" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N28" s="1">
         <v>0</v>
       </c>
       <c r="O28" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28" s="1">
         <v>0</v>
@@ -4499,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T28" s="1">
         <v>0</v>
@@ -4511,10 +4511,10 @@
         <v>0</v>
       </c>
       <c r="W28" s="1">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="X28" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y28" s="1">
         <v>0</v>
@@ -4523,13 +4523,13 @@
         <v>0</v>
       </c>
       <c r="AA28" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AB28" s="1">
         <v>0</v>
       </c>
       <c r="AC28" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD28" s="1">
         <v>0</v>
@@ -4541,10 +4541,10 @@
         <v>0</v>
       </c>
       <c r="AG28" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH28" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="B29" s="1">
-        <v>2121</v>
+        <v>2360</v>
       </c>
       <c r="C29" s="1">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E29" s="1">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="F29" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -4604,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1">
         <v>0</v>
@@ -4613,13 +4613,13 @@
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N29" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O29" s="1">
         <v>0</v>
@@ -4631,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="R29" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S29" s="1">
         <v>0</v>
@@ -4655,13 +4655,13 @@
         <v>0</v>
       </c>
       <c r="Z29" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA29" s="1">
         <v>0</v>
       </c>
       <c r="AB29" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC29" s="1">
         <v>0</v>
@@ -4715,49 +4715,49 @@
     </row>
     <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1">
-        <v>2113</v>
+        <v>2291</v>
       </c>
       <c r="C30" s="1">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="D30" s="1">
         <v>13</v>
       </c>
       <c r="E30" s="1">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F30" s="1">
+        <v>16</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
+        <v>6</v>
+      </c>
+      <c r="K30" s="1">
         <v>4</v>
       </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1">
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
         <v>2</v>
       </c>
-      <c r="I30" s="1">
-        <v>9</v>
-      </c>
-      <c r="J30" s="1">
-        <v>3</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1">
-        <v>14</v>
-      </c>
-      <c r="M30" s="1">
-        <v>9</v>
-      </c>
       <c r="N30" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="1">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T30" s="1">
         <v>0</v>
@@ -4781,13 +4781,13 @@
         <v>0</v>
       </c>
       <c r="W30" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" s="1">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Y30" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="1">
         <v>0</v>
@@ -4799,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="AC30" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD30" s="1">
         <v>0</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="AH30" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
@@ -4850,22 +4850,22 @@
     </row>
     <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1">
-        <v>2074</v>
+        <v>2243</v>
       </c>
       <c r="C31" s="1">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="D31" s="1">
         <v>13</v>
       </c>
       <c r="E31" s="1">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -4874,37 +4874,37 @@
         <v>0</v>
       </c>
       <c r="I31" s="1">
+        <v>7</v>
+      </c>
+      <c r="J31" s="1">
+        <v>5</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>7</v>
+      </c>
+      <c r="N31" s="1">
+        <v>6</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1">
         <v>11</v>
-      </c>
-      <c r="J31" s="1">
-        <v>0</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
-        <v>43</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>0</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>0</v>
-      </c>
-      <c r="R31" s="1">
-        <v>0</v>
-      </c>
-      <c r="S31" s="1">
-        <v>0</v>
       </c>
       <c r="T31" s="1">
         <v>0</v>
@@ -4913,22 +4913,22 @@
         <v>5</v>
       </c>
       <c r="V31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="X31" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y31" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z31" s="1">
         <v>0</v>
       </c>
       <c r="AA31" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB31" s="1">
         <v>0</v>
@@ -4985,46 +4985,46 @@
     </row>
     <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B32" s="1">
-        <v>2061</v>
+        <v>2235</v>
       </c>
       <c r="C32" s="1">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="D32" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="F32" s="1">
+        <v>8</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>9</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>10</v>
+      </c>
+      <c r="M32" s="1">
+        <v>9</v>
+      </c>
+      <c r="N32" s="1">
         <v>4</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1">
-        <v>26</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1">
-        <v>7</v>
-      </c>
-      <c r="M32" s="1">
-        <v>13</v>
-      </c>
-      <c r="N32" s="1">
-        <v>5</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -5120,49 +5120,49 @@
     </row>
     <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="B33" s="1">
-        <v>2031</v>
+        <v>2188</v>
       </c>
       <c r="C33" s="1">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D33" s="1">
         <v>13</v>
       </c>
       <c r="E33" s="1">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F33" s="1">
+        <v>7</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
         <v>12</v>
       </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1">
-        <v>1</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
         <v>6</v>
       </c>
-      <c r="K33" s="1">
-        <v>1</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>2</v>
-      </c>
       <c r="N33" s="1">
         <v>0</v>
       </c>
       <c r="O33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="1">
         <v>0</v>
@@ -5186,14 +5186,14 @@
         <v>0</v>
       </c>
       <c r="W33" s="1">
+        <v>0</v>
+      </c>
+      <c r="X33" s="1">
+        <v>15</v>
+      </c>
+      <c r="Y33" s="1">
         <v>2</v>
       </c>
-      <c r="X33" s="1">
-        <v>19</v>
-      </c>
-      <c r="Y33" s="1">
-        <v>0</v>
-      </c>
       <c r="Z33" s="1">
         <v>0</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="AC33" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD33" s="1">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="AH33" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
@@ -5255,92 +5255,92 @@
     </row>
     <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="B34" s="1">
-        <v>2010</v>
+        <v>2181</v>
       </c>
       <c r="C34" s="1">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="D34" s="1">
         <v>13</v>
       </c>
       <c r="E34" s="1">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F34" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J34" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+      <c r="S34" s="1">
+        <v>11</v>
+      </c>
+      <c r="T34" s="1">
+        <v>0</v>
+      </c>
+      <c r="U34" s="1">
+        <v>5</v>
+      </c>
+      <c r="V34" s="1">
+        <v>0</v>
+      </c>
+      <c r="W34" s="1">
+        <v>18</v>
+      </c>
+      <c r="X34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="1">
         <v>3</v>
       </c>
-      <c r="O34" s="1">
-        <v>0</v>
-      </c>
-      <c r="P34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>0</v>
-      </c>
-      <c r="R34" s="1">
-        <v>0</v>
-      </c>
-      <c r="S34" s="1">
-        <v>0</v>
-      </c>
-      <c r="T34" s="1">
-        <v>0</v>
-      </c>
-      <c r="U34" s="1">
-        <v>0</v>
-      </c>
-      <c r="V34" s="1">
-        <v>0</v>
-      </c>
-      <c r="W34" s="1">
-        <v>0</v>
-      </c>
-      <c r="X34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="1">
-        <v>17</v>
-      </c>
-      <c r="Z34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="1">
-        <v>0</v>
-      </c>
       <c r="AD34" s="1">
         <v>0</v>
       </c>
@@ -5351,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="AG34" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH34" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
@@ -5390,22 +5390,22 @@
     </row>
     <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B35" s="1">
-        <v>2008</v>
+        <v>2167</v>
       </c>
       <c r="C35" s="1">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="D35" s="1">
         <v>13</v>
       </c>
       <c r="E35" s="1">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="F35" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -5414,19 +5414,19 @@
         <v>0</v>
       </c>
       <c r="I35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" s="1">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="N35" s="1">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T35" s="1">
         <v>0</v>
@@ -5453,16 +5453,16 @@
         <v>5</v>
       </c>
       <c r="V35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X35" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="1">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AH35" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
@@ -5525,61 +5525,61 @@
     </row>
     <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="B36" s="1">
-        <v>1978</v>
+        <v>2142</v>
       </c>
       <c r="C36" s="1">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E36" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F36" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36" s="1">
         <v>4</v>
       </c>
       <c r="K36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="1">
+        <v>2</v>
+      </c>
+      <c r="N36" s="1">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="1">
         <v>6</v>
-      </c>
-      <c r="N36" s="1">
-        <v>0</v>
-      </c>
-      <c r="O36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>0</v>
-      </c>
-      <c r="R36" s="1">
-        <v>0</v>
-      </c>
-      <c r="S36" s="1">
-        <v>0</v>
       </c>
       <c r="T36" s="1">
         <v>0</v>
@@ -5588,25 +5588,25 @@
         <v>5</v>
       </c>
       <c r="V36" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W36" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X36" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y36" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Z36" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA36" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" s="1">
         <v>0</v>
@@ -5660,46 +5660,46 @@
     </row>
     <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1">
-        <v>1972</v>
+        <v>2113</v>
       </c>
       <c r="C37" s="1">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="D37" s="1">
         <v>13</v>
       </c>
       <c r="E37" s="1">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F37" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J37" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="1">
+        <v>14</v>
+      </c>
+      <c r="M37" s="1">
+        <v>9</v>
+      </c>
+      <c r="N37" s="1">
         <v>2</v>
-      </c>
-      <c r="M37" s="1">
-        <v>2</v>
-      </c>
-      <c r="N37" s="1">
-        <v>0</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -5720,22 +5720,22 @@
         <v>0</v>
       </c>
       <c r="U37" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V37" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W37" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X37" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y37" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z37" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="1">
         <v>0</v>
@@ -5795,19 +5795,19 @@
     </row>
     <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="B38" s="1">
-        <v>1945</v>
+        <v>2095</v>
       </c>
       <c r="C38" s="1">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="D38" s="1">
         <v>13</v>
       </c>
       <c r="E38" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F38" s="1">
         <v>17</v>
@@ -5819,22 +5819,22 @@
         <v>0</v>
       </c>
       <c r="I38" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J38" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L38" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M38" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N38" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O38" s="1">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T38" s="1">
         <v>0</v>
@@ -5867,10 +5867,10 @@
         <v>0</v>
       </c>
       <c r="Y38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="1">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="AC38" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD38" s="1">
         <v>0</v>
@@ -5930,22 +5930,22 @@
     </row>
     <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="B39" s="1">
-        <v>1926</v>
+        <v>2086</v>
       </c>
       <c r="C39" s="1">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="D39" s="1">
         <v>13</v>
       </c>
       <c r="E39" s="1">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F39" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -5954,49 +5954,49 @@
         <v>0</v>
       </c>
       <c r="I39" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>43</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+      <c r="S39" s="1">
+        <v>0</v>
+      </c>
+      <c r="T39" s="1">
+        <v>0</v>
+      </c>
+      <c r="U39" s="1">
+        <v>5</v>
+      </c>
+      <c r="V39" s="1">
         <v>1</v>
       </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
-        <v>8</v>
-      </c>
-      <c r="N39" s="1">
-        <v>1</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
-      <c r="P39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>0</v>
-      </c>
-      <c r="R39" s="1">
-        <v>0</v>
-      </c>
-      <c r="S39" s="1">
-        <v>11</v>
-      </c>
-      <c r="T39" s="1">
-        <v>0</v>
-      </c>
-      <c r="U39" s="1">
-        <v>0</v>
-      </c>
-      <c r="V39" s="1">
-        <v>0</v>
-      </c>
       <c r="W39" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="X39" s="1">
         <v>0</v>
@@ -6008,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="AA39" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AB39" s="1">
         <v>0</v>
@@ -6065,46 +6065,46 @@
     </row>
     <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B40" s="1">
-        <v>1860</v>
+        <v>2061</v>
       </c>
       <c r="C40" s="1">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="D40" s="1">
         <v>13</v>
       </c>
       <c r="E40" s="1">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" s="1">
         <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M40" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N40" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O40" s="1">
         <v>0</v>
@@ -6125,16 +6125,16 @@
         <v>0</v>
       </c>
       <c r="U40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V40" s="1">
         <v>0</v>
       </c>
       <c r="W40" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X40" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="1">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AA40" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
@@ -6200,22 +6200,22 @@
     </row>
     <row r="41" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B41" s="1">
-        <v>1842</v>
+        <v>2056</v>
       </c>
       <c r="C41" s="1">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="D41" s="1">
         <v>13</v>
       </c>
       <c r="E41" s="1">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="F41" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
@@ -6227,19 +6227,19 @@
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K41" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
@@ -6251,10 +6251,10 @@
         <v>0</v>
       </c>
       <c r="R41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T41" s="1">
         <v>0</v>
@@ -6263,22 +6263,22 @@
         <v>5</v>
       </c>
       <c r="V41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X41" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z41" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB41" s="1">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="B42" s="1">
-        <v>1785</v>
+        <v>2051</v>
       </c>
       <c r="C42" s="1">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D42" s="1">
         <v>13</v>
       </c>
       <c r="E42" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F42" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
@@ -6359,13 +6359,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K42" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -6374,10 +6374,10 @@
         <v>3</v>
       </c>
       <c r="N42" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O42" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P42" s="1">
         <v>0</v>
@@ -6386,10 +6386,10 @@
         <v>0</v>
       </c>
       <c r="R42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T42" s="1">
         <v>0</v>
@@ -6398,13 +6398,13 @@
         <v>5</v>
       </c>
       <c r="V42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" s="1">
         <v>0</v>
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="AA42" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AB42" s="1">
         <v>0</v>
@@ -6434,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="AH42" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
@@ -6470,22 +6470,22 @@
     </row>
     <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="B43" s="1">
-        <v>1755</v>
+        <v>2038</v>
       </c>
       <c r="C43" s="1">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D43" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F43" s="1">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
@@ -6494,64 +6494,64 @@
         <v>0</v>
       </c>
       <c r="I43" s="1">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J43" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K43" s="1">
         <v>0</v>
       </c>
       <c r="L43" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M43" s="1">
+        <v>6</v>
+      </c>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+      <c r="S43" s="1">
+        <v>0</v>
+      </c>
+      <c r="T43" s="1">
+        <v>0</v>
+      </c>
+      <c r="U43" s="1">
+        <v>5</v>
+      </c>
+      <c r="V43" s="1">
+        <v>0</v>
+      </c>
+      <c r="W43" s="1">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1">
+        <v>12</v>
+      </c>
+      <c r="Y43" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="1">
         <v>3</v>
       </c>
-      <c r="N43" s="1">
+      <c r="AB43" s="1">
         <v>1</v>
-      </c>
-      <c r="O43" s="1">
-        <v>0</v>
-      </c>
-      <c r="P43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>0</v>
-      </c>
-      <c r="R43" s="1">
-        <v>0</v>
-      </c>
-      <c r="S43" s="1">
-        <v>0</v>
-      </c>
-      <c r="T43" s="1">
-        <v>0</v>
-      </c>
-      <c r="U43" s="1">
-        <v>0</v>
-      </c>
-      <c r="V43" s="1">
-        <v>0</v>
-      </c>
-      <c r="W43" s="1">
-        <v>0</v>
-      </c>
-      <c r="X43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="1">
-        <v>0</v>
       </c>
       <c r="AC43" s="1">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1">
-        <v>1741</v>
+        <v>2010</v>
       </c>
       <c r="C44" s="1">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D44" s="1">
         <v>13</v>
       </c>
       <c r="E44" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F44" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
@@ -6629,64 +6629,64 @@
         <v>0</v>
       </c>
       <c r="I44" s="1">
+        <v>6</v>
+      </c>
+      <c r="J44" s="1">
+        <v>6</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>3</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>0</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1">
+        <v>0</v>
+      </c>
+      <c r="X44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>17</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="1">
         <v>1</v>
-      </c>
-      <c r="J44" s="1">
-        <v>5</v>
-      </c>
-      <c r="K44" s="1">
-        <v>3</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>3</v>
-      </c>
-      <c r="N44" s="1">
-        <v>2</v>
-      </c>
-      <c r="O44" s="1">
-        <v>2</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>1</v>
-      </c>
-      <c r="S44" s="1">
-        <v>6</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1">
-        <v>5</v>
-      </c>
-      <c r="V44" s="1">
-        <v>1</v>
-      </c>
-      <c r="W44" s="1">
-        <v>1</v>
-      </c>
-      <c r="X44" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="1">
-        <v>9</v>
-      </c>
-      <c r="AB44" s="1">
-        <v>0</v>
       </c>
       <c r="AC44" s="1">
         <v>0</v>
@@ -6740,49 +6740,49 @@
     </row>
     <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B45" s="1">
-        <v>1693</v>
+        <v>1965</v>
       </c>
       <c r="C45" s="1">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D45" s="1">
         <v>13</v>
       </c>
       <c r="E45" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F45" s="1">
+        <v>18</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
         <v>3</v>
       </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="1">
-        <v>4</v>
-      </c>
-      <c r="J45" s="1">
+      <c r="N45" s="1">
+        <v>11</v>
+      </c>
+      <c r="O45" s="1">
         <v>5</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
-      <c r="L45" s="1">
-        <v>0</v>
-      </c>
-      <c r="M45" s="1">
-        <v>5</v>
-      </c>
-      <c r="N45" s="1">
-        <v>0</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
       </c>
       <c r="P45" s="1">
         <v>0</v>
@@ -6809,10 +6809,10 @@
         <v>0</v>
       </c>
       <c r="X45" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="1">
         <v>0</v>
@@ -6875,31 +6875,31 @@
     </row>
     <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="B46" s="1">
-        <v>1679</v>
+        <v>1916</v>
       </c>
       <c r="C46" s="1">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D46" s="1">
         <v>13</v>
       </c>
       <c r="E46" s="1">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1">
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J46" s="1">
         <v>0</v>
@@ -6908,44 +6908,44 @@
         <v>0</v>
       </c>
       <c r="L46" s="1">
+        <v>11</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
+        <v>0</v>
+      </c>
+      <c r="U46" s="1">
+        <v>5</v>
+      </c>
+      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1">
+        <v>7</v>
+      </c>
+      <c r="X46" s="1">
         <v>3</v>
       </c>
-      <c r="M46" s="1">
-        <v>13</v>
-      </c>
-      <c r="N46" s="1">
-        <v>0</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
-      <c r="T46" s="1">
-        <v>0</v>
-      </c>
-      <c r="U46" s="1">
-        <v>4</v>
-      </c>
-      <c r="V46" s="1">
-        <v>1</v>
-      </c>
-      <c r="W46" s="1">
-        <v>6</v>
-      </c>
-      <c r="X46" s="1">
-        <v>0</v>
-      </c>
       <c r="Y46" s="1">
         <v>0</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="AA46" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB46" s="1">
         <v>0</v>
@@ -7013,25 +7013,25 @@
         <v>66</v>
       </c>
       <c r="B47" s="1">
-        <v>1660</v>
+        <v>1794</v>
       </c>
       <c r="C47" s="1">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D47" s="1">
         <v>13</v>
       </c>
       <c r="E47" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F47" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="1">
         <v>6</v>
@@ -7070,7 +7070,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V47" s="1">
         <v>0</v>
@@ -7145,22 +7145,22 @@
     </row>
     <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B48" s="1">
-        <v>1579</v>
+        <v>1793</v>
       </c>
       <c r="C48" s="1">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D48" s="1">
         <v>13</v>
       </c>
       <c r="E48" s="1">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F48" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
@@ -7169,10 +7169,10 @@
         <v>0</v>
       </c>
       <c r="I48" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J48" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K48" s="1">
         <v>0</v>
@@ -7181,7 +7181,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="1">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="N48" s="1">
         <v>1</v>
@@ -7199,31 +7199,31 @@
         <v>0</v>
       </c>
       <c r="S48" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T48" s="1">
         <v>0</v>
       </c>
       <c r="U48" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V48" s="1">
         <v>0</v>
       </c>
       <c r="W48" s="1">
+        <v>0</v>
+      </c>
+      <c r="X48" s="1">
+        <v>12</v>
+      </c>
+      <c r="Y48" s="1">
         <v>5</v>
       </c>
-      <c r="X48" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y48" s="1">
-        <v>0</v>
-      </c>
       <c r="Z48" s="1">
         <v>0</v>
       </c>
       <c r="AA48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -7280,43 +7280,43 @@
     </row>
     <row r="49" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="B49" s="1">
-        <v>1501</v>
+        <v>1739</v>
       </c>
       <c r="C49" s="1">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D49" s="1">
         <v>13</v>
       </c>
       <c r="E49" s="1">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F49" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G49" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I49" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1">
         <v>0</v>
       </c>
       <c r="L49" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M49" s="1">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="N49" s="1">
         <v>1</v>
@@ -7340,28 +7340,28 @@
         <v>0</v>
       </c>
       <c r="U49" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V49" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W49" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X49" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="1">
         <v>1</v>
       </c>
-      <c r="Z49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="1">
-        <v>4</v>
-      </c>
       <c r="AB49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC49" s="1">
         <v>0</v>
@@ -7415,22 +7415,22 @@
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B50" s="1">
-        <v>1495</v>
+        <v>1678</v>
       </c>
       <c r="C50" s="1">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="D50" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E50" s="1">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F50" s="1">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
@@ -7439,10 +7439,10 @@
         <v>0</v>
       </c>
       <c r="I50" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K50" s="1">
         <v>0</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="M50" s="1">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
@@ -7469,34 +7469,34 @@
         <v>0</v>
       </c>
       <c r="S50" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T50" s="1">
         <v>0</v>
       </c>
       <c r="U50" s="1">
+        <v>3</v>
+      </c>
+      <c r="V50" s="1">
+        <v>0</v>
+      </c>
+      <c r="W50" s="1">
+        <v>0</v>
+      </c>
+      <c r="X50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB50" s="1">
         <v>4</v>
-      </c>
-      <c r="V50" s="1">
-        <v>0</v>
-      </c>
-      <c r="W50" s="1">
-        <v>0</v>
-      </c>
-      <c r="X50" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="1">
-        <v>0</v>
       </c>
       <c r="AC50" s="1">
         <v>0</v>
@@ -7550,43 +7550,43 @@
     </row>
     <row r="51" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="B51" s="1">
-        <v>1488</v>
+        <v>1675</v>
       </c>
       <c r="C51" s="1">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="D51" s="1">
+        <v>13</v>
+      </c>
+      <c r="E51" s="1">
+        <v>19</v>
+      </c>
+      <c r="F51" s="1">
+        <v>13</v>
+      </c>
+      <c r="G51" s="1">
+        <v>8</v>
+      </c>
+      <c r="H51" s="1">
+        <v>10</v>
+      </c>
+      <c r="I51" s="1">
         <v>5</v>
       </c>
-      <c r="E51" s="1">
-        <v>9</v>
-      </c>
-      <c r="F51" s="1">
-        <v>12</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="1">
-        <v>0</v>
-      </c>
       <c r="J51" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
         <v>0</v>
       </c>
       <c r="L51" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M51" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N51" s="1">
         <v>1</v>
@@ -7610,28 +7610,28 @@
         <v>0</v>
       </c>
       <c r="U51" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V51" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W51" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X51" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y51" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z51" s="1">
         <v>0</v>
       </c>
       <c r="AA51" s="1">
+        <v>5</v>
+      </c>
+      <c r="AB51" s="1">
         <v>1</v>
-      </c>
-      <c r="AB51" s="1">
-        <v>2</v>
       </c>
       <c r="AC51" s="1">
         <v>0</v>
@@ -7688,19 +7688,19 @@
         <v>84</v>
       </c>
       <c r="B52" s="1">
-        <v>1460</v>
+        <v>1617</v>
       </c>
       <c r="C52" s="1">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="1">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
@@ -7709,25 +7709,25 @@
         <v>0</v>
       </c>
       <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>5</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
         <v>1</v>
       </c>
-      <c r="J52" s="1">
-        <v>4</v>
-      </c>
-      <c r="K52" s="1">
-        <v>0</v>
-      </c>
-      <c r="L52" s="1">
-        <v>0</v>
-      </c>
-      <c r="M52" s="1">
-        <v>0</v>
-      </c>
       <c r="N52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O52" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P52" s="1">
         <v>0</v>
@@ -7739,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="S52" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T52" s="1">
         <v>0</v>
       </c>
       <c r="U52" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V52" s="1">
         <v>0</v>
@@ -7757,7 +7757,7 @@
         <v>0</v>
       </c>
       <c r="Y52" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="1">
         <v>0</v>
@@ -7820,34 +7820,34 @@
     </row>
     <row r="53" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="B53" s="1">
-        <v>1458</v>
+        <v>1604</v>
       </c>
       <c r="C53" s="1">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D53" s="1">
         <v>13</v>
       </c>
       <c r="E53" s="1">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F53" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
@@ -7856,7 +7856,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N53" s="1">
         <v>3</v>
@@ -7880,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V53" s="1">
         <v>0</v>
@@ -7898,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="AA53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB53" s="1">
         <v>0</v>
@@ -7955,22 +7955,22 @@
     </row>
     <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="B54" s="1">
-        <v>1457</v>
+        <v>1600</v>
       </c>
       <c r="C54" s="1">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="D54" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>0</v>
       </c>
       <c r="I54" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J54" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -7991,10 +7991,10 @@
         <v>0</v>
       </c>
       <c r="M54" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N54" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O54" s="1">
         <v>0</v>
@@ -8024,16 +8024,16 @@
         <v>0</v>
       </c>
       <c r="X54" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z54" s="1">
         <v>0</v>
       </c>
       <c r="AA54" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB54" s="1">
         <v>0</v>
@@ -8090,22 +8090,22 @@
     </row>
     <row r="55" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B55" s="1">
-        <v>1450</v>
+        <v>1588</v>
       </c>
       <c r="C55" s="1">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D55" s="1">
         <v>13</v>
       </c>
       <c r="E55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
@@ -8117,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1">
         <v>0</v>
@@ -8126,7 +8126,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N55" s="1">
         <v>3</v>
@@ -8150,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V55" s="1">
         <v>0</v>
@@ -8159,19 +8159,19 @@
         <v>0</v>
       </c>
       <c r="X55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y55" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z55" s="1">
         <v>0</v>
       </c>
       <c r="AA55" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB55" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC55" s="1">
         <v>0</v>
@@ -8225,22 +8225,22 @@
     </row>
     <row r="56" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="B56" s="1">
-        <v>1446</v>
+        <v>1586</v>
       </c>
       <c r="C56" s="1">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="D56" s="1">
         <v>13</v>
       </c>
       <c r="E56" s="1">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="F56" s="1">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
@@ -8261,10 +8261,10 @@
         <v>0</v>
       </c>
       <c r="M56" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N56" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O56" s="1">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V56" s="1">
         <v>0</v>
@@ -8294,16 +8294,16 @@
         <v>0</v>
       </c>
       <c r="X56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z56" s="1">
         <v>0</v>
       </c>
       <c r="AA56" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB56" s="1">
         <v>0</v>
@@ -8360,88 +8360,88 @@
     </row>
     <row r="57" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B57" s="1">
-        <v>1416</v>
+        <v>1567</v>
       </c>
       <c r="C57" s="1">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="D57" s="1">
         <v>13</v>
       </c>
       <c r="E57" s="1">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="F57" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1">
+        <v>4</v>
+      </c>
+      <c r="I57" s="1">
+        <v>5</v>
+      </c>
+      <c r="J57" s="1">
+        <v>3</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>5</v>
+      </c>
+      <c r="N57" s="1">
+        <v>4</v>
+      </c>
+      <c r="O57" s="1">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="1">
+        <v>0</v>
+      </c>
+      <c r="T57" s="1">
+        <v>0</v>
+      </c>
+      <c r="U57" s="1">
+        <v>2</v>
+      </c>
+      <c r="V57" s="1">
+        <v>0</v>
+      </c>
+      <c r="W57" s="1">
         <v>1</v>
-      </c>
-      <c r="I57" s="1">
-        <v>4</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
-      <c r="K57" s="1">
-        <v>0</v>
-      </c>
-      <c r="L57" s="1">
-        <v>4</v>
-      </c>
-      <c r="M57" s="1">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1">
-        <v>0</v>
-      </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
-      <c r="T57" s="1">
-        <v>0</v>
-      </c>
-      <c r="U57" s="1">
-        <v>0</v>
-      </c>
-      <c r="V57" s="1">
-        <v>2</v>
-      </c>
-      <c r="W57" s="1">
-        <v>4</v>
       </c>
       <c r="X57" s="1">
         <v>7</v>
       </c>
       <c r="Y57" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="1">
         <v>1</v>
       </c>
-      <c r="Z57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="1">
-        <v>2</v>
-      </c>
       <c r="AB57" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" s="1">
         <v>0</v>
@@ -8495,34 +8495,34 @@
     </row>
     <row r="58" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="B58" s="1">
-        <v>1330</v>
+        <v>1561</v>
       </c>
       <c r="C58" s="1">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="D58" s="1">
+        <v>13</v>
+      </c>
+      <c r="E58" s="1">
+        <v>48</v>
+      </c>
+      <c r="F58" s="1">
+        <v>3</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
         <v>5</v>
       </c>
-      <c r="E58" s="1">
-        <v>0</v>
-      </c>
-      <c r="F58" s="1">
-        <v>37</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
-        <v>0</v>
-      </c>
       <c r="J58" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
@@ -8531,13 +8531,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N58" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O58" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P58" s="1">
         <v>0</v>
@@ -8549,13 +8549,13 @@
         <v>0</v>
       </c>
       <c r="S58" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T58" s="1">
         <v>0</v>
       </c>
       <c r="U58" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V58" s="1">
         <v>0</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="X58" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="1">
         <v>0</v>
@@ -8630,88 +8630,88 @@
     </row>
     <row r="59" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B59" s="1">
-        <v>1326</v>
+        <v>1516</v>
       </c>
       <c r="C59" s="1">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="D59" s="1">
         <v>13</v>
       </c>
       <c r="E59" s="1">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="F59" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J59" s="1">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1">
+        <v>6</v>
+      </c>
+      <c r="M59" s="1">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1">
+        <v>0</v>
+      </c>
+      <c r="O59" s="1">
+        <v>0</v>
+      </c>
+      <c r="P59" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+      <c r="S59" s="1">
+        <v>0</v>
+      </c>
+      <c r="T59" s="1">
+        <v>0</v>
+      </c>
+      <c r="U59" s="1">
+        <v>0</v>
+      </c>
+      <c r="V59" s="1">
+        <v>2</v>
+      </c>
+      <c r="W59" s="1">
+        <v>4</v>
+      </c>
+      <c r="X59" s="1">
+        <v>7</v>
+      </c>
+      <c r="Y59" s="1">
         <v>1</v>
       </c>
-      <c r="K59" s="1">
-        <v>0</v>
-      </c>
-      <c r="L59" s="1">
-        <v>0</v>
-      </c>
-      <c r="M59" s="1">
-        <v>0</v>
-      </c>
-      <c r="N59" s="1">
-        <v>6</v>
-      </c>
-      <c r="O59" s="1">
-        <v>0</v>
-      </c>
-      <c r="P59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="1">
-        <v>0</v>
-      </c>
-      <c r="R59" s="1">
-        <v>0</v>
-      </c>
-      <c r="S59" s="1">
-        <v>0</v>
-      </c>
-      <c r="T59" s="1">
-        <v>0</v>
-      </c>
-      <c r="U59" s="1">
-        <v>0</v>
-      </c>
-      <c r="V59" s="1">
-        <v>0</v>
-      </c>
-      <c r="W59" s="1">
-        <v>0</v>
-      </c>
-      <c r="X59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="1">
-        <v>0</v>
-      </c>
       <c r="Z59" s="1">
         <v>0</v>
       </c>
       <c r="AA59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC59" s="1">
         <v>0</v>
@@ -8765,10 +8765,10 @@
     </row>
     <row r="60" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B60" s="1">
-        <v>1326</v>
+        <v>1507</v>
       </c>
       <c r="C60" s="1">
         <v>67</v>
@@ -8777,73 +8777,73 @@
         <v>13</v>
       </c>
       <c r="E60" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
         <v>4</v>
       </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="1">
-        <v>24</v>
-      </c>
       <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>19</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0</v>
+      </c>
+      <c r="U60" s="1">
+        <v>5</v>
+      </c>
+      <c r="V60" s="1">
+        <v>0</v>
+      </c>
+      <c r="W60" s="1">
+        <v>0</v>
+      </c>
+      <c r="X60" s="1">
+        <v>9</v>
+      </c>
+      <c r="Y60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="1">
         <v>6</v>
-      </c>
-      <c r="K60" s="1">
-        <v>0</v>
-      </c>
-      <c r="L60" s="1">
-        <v>2</v>
-      </c>
-      <c r="M60" s="1">
-        <v>4</v>
-      </c>
-      <c r="N60" s="1">
-        <v>1</v>
-      </c>
-      <c r="O60" s="1">
-        <v>0</v>
-      </c>
-      <c r="P60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="1">
-        <v>0</v>
-      </c>
-      <c r="R60" s="1">
-        <v>0</v>
-      </c>
-      <c r="S60" s="1">
-        <v>0</v>
-      </c>
-      <c r="T60" s="1">
-        <v>0</v>
-      </c>
-      <c r="U60" s="1">
-        <v>0</v>
-      </c>
-      <c r="V60" s="1">
-        <v>0</v>
-      </c>
-      <c r="W60" s="1">
-        <v>0</v>
-      </c>
-      <c r="X60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="1">
-        <v>0</v>
       </c>
       <c r="AB60" s="1">
         <v>0</v>
@@ -8900,22 +8900,22 @@
     </row>
     <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B61" s="1">
-        <v>1265</v>
+        <v>1496</v>
       </c>
       <c r="C61" s="1">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D61" s="1">
         <v>13</v>
       </c>
       <c r="E61" s="1">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F61" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
@@ -8927,7 +8927,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
@@ -8936,10 +8936,10 @@
         <v>0</v>
       </c>
       <c r="M61" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" s="1">
         <v>0</v>
@@ -8969,10 +8969,10 @@
         <v>0</v>
       </c>
       <c r="X61" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y61" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z61" s="1">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="62" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>1218</v>
+        <v>1478</v>
       </c>
       <c r="C62" s="1">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="D62" s="1">
         <v>13</v>
       </c>
       <c r="E62" s="1">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F62" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
@@ -9059,10 +9059,10 @@
         <v>0</v>
       </c>
       <c r="I62" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -9071,10 +9071,10 @@
         <v>0</v>
       </c>
       <c r="M62" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N62" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O62" s="1">
         <v>0</v>
@@ -9104,7 +9104,7 @@
         <v>0</v>
       </c>
       <c r="X62" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="1">
         <v>0</v>
@@ -9113,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="AA62" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB62" s="1">
         <v>0</v>
@@ -9170,23 +9170,23 @@
     </row>
     <row r="63" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B63" s="1">
-        <v>1188</v>
+        <v>1380</v>
       </c>
       <c r="C63" s="1">
+        <v>60</v>
+      </c>
+      <c r="D63" s="1">
+        <v>5</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="1">
         <v>37</v>
       </c>
-      <c r="D63" s="1">
-        <v>13</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0</v>
-      </c>
-      <c r="F63" s="1">
-        <v>3</v>
-      </c>
       <c r="G63" s="1">
         <v>0</v>
       </c>
@@ -9197,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
@@ -9209,10 +9209,10 @@
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P63" s="1">
         <v>0</v>
@@ -9224,34 +9224,34 @@
         <v>0</v>
       </c>
       <c r="S63" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T63" s="1">
         <v>0</v>
       </c>
       <c r="U63" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V63" s="1">
         <v>0</v>
       </c>
       <c r="W63" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X63" s="1">
         <v>0</v>
       </c>
       <c r="Y63" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z63" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA63" s="1">
         <v>0</v>
       </c>
       <c r="AB63" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC63" s="1">
         <v>0</v>
@@ -9305,50 +9305,50 @@
     </row>
     <row r="64" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B64" s="1">
-        <v>1180</v>
+        <v>1348</v>
       </c>
       <c r="C64" s="1">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D64" s="1">
         <v>13</v>
       </c>
       <c r="E64" s="1">
+        <v>31</v>
+      </c>
+      <c r="F64" s="1">
         <v>11</v>
       </c>
-      <c r="F64" s="1">
-        <v>9</v>
-      </c>
       <c r="G64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <v>0</v>
+      </c>
+      <c r="N64" s="1">
+        <v>2</v>
+      </c>
+      <c r="O64" s="1">
         <v>3</v>
       </c>
-      <c r="K64" s="1">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1">
-        <v>0</v>
-      </c>
-      <c r="M64" s="1">
-        <v>2</v>
-      </c>
-      <c r="N64" s="1">
-        <v>0</v>
-      </c>
-      <c r="O64" s="1">
-        <v>0</v>
-      </c>
       <c r="P64" s="1">
         <v>0</v>
       </c>
@@ -9359,31 +9359,31 @@
         <v>0</v>
       </c>
       <c r="S64" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T64" s="1">
         <v>0</v>
       </c>
       <c r="U64" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V64" s="1">
         <v>0</v>
       </c>
       <c r="W64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X64" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y64" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z64" s="1">
         <v>0</v>
       </c>
       <c r="AA64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB64" s="1">
         <v>0</v>
@@ -9440,49 +9440,49 @@
     </row>
     <row r="65" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B65" s="1">
-        <v>1178</v>
+        <v>1326</v>
       </c>
       <c r="C65" s="1">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D65" s="1">
         <v>13</v>
       </c>
       <c r="E65" s="1">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F65" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
       </c>
       <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1">
+        <v>24</v>
+      </c>
+      <c r="J65" s="1">
+        <v>6</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
         <v>2</v>
       </c>
-      <c r="I65" s="1">
-        <v>0</v>
-      </c>
-      <c r="J65" s="1">
-        <v>0</v>
-      </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
-      <c r="L65" s="1">
-        <v>0</v>
-      </c>
       <c r="M65" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N65" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P65" s="1">
         <v>0</v>
@@ -9494,13 +9494,13 @@
         <v>0</v>
       </c>
       <c r="S65" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T65" s="1">
         <v>0</v>
       </c>
       <c r="U65" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V65" s="1">
         <v>0</v>
@@ -9575,13 +9575,13 @@
     </row>
     <row r="66" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B66" s="1">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="C66" s="1">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
@@ -9710,22 +9710,22 @@
     </row>
     <row r="67" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="B67" s="1">
-        <v>1142</v>
+        <v>1188</v>
       </c>
       <c r="C67" s="1">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D67" s="1">
         <v>13</v>
       </c>
       <c r="E67" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F67" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
@@ -9734,11 +9734,11 @@
         <v>0</v>
       </c>
       <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
         <v>3</v>
       </c>
-      <c r="J67" s="1">
-        <v>1</v>
-      </c>
       <c r="K67" s="1">
         <v>0</v>
       </c>
@@ -9746,52 +9746,52 @@
         <v>0</v>
       </c>
       <c r="M67" s="1">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>0</v>
+      </c>
+      <c r="O67" s="1">
+        <v>0</v>
+      </c>
+      <c r="P67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>0</v>
+      </c>
+      <c r="R67" s="1">
+        <v>0</v>
+      </c>
+      <c r="S67" s="1">
+        <v>3</v>
+      </c>
+      <c r="T67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="1">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1">
+        <v>0</v>
+      </c>
+      <c r="W67" s="1">
         <v>2</v>
       </c>
-      <c r="N67" s="1">
+      <c r="X67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z67" s="1">
         <v>3</v>
       </c>
-      <c r="O67" s="1">
-        <v>0</v>
-      </c>
-      <c r="P67" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="1">
-        <v>0</v>
-      </c>
-      <c r="R67" s="1">
-        <v>0</v>
-      </c>
-      <c r="S67" s="1">
-        <v>11</v>
-      </c>
-      <c r="T67" s="1">
-        <v>0</v>
-      </c>
-      <c r="U67" s="1">
+      <c r="AA67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="1">
         <v>5</v>
-      </c>
-      <c r="V67" s="1">
-        <v>0</v>
-      </c>
-      <c r="W67" s="1">
-        <v>0</v>
-      </c>
-      <c r="X67" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y67" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z67" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA67" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB67" s="1">
-        <v>0</v>
       </c>
       <c r="AC67" s="1">
         <v>0</v>
@@ -9845,49 +9845,49 @@
     </row>
     <row r="68" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B68" s="1">
-        <v>1073</v>
+        <v>1170</v>
       </c>
       <c r="C68" s="1">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D68" s="1">
         <v>13</v>
       </c>
       <c r="E68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F68" s="1">
+        <v>25</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
         <v>2</v>
       </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1">
-        <v>0</v>
-      </c>
-      <c r="I68" s="1">
-        <v>8</v>
-      </c>
-      <c r="J68" s="1">
-        <v>0</v>
-      </c>
-      <c r="K68" s="1">
-        <v>0</v>
-      </c>
-      <c r="L68" s="1">
-        <v>0</v>
-      </c>
-      <c r="M68" s="1">
-        <v>15</v>
-      </c>
       <c r="N68" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P68" s="1">
         <v>0</v>
@@ -9905,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V68" s="1">
         <v>0</v>
@@ -9914,16 +9914,16 @@
         <v>0</v>
       </c>
       <c r="X68" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA68" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB68" s="1">
         <v>0</v>
@@ -9980,22 +9980,22 @@
     </row>
     <row r="69" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B69" s="1">
-        <v>1050</v>
+        <v>1073</v>
       </c>
       <c r="C69" s="1">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D69" s="1">
         <v>13</v>
       </c>
       <c r="E69" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
@@ -10004,61 +10004,61 @@
         <v>0</v>
       </c>
       <c r="I69" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
+        <v>15</v>
+      </c>
+      <c r="N69" s="1">
+        <v>0</v>
+      </c>
+      <c r="O69" s="1">
+        <v>0</v>
+      </c>
+      <c r="P69" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>0</v>
+      </c>
+      <c r="R69" s="1">
+        <v>0</v>
+      </c>
+      <c r="S69" s="1">
+        <v>0</v>
+      </c>
+      <c r="T69" s="1">
+        <v>0</v>
+      </c>
+      <c r="U69" s="1">
+        <v>5</v>
+      </c>
+      <c r="V69" s="1">
+        <v>0</v>
+      </c>
+      <c r="W69" s="1">
+        <v>0</v>
+      </c>
+      <c r="X69" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y69" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="1">
         <v>1</v>
-      </c>
-      <c r="K69" s="1">
-        <v>1</v>
-      </c>
-      <c r="L69" s="1">
-        <v>0</v>
-      </c>
-      <c r="M69" s="1">
-        <v>2</v>
-      </c>
-      <c r="N69" s="1">
-        <v>1</v>
-      </c>
-      <c r="O69" s="1">
-        <v>1</v>
-      </c>
-      <c r="P69" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="1">
-        <v>0</v>
-      </c>
-      <c r="R69" s="1">
-        <v>0</v>
-      </c>
-      <c r="S69" s="1">
-        <v>0</v>
-      </c>
-      <c r="T69" s="1">
-        <v>0</v>
-      </c>
-      <c r="U69" s="1">
-        <v>0</v>
-      </c>
-      <c r="V69" s="1">
-        <v>0</v>
-      </c>
-      <c r="W69" s="1">
-        <v>0</v>
-      </c>
-      <c r="X69" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z69" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA69" s="1">
-        <v>0</v>
       </c>
       <c r="AB69" s="1">
         <v>0</v>
@@ -10115,13 +10115,13 @@
     </row>
     <row r="70" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B70" s="1">
-        <v>1035</v>
+        <v>1051</v>
       </c>
       <c r="C70" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D70" s="1">
         <v>5</v>
@@ -10136,7 +10136,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I70" s="1">
         <v>12</v>
@@ -10250,22 +10250,22 @@
     </row>
     <row r="71" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B71" s="1">
-        <v>902</v>
+        <v>1032</v>
       </c>
       <c r="C71" s="1">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D71" s="1">
         <v>13</v>
       </c>
       <c r="E71" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F71" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
@@ -10274,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J71" s="1">
         <v>0</v>
@@ -10286,11 +10286,11 @@
         <v>0</v>
       </c>
       <c r="M71" s="1">
+        <v>6</v>
+      </c>
+      <c r="N71" s="1">
         <v>4</v>
       </c>
-      <c r="N71" s="1">
-        <v>0</v>
-      </c>
       <c r="O71" s="1">
         <v>0</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T71" s="1">
         <v>0</v>
@@ -10316,10 +10316,10 @@
         <v>0</v>
       </c>
       <c r="W71" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y71" s="1">
         <v>0</v>
@@ -10385,85 +10385,85 @@
     </row>
     <row r="72" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B72" s="1">
-        <v>897</v>
+        <v>1007</v>
       </c>
       <c r="C72" s="1">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1">
+        <v>16</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
+        <v>17</v>
+      </c>
+      <c r="N72" s="1">
+        <v>0</v>
+      </c>
+      <c r="O72" s="1">
+        <v>0</v>
+      </c>
+      <c r="P72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1">
+        <v>0</v>
+      </c>
+      <c r="S72" s="1">
+        <v>11</v>
+      </c>
+      <c r="T72" s="1">
+        <v>0</v>
+      </c>
+      <c r="U72" s="1">
+        <v>4</v>
+      </c>
+      <c r="V72" s="1">
+        <v>0</v>
+      </c>
+      <c r="W72" s="1">
+        <v>0</v>
+      </c>
+      <c r="X72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="1">
         <v>1</v>
-      </c>
-      <c r="F72" s="1">
-        <v>16</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0</v>
-      </c>
-      <c r="H72" s="1">
-        <v>0</v>
-      </c>
-      <c r="I72" s="1">
-        <v>0</v>
-      </c>
-      <c r="J72" s="1">
-        <v>5</v>
-      </c>
-      <c r="K72" s="1">
-        <v>0</v>
-      </c>
-      <c r="L72" s="1">
-        <v>0</v>
-      </c>
-      <c r="M72" s="1">
-        <v>1</v>
-      </c>
-      <c r="N72" s="1">
-        <v>0</v>
-      </c>
-      <c r="O72" s="1">
-        <v>2</v>
-      </c>
-      <c r="P72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="1">
-        <v>0</v>
-      </c>
-      <c r="R72" s="1">
-        <v>0</v>
-      </c>
-      <c r="S72" s="1">
-        <v>6</v>
-      </c>
-      <c r="T72" s="1">
-        <v>0</v>
-      </c>
-      <c r="U72" s="1">
-        <v>5</v>
-      </c>
-      <c r="V72" s="1">
-        <v>0</v>
-      </c>
-      <c r="W72" s="1">
-        <v>0</v>
-      </c>
-      <c r="X72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="1">
-        <v>0</v>
       </c>
       <c r="AB72" s="1">
         <v>0</v>
@@ -10520,22 +10520,22 @@
     </row>
     <row r="73" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B73" s="1">
-        <v>850</v>
+        <v>902</v>
       </c>
       <c r="C73" s="1">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D73" s="1">
         <v>13</v>
       </c>
       <c r="E73" s="1">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F73" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
@@ -10544,52 +10544,52 @@
         <v>0</v>
       </c>
       <c r="I73" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J73" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0</v>
+      </c>
+      <c r="M73" s="1">
+        <v>4</v>
+      </c>
+      <c r="N73" s="1">
+        <v>0</v>
+      </c>
+      <c r="O73" s="1">
+        <v>0</v>
+      </c>
+      <c r="P73" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>0</v>
+      </c>
+      <c r="R73" s="1">
+        <v>0</v>
+      </c>
+      <c r="S73" s="1">
+        <v>6</v>
+      </c>
+      <c r="T73" s="1">
+        <v>0</v>
+      </c>
+      <c r="U73" s="1">
+        <v>0</v>
+      </c>
+      <c r="V73" s="1">
+        <v>0</v>
+      </c>
+      <c r="W73" s="1">
         <v>1</v>
       </c>
-      <c r="L73" s="1">
-        <v>0</v>
-      </c>
-      <c r="M73" s="1">
-        <v>0</v>
-      </c>
-      <c r="N73" s="1">
-        <v>2</v>
-      </c>
-      <c r="O73" s="1">
-        <v>0</v>
-      </c>
-      <c r="P73" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="1">
-        <v>0</v>
-      </c>
-      <c r="R73" s="1">
-        <v>0</v>
-      </c>
-      <c r="S73" s="1">
-        <v>0</v>
-      </c>
-      <c r="T73" s="1">
-        <v>0</v>
-      </c>
-      <c r="U73" s="1">
-        <v>0</v>
-      </c>
-      <c r="V73" s="1">
-        <v>0</v>
-      </c>
-      <c r="W73" s="1">
-        <v>0</v>
-      </c>
       <c r="X73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y73" s="1">
         <v>0</v>
@@ -10655,13 +10655,13 @@
     </row>
     <row r="74" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B74" s="1">
-        <v>815</v>
+        <v>855</v>
       </c>
       <c r="C74" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D74" s="1">
         <v>13</v>
@@ -10715,7 +10715,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V74" s="1">
         <v>0</v>
@@ -10790,22 +10790,22 @@
     </row>
     <row r="75" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="B75" s="1">
-        <v>679</v>
+        <v>852</v>
       </c>
       <c r="C75" s="1">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D75" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F75" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
@@ -10823,16 +10823,16 @@
         <v>0</v>
       </c>
       <c r="L75" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M75" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N75" s="1">
         <v>0</v>
       </c>
       <c r="O75" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P75" s="1">
         <v>0</v>
@@ -10844,13 +10844,13 @@
         <v>0</v>
       </c>
       <c r="S75" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T75" s="1">
         <v>0</v>
       </c>
       <c r="U75" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V75" s="1">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="AA75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB75" s="1">
         <v>0</v>
@@ -10889,7 +10889,7 @@
         <v>0</v>
       </c>
       <c r="AH75" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1"/>
@@ -10925,47 +10925,47 @@
     </row>
     <row r="76" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B76" s="1">
-        <v>674</v>
+        <v>850</v>
       </c>
       <c r="C76" s="1">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D76" s="1">
         <v>13</v>
       </c>
       <c r="E76" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F76" s="1">
+        <v>8</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>3</v>
+      </c>
+      <c r="J76" s="1">
+        <v>8</v>
+      </c>
+      <c r="K76" s="1">
+        <v>1</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1">
         <v>2</v>
       </c>
-      <c r="G76" s="1">
-        <v>0</v>
-      </c>
-      <c r="H76" s="1">
-        <v>0</v>
-      </c>
-      <c r="I76" s="1">
-        <v>0</v>
-      </c>
-      <c r="J76" s="1">
-        <v>0</v>
-      </c>
-      <c r="K76" s="1">
-        <v>0</v>
-      </c>
-      <c r="L76" s="1">
-        <v>0</v>
-      </c>
-      <c r="M76" s="1">
-        <v>0</v>
-      </c>
-      <c r="N76" s="1">
-        <v>0</v>
-      </c>
       <c r="O76" s="1">
         <v>0</v>
       </c>
@@ -10994,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y76" s="1">
         <v>0</v>
@@ -11006,7 +11006,7 @@
         <v>0</v>
       </c>
       <c r="AB76" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC76" s="1">
         <v>0</v>
@@ -11060,19 +11060,19 @@
     </row>
     <row r="77" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="B77" s="1">
-        <v>592</v>
+        <v>748</v>
       </c>
       <c r="C77" s="1">
         <v>40</v>
       </c>
       <c r="D77" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -11081,10 +11081,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I77" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J77" s="1">
         <v>0</v>
@@ -11093,13 +11093,13 @@
         <v>0</v>
       </c>
       <c r="L77" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M77" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" s="1">
         <v>0</v>
@@ -11114,22 +11114,22 @@
         <v>0</v>
       </c>
       <c r="S77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" s="1">
         <v>0</v>
       </c>
       <c r="U77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V77" s="1">
         <v>0</v>
       </c>
       <c r="W77" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X77" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y77" s="1">
         <v>0</v>
@@ -11195,22 +11195,22 @@
     </row>
     <row r="78" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="B78" s="1">
-        <v>460</v>
+        <v>674</v>
       </c>
       <c r="C78" s="1">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D78" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E78" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F78" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
@@ -11237,46 +11237,46 @@
         <v>0</v>
       </c>
       <c r="O78" s="1">
+        <v>0</v>
+      </c>
+      <c r="P78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>0</v>
+      </c>
+      <c r="R78" s="1">
+        <v>0</v>
+      </c>
+      <c r="S78" s="1">
+        <v>0</v>
+      </c>
+      <c r="T78" s="1">
+        <v>0</v>
+      </c>
+      <c r="U78" s="1">
+        <v>0</v>
+      </c>
+      <c r="V78" s="1">
+        <v>0</v>
+      </c>
+      <c r="W78" s="1">
+        <v>0</v>
+      </c>
+      <c r="X78" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="1">
         <v>1</v>
-      </c>
-      <c r="P78" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="1">
-        <v>0</v>
-      </c>
-      <c r="R78" s="1">
-        <v>0</v>
-      </c>
-      <c r="S78" s="1">
-        <v>6</v>
-      </c>
-      <c r="T78" s="1">
-        <v>0</v>
-      </c>
-      <c r="U78" s="1">
-        <v>5</v>
-      </c>
-      <c r="V78" s="1">
-        <v>0</v>
-      </c>
-      <c r="W78" s="1">
-        <v>0</v>
-      </c>
-      <c r="X78" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB78" s="1">
-        <v>0</v>
       </c>
       <c r="AC78" s="1">
         <v>0</v>
@@ -11330,19 +11330,19 @@
     </row>
     <row r="79" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="B79" s="1">
-        <v>451</v>
+        <v>630</v>
       </c>
       <c r="C79" s="1">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D79" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -11366,7 +11366,7 @@
         <v>0</v>
       </c>
       <c r="M79" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N79" s="1">
         <v>0</v>
@@ -11390,13 +11390,13 @@
         <v>0</v>
       </c>
       <c r="U79" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V79" s="1">
         <v>0</v>
       </c>
       <c r="W79" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X79" s="1">
         <v>0</v>
@@ -11408,7 +11408,7 @@
         <v>0</v>
       </c>
       <c r="AA79" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB79" s="1">
         <v>0</v>
@@ -11465,79 +11465,79 @@
     </row>
     <row r="80" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B80" s="1">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="C80" s="1">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D80" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
       </c>
       <c r="F80" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
       </c>
       <c r="H80" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I80" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
       </c>
       <c r="L80" s="1">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1">
         <v>2</v>
       </c>
-      <c r="M80" s="1">
+      <c r="O80" s="1">
+        <v>0</v>
+      </c>
+      <c r="P80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>0</v>
+      </c>
+      <c r="R80" s="1">
+        <v>0</v>
+      </c>
+      <c r="S80" s="1">
+        <v>0</v>
+      </c>
+      <c r="T80" s="1">
+        <v>0</v>
+      </c>
+      <c r="U80" s="1">
+        <v>0</v>
+      </c>
+      <c r="V80" s="1">
+        <v>0</v>
+      </c>
+      <c r="W80" s="1">
+        <v>0</v>
+      </c>
+      <c r="X80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="1">
         <v>1</v>
-      </c>
-      <c r="N80" s="1">
-        <v>0</v>
-      </c>
-      <c r="O80" s="1">
-        <v>0</v>
-      </c>
-      <c r="P80" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="1">
-        <v>0</v>
-      </c>
-      <c r="R80" s="1">
-        <v>0</v>
-      </c>
-      <c r="S80" s="1">
-        <v>1</v>
-      </c>
-      <c r="T80" s="1">
-        <v>0</v>
-      </c>
-      <c r="U80" s="1">
-        <v>1</v>
-      </c>
-      <c r="V80" s="1">
-        <v>0</v>
-      </c>
-      <c r="W80" s="1">
-        <v>6</v>
-      </c>
-      <c r="X80" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y80" s="1">
-        <v>0</v>
       </c>
       <c r="Z80" s="1">
         <v>0</v>
@@ -11600,85 +11600,85 @@
     </row>
     <row r="81" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B81" s="1">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="C81" s="1">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D81" s="1">
+        <v>13</v>
+      </c>
+      <c r="E81" s="1">
+        <v>12</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1">
+        <v>0</v>
+      </c>
+      <c r="L81" s="1">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>3</v>
+      </c>
+      <c r="N81" s="1">
+        <v>0</v>
+      </c>
+      <c r="O81" s="1">
+        <v>0</v>
+      </c>
+      <c r="P81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>0</v>
+      </c>
+      <c r="R81" s="1">
+        <v>0</v>
+      </c>
+      <c r="S81" s="1">
+        <v>0</v>
+      </c>
+      <c r="T81" s="1">
+        <v>0</v>
+      </c>
+      <c r="U81" s="1">
         <v>4</v>
       </c>
-      <c r="E81" s="1">
-        <v>0</v>
-      </c>
-      <c r="F81" s="1">
-        <v>9</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0</v>
-      </c>
-      <c r="H81" s="1">
-        <v>0</v>
-      </c>
-      <c r="I81" s="1">
-        <v>0</v>
-      </c>
-      <c r="J81" s="1">
+      <c r="V81" s="1">
+        <v>0</v>
+      </c>
+      <c r="W81" s="1">
+        <v>5</v>
+      </c>
+      <c r="X81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="1">
         <v>1</v>
-      </c>
-      <c r="K81" s="1">
-        <v>0</v>
-      </c>
-      <c r="L81" s="1">
-        <v>0</v>
-      </c>
-      <c r="M81" s="1">
-        <v>0</v>
-      </c>
-      <c r="N81" s="1">
-        <v>2</v>
-      </c>
-      <c r="O81" s="1">
-        <v>0</v>
-      </c>
-      <c r="P81" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="1">
-        <v>0</v>
-      </c>
-      <c r="R81" s="1">
-        <v>0</v>
-      </c>
-      <c r="S81" s="1">
-        <v>0</v>
-      </c>
-      <c r="T81" s="1">
-        <v>0</v>
-      </c>
-      <c r="U81" s="1">
-        <v>0</v>
-      </c>
-      <c r="V81" s="1">
-        <v>0</v>
-      </c>
-      <c r="W81" s="1">
-        <v>0</v>
-      </c>
-      <c r="X81" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z81" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="1">
-        <v>0</v>
       </c>
       <c r="AB81" s="1">
         <v>0</v>
@@ -11735,22 +11735,22 @@
     </row>
     <row r="82" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B82" s="1">
-        <v>220</v>
+        <v>460</v>
       </c>
       <c r="C82" s="1">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D82" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
       </c>
       <c r="F82" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -11777,7 +11777,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P82" s="1">
         <v>0</v>
@@ -11789,13 +11789,13 @@
         <v>0</v>
       </c>
       <c r="S82" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T82" s="1">
         <v>0</v>
       </c>
       <c r="U82" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V82" s="1">
         <v>0</v>
@@ -11813,7 +11813,7 @@
         <v>0</v>
       </c>
       <c r="AA82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB82" s="1">
         <v>0</v>
@@ -12140,7 +12140,7 @@
     </row>
     <row r="85" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B85" s="1">
         <v>130</v>
@@ -13085,7 +13085,7 @@
     </row>
     <row r="92" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B92" s="1">
         <v>0</v>
@@ -13220,7 +13220,7 @@
     </row>
     <row r="93" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B93" s="1">
         <v>0</v>
